--- a/results/tables/NSGA-II收敛曲线数据.xlsx
+++ b/results/tables/NSGA-II收敛曲线数据.xlsx
@@ -465,19 +465,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>528.4</v>
+        <v>720</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.046284310616976e-06</v>
+        <v>3.52757981448728e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -485,19 +485,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>487.6</v>
+        <v>640.4</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.501782876926775e-06</v>
+        <v>3.52757981448728e-06</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -505,19 +505,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>463.2</v>
+        <v>640.4</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.431691254345785e-06</v>
+        <v>3.52757981448728e-06</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -525,19 +525,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>463.2</v>
+        <v>613.6</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.139754965754472e-06</v>
+        <v>2.57323545212612e-06</v>
       </c>
       <c r="E5" t="n">
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -545,19 +545,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>456.4</v>
+        <v>613.6</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.139754965754472e-06</v>
+        <v>2.195127106333026e-06</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +565,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>411.2</v>
+        <v>547.6</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.539187726463023e-06</v>
+        <v>2.195127106333026e-06</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -585,19 +585,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>383.2</v>
+        <v>476.4</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4.539187726463023e-06</v>
+        <v>1.471897504185953e-06</v>
       </c>
       <c r="E8" t="n">
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -605,19 +605,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>351.2</v>
+        <v>437.6</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>4.002663998697251e-06</v>
+        <v>1.266807171719807e-06</v>
       </c>
       <c r="E9" t="n">
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -625,19 +625,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>344.8</v>
+        <v>409.6</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3.735961114580082e-06</v>
+        <v>1.082125089661989e-06</v>
       </c>
       <c r="E10" t="n">
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -645,19 +645,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>318.4</v>
+        <v>404</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.722442460186423e-06</v>
+        <v>1.082125089661989e-06</v>
       </c>
       <c r="E11" t="n">
         <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -665,19 +665,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>264</v>
+        <v>404</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.661746664997297e-06</v>
+        <v>1.009671983906521e-06</v>
       </c>
       <c r="E12" t="n">
         <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -685,19 +685,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>254.8</v>
+        <v>387.2</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.632292219086279e-06</v>
+        <v>8.279397308833682e-07</v>
       </c>
       <c r="E13" t="n">
         <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -705,19 +705,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>248</v>
+        <v>387.2</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.203673946009421e-06</v>
+        <v>8.279397308833682e-07</v>
       </c>
       <c r="E14" t="n">
         <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -725,19 +725,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>248</v>
+        <v>308.8</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.203673946009421e-06</v>
+        <v>6.044692053261508e-07</v>
       </c>
       <c r="E15" t="n">
         <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -745,19 +745,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>248</v>
+        <v>307.6</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.203673946009421e-06</v>
+        <v>5.441628669664438e-07</v>
       </c>
       <c r="E16" t="n">
         <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -765,19 +765,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>241.6</v>
+        <v>306.4</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.203673946009421e-06</v>
+        <v>5.441628669664438e-07</v>
       </c>
       <c r="E17" t="n">
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -785,19 +785,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>241.6</v>
+        <v>304</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.980067291883172e-06</v>
+        <v>5.397055178436672e-07</v>
       </c>
       <c r="E18" t="n">
         <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -805,19 +805,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>237.6</v>
+        <v>304</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.96244112264312e-06</v>
+        <v>5.044189592783209e-07</v>
       </c>
       <c r="E19" t="n">
         <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -825,19 +825,19 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>207.6</v>
+        <v>234.4</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.96244112264312e-06</v>
+        <v>3.135265505844914e-07</v>
       </c>
       <c r="E20" t="n">
         <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -845,19 +845,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>207.6</v>
+        <v>234.4</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.516306464985733e-06</v>
+        <v>3.135265505844914e-07</v>
       </c>
       <c r="E21" t="n">
         <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -865,19 +865,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>207.6</v>
+        <v>234.4</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.025665661192044e-06</v>
+        <v>3.023214077983883e-07</v>
       </c>
       <c r="E22" t="n">
         <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -885,19 +885,19 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>207.6</v>
+        <v>232</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.025665661192044e-06</v>
+        <v>2.43875738348402e-07</v>
       </c>
       <c r="E23" t="n">
         <v>100</v>
       </c>
       <c r="F23" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -905,19 +905,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>207.6</v>
+        <v>232</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.770064076137293e-07</v>
+        <v>2.433491484122306e-07</v>
       </c>
       <c r="E24" t="n">
         <v>100</v>
       </c>
       <c r="F24" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -925,19 +925,19 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>207.6</v>
+        <v>225.6</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.60607071072079e-07</v>
+        <v>2.375765677362542e-07</v>
       </c>
       <c r="E25" t="n">
         <v>100</v>
       </c>
       <c r="F25" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -945,19 +945,19 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>207.6</v>
+        <v>213.6</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>9.320862229060817e-07</v>
+        <v>2.123197052013852e-07</v>
       </c>
       <c r="E26" t="n">
         <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -965,19 +965,19 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>207.6</v>
+        <v>213.6</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>9.266985393367876e-07</v>
+        <v>1.44247253917167e-07</v>
       </c>
       <c r="E27" t="n">
         <v>100</v>
       </c>
       <c r="F27" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -985,19 +985,19 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>207.6</v>
+        <v>209.6</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>9.266985393367876e-07</v>
+        <v>1.44247253917167e-07</v>
       </c>
       <c r="E28" t="n">
         <v>100</v>
       </c>
       <c r="F28" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -1005,19 +1005,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>207.6</v>
+        <v>206.4</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>8.938274473841599e-07</v>
+        <v>1.128053844568153e-07</v>
       </c>
       <c r="E29" t="n">
         <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1025,19 +1025,19 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>206.8</v>
+        <v>206.4</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>8.186498991361359e-07</v>
+        <v>1.128053844568153e-07</v>
       </c>
       <c r="E30" t="n">
         <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -1045,19 +1045,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>206.8</v>
+        <v>176.8</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>8.186498991361359e-07</v>
+        <v>1.063961123608777e-07</v>
       </c>
       <c r="E31" t="n">
         <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>83</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
@@ -1065,19 +1065,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>201.2</v>
+        <v>176.8</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>8.186498991361359e-07</v>
+        <v>1.063961123608777e-07</v>
       </c>
       <c r="E32" t="n">
         <v>100</v>
       </c>
       <c r="F32" t="n">
-        <v>91</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -1085,19 +1085,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>201.2</v>
+        <v>176.8</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>7.95203381007554e-07</v>
+        <v>1.063961123608777e-07</v>
       </c>
       <c r="E33" t="n">
         <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>94</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
@@ -1105,19 +1105,19 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>194.4</v>
+        <v>176.8</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>7.911367342442285e-07</v>
+        <v>8.587000618987618e-08</v>
       </c>
       <c r="E34" t="n">
         <v>100</v>
       </c>
       <c r="F34" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
@@ -1125,19 +1125,19 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>194.4</v>
+        <v>176.8</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>7.911367342442285e-07</v>
+        <v>8.399519212444371e-08</v>
       </c>
       <c r="E35" t="n">
         <v>100</v>
       </c>
       <c r="F35" t="n">
-        <v>92</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
@@ -1145,19 +1145,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>194.4</v>
+        <v>162.8</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>7.222818695683382e-07</v>
+        <v>6.719094292343583e-08</v>
       </c>
       <c r="E36" t="n">
         <v>100</v>
       </c>
       <c r="F36" t="n">
-        <v>98</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
@@ -1165,19 +1165,19 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>193.6</v>
+        <v>162.8</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>7.222818695683382e-07</v>
+        <v>3.597703584219106e-08</v>
       </c>
       <c r="E37" t="n">
         <v>100</v>
       </c>
       <c r="F37" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -1185,19 +1185,19 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>193.6</v>
+        <v>162.8</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>7.222818695683382e-07</v>
+        <v>3.597628196986462e-08</v>
       </c>
       <c r="E38" t="n">
         <v>100</v>
       </c>
       <c r="F38" t="n">
-        <v>92</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
@@ -1205,19 +1205,19 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>191.2</v>
+        <v>162.8</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>7.222818695683382e-07</v>
+        <v>3.54485911262395e-08</v>
       </c>
       <c r="E39" t="n">
         <v>100</v>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
@@ -1225,19 +1225,19 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>191.2</v>
+        <v>155.2</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>6.601607493461079e-07</v>
+        <v>3.54485911262395e-08</v>
       </c>
       <c r="E40" t="n">
         <v>100</v>
       </c>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
@@ -1245,19 +1245,19 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>188.8</v>
+        <v>155.2</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>6.522973774539079e-07</v>
+        <v>3.54485911262395e-08</v>
       </c>
       <c r="E41" t="n">
         <v>100</v>
       </c>
       <c r="F41" t="n">
-        <v>100</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -1265,19 +1265,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>184.8</v>
+        <v>152</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>6.522973774539079e-07</v>
+        <v>3.54485911262395e-08</v>
       </c>
       <c r="E42" t="n">
         <v>100</v>
       </c>
       <c r="F42" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43">
@@ -1285,19 +1285,19 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>184.8</v>
+        <v>148.8</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>6.522973774539079e-07</v>
+        <v>3.54485911262395e-08</v>
       </c>
       <c r="E43" t="n">
         <v>100</v>
       </c>
       <c r="F43" t="n">
-        <v>100</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44">
@@ -1305,19 +1305,19 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>184.8</v>
+        <v>148.8</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>6.407727310718586e-07</v>
+        <v>3.278501778554797e-08</v>
       </c>
       <c r="E44" t="n">
         <v>100</v>
       </c>
       <c r="F44" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45">
@@ -1325,19 +1325,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>177.6</v>
+        <v>146.8</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>6.407727310718586e-07</v>
+        <v>3.278501778554797e-08</v>
       </c>
       <c r="E45" t="n">
         <v>100</v>
       </c>
       <c r="F45" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46">
@@ -1345,19 +1345,19 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>174.8</v>
+        <v>146.8</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>6.407727310718586e-07</v>
+        <v>3.278501778554797e-08</v>
       </c>
       <c r="E46" t="n">
         <v>100</v>
       </c>
       <c r="F46" t="n">
-        <v>98</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47">
@@ -1365,19 +1365,19 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>174.8</v>
+        <v>122.4</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>6.407727310718586e-07</v>
+        <v>3.278501778554797e-08</v>
       </c>
       <c r="E47" t="n">
         <v>100</v>
       </c>
       <c r="F47" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48">
@@ -1385,19 +1385,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>174.8</v>
+        <v>122.4</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>6.314137045857813e-07</v>
+        <v>3.253169665327161e-08</v>
       </c>
       <c r="E48" t="n">
         <v>100</v>
       </c>
       <c r="F48" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
@@ -1405,19 +1405,19 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>174.8</v>
+        <v>122.4</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>6.222471803828546e-07</v>
+        <v>3.251384413961448e-08</v>
       </c>
       <c r="E49" t="n">
         <v>100</v>
       </c>
       <c r="F49" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
@@ -1425,19 +1425,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>174.8</v>
+        <v>121.6</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>6.222471803828546e-07</v>
+        <v>3.076892824447345e-08</v>
       </c>
       <c r="E50" t="n">
         <v>100</v>
       </c>
       <c r="F50" t="n">
-        <v>99</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51">
@@ -1445,19 +1445,19 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>174.8</v>
+        <v>121.6</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>6.222471803828546e-07</v>
+        <v>3.076892824447345e-08</v>
       </c>
       <c r="E51" t="n">
         <v>100</v>
       </c>
       <c r="F51" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52">
@@ -1465,19 +1465,19 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>174.8</v>
+        <v>118.4</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>6.222471803828546e-07</v>
+        <v>3.076892824447345e-08</v>
       </c>
       <c r="E52" t="n">
         <v>100</v>
       </c>
       <c r="F52" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53">
@@ -1485,19 +1485,19 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>174.8</v>
+        <v>118.4</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>5.869419454434815e-07</v>
+        <v>2.869806251667129e-08</v>
       </c>
       <c r="E53" t="n">
         <v>100</v>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
@@ -1505,19 +1505,19 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>174.8</v>
+        <v>118.4</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>5.418094374331418e-07</v>
+        <v>2.869806251667129e-08</v>
       </c>
       <c r="E54" t="n">
         <v>100</v>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55">
@@ -1525,19 +1525,19 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>166</v>
+        <v>112.4</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>5.137483247897269e-07</v>
+        <v>2.621347007927886e-08</v>
       </c>
       <c r="E55" t="n">
         <v>100</v>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56">
@@ -1545,19 +1545,19 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>166</v>
+        <v>110.8</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>5.137483247897269e-07</v>
+        <v>2.599017697217961e-08</v>
       </c>
       <c r="E56" t="n">
         <v>100</v>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57">
@@ -1565,19 +1565,19 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>166</v>
+        <v>110.8</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>5.137483247897269e-07</v>
+        <v>2.599017697217961e-08</v>
       </c>
       <c r="E57" t="n">
         <v>100</v>
       </c>
       <c r="F57" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58">
@@ -1585,19 +1585,19 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>166</v>
+        <v>107.2</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>4.85182967416505e-07</v>
+        <v>2.369202573732287e-08</v>
       </c>
       <c r="E58" t="n">
         <v>100</v>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59">
@@ -1605,19 +1605,19 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>165.2</v>
+        <v>107.2</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>4.716943761270616e-07</v>
+        <v>2.369202573732287e-08</v>
       </c>
       <c r="E59" t="n">
         <v>100</v>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60">
@@ -1625,19 +1625,19 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>165.2</v>
+        <v>107.2</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>4.716943761270616e-07</v>
+        <v>2.369202573732287e-08</v>
       </c>
       <c r="E60" t="n">
         <v>100</v>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
@@ -1645,19 +1645,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>165.2</v>
+        <v>107.2</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>4.716943761270616e-07</v>
+        <v>2.314577505056094e-08</v>
       </c>
       <c r="E61" t="n">
         <v>100</v>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62">
@@ -1665,19 +1665,19 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>165.2</v>
+        <v>107.2</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>3.778082578236462e-07</v>
+        <v>2.314577505056094e-08</v>
       </c>
       <c r="E62" t="n">
         <v>100</v>
       </c>
       <c r="F62" t="n">
-        <v>100</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63">
@@ -1685,19 +1685,19 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>165.2</v>
+        <v>107.2</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>3.778082578236462e-07</v>
+        <v>2.070911041437778e-08</v>
       </c>
       <c r="E63" t="n">
         <v>100</v>
       </c>
       <c r="F63" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64">
@@ -1705,19 +1705,19 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>165.2</v>
+        <v>107.2</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>3.778082578236462e-07</v>
+        <v>2.070911041437778e-08</v>
       </c>
       <c r="E64" t="n">
         <v>100</v>
       </c>
       <c r="F64" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65">
@@ -1725,19 +1725,19 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>165.2</v>
+        <v>107.2</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>2.070911041437778e-08</v>
       </c>
       <c r="E65" t="n">
         <v>100</v>
       </c>
       <c r="F65" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66">
@@ -1745,19 +1745,19 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>165.2</v>
+        <v>99.2</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>2.070911041437778e-08</v>
       </c>
       <c r="E66" t="n">
         <v>100</v>
       </c>
       <c r="F66" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67">
@@ -1765,19 +1765,19 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>160.4</v>
+        <v>99.2</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>2.070911041437778e-08</v>
       </c>
       <c r="E67" t="n">
         <v>100</v>
       </c>
       <c r="F67" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68">
@@ -1785,19 +1785,19 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>160.4</v>
+        <v>99.2</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>2.070911041437778e-08</v>
       </c>
       <c r="E68" t="n">
         <v>100</v>
       </c>
       <c r="F68" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69">
@@ -1805,19 +1805,19 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>160.4</v>
+        <v>99.2</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>2.070911041437778e-08</v>
       </c>
       <c r="E69" t="n">
         <v>100</v>
       </c>
       <c r="F69" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70">
@@ -1825,19 +1825,19 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>150.8</v>
+        <v>97.60000000000001</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>2.070911041437778e-08</v>
       </c>
       <c r="E70" t="n">
         <v>100</v>
       </c>
       <c r="F70" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71">
@@ -1845,19 +1845,19 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>150.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>2.047238052127635e-08</v>
       </c>
       <c r="E71" t="n">
         <v>100</v>
       </c>
       <c r="F71" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72">
@@ -1865,19 +1865,19 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>146</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>1.715010907710132e-08</v>
       </c>
       <c r="E72" t="n">
         <v>100</v>
       </c>
       <c r="F72" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73">
@@ -1885,19 +1885,19 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>146</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>1.715010907710132e-08</v>
       </c>
       <c r="E73" t="n">
         <v>100</v>
       </c>
       <c r="F73" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74">
@@ -1905,19 +1905,19 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>146</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>1.715010907710132e-08</v>
       </c>
       <c r="E74" t="n">
         <v>100</v>
       </c>
       <c r="F74" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="75">
@@ -1925,13 +1925,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>146</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>1.715010907710132e-08</v>
       </c>
       <c r="E75" t="n">
         <v>100</v>
@@ -1945,13 +1945,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>146</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>1.715010907710132e-08</v>
       </c>
       <c r="E76" t="n">
         <v>100</v>
@@ -1965,13 +1965,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>146</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>1.715010907710132e-08</v>
       </c>
       <c r="E77" t="n">
         <v>100</v>
@@ -1985,19 +1985,19 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>146</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>1.715010907710132e-08</v>
       </c>
       <c r="E78" t="n">
         <v>100</v>
       </c>
       <c r="F78" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79">
@@ -2005,19 +2005,19 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>146</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>1.7000334739631e-08</v>
       </c>
       <c r="E79" t="n">
         <v>100</v>
       </c>
       <c r="F79" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="80">
@@ -2025,19 +2025,19 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>146</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>1.218520298075702e-08</v>
       </c>
       <c r="E80" t="n">
         <v>100</v>
       </c>
       <c r="F80" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81">
@@ -2045,19 +2045,19 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>141.6</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>1.218520298075702e-08</v>
       </c>
       <c r="E81" t="n">
         <v>100</v>
       </c>
       <c r="F81" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="82">
@@ -2065,19 +2065,19 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>138.8</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>1.218520298075702e-08</v>
       </c>
       <c r="E82" t="n">
         <v>100</v>
       </c>
       <c r="F82" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="83">
@@ -2085,19 +2085,19 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>138.8</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>3.447327441240261e-07</v>
+        <v>1.218520298075702e-08</v>
       </c>
       <c r="E83" t="n">
         <v>100</v>
       </c>
       <c r="F83" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
     </row>
     <row r="84">
@@ -2105,19 +2105,19 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>138.8</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>3.2470058718375e-07</v>
+        <v>1.218520298075702e-08</v>
       </c>
       <c r="E84" t="n">
         <v>100</v>
       </c>
       <c r="F84" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85">
@@ -2125,19 +2125,19 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>138.8</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>3.2470058718375e-07</v>
+        <v>1.218520298075702e-08</v>
       </c>
       <c r="E85" t="n">
         <v>100</v>
       </c>
       <c r="F85" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="86">
@@ -2145,19 +2145,19 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>135.2</v>
+        <v>88</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>3.2470058718375e-07</v>
+        <v>1.218520298075702e-08</v>
       </c>
       <c r="E86" t="n">
         <v>100</v>
       </c>
       <c r="F86" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87">
@@ -2165,19 +2165,19 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>135.2</v>
+        <v>88</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>3.2470058718375e-07</v>
+        <v>1.218520298075702e-08</v>
       </c>
       <c r="E87" t="n">
         <v>100</v>
       </c>
       <c r="F87" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
     </row>
     <row r="88">
@@ -2185,19 +2185,19 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>135.2</v>
+        <v>88</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>3.2470058718375e-07</v>
+        <v>1.218520298075702e-08</v>
       </c>
       <c r="E88" t="n">
         <v>100</v>
       </c>
       <c r="F88" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="89">
@@ -2205,19 +2205,19 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>135.2</v>
+        <v>88</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>3.2470058718375e-07</v>
+        <v>1.218520298075702e-08</v>
       </c>
       <c r="E89" t="n">
         <v>100</v>
       </c>
       <c r="F89" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90">
@@ -2225,13 +2225,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>3.2470058718375e-07</v>
+        <v>1.061321176722244e-08</v>
       </c>
       <c r="E90" t="n">
         <v>100</v>
@@ -2245,13 +2245,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>132</v>
+        <v>87.2</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>3.2470058718375e-07</v>
+        <v>1.061321176722244e-08</v>
       </c>
       <c r="E91" t="n">
         <v>100</v>
@@ -2265,19 +2265,19 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>132</v>
+        <v>87.2</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>3.2470058718375e-07</v>
+        <v>1.061321176722244e-08</v>
       </c>
       <c r="E92" t="n">
         <v>100</v>
       </c>
       <c r="F92" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93">
@@ -2285,13 +2285,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>132</v>
+        <v>87.2</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>3.2470058718375e-07</v>
+        <v>1.061321176722244e-08</v>
       </c>
       <c r="E93" t="n">
         <v>100</v>
@@ -2305,13 +2305,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>132</v>
+        <v>87.2</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>3.2470058718375e-07</v>
+        <v>1.041578197360177e-08</v>
       </c>
       <c r="E94" t="n">
         <v>100</v>
@@ -2325,13 +2325,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>132</v>
+        <v>87.2</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>3.2470058718375e-07</v>
+        <v>1.041578197360177e-08</v>
       </c>
       <c r="E95" t="n">
         <v>100</v>
@@ -2345,13 +2345,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>132</v>
+        <v>87.2</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>3.232492924518153e-07</v>
+        <v>1.041578197360177e-08</v>
       </c>
       <c r="E96" t="n">
         <v>100</v>
@@ -2365,13 +2365,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>132</v>
+        <v>87.2</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>3.232492924518153e-07</v>
+        <v>1.041578197360177e-08</v>
       </c>
       <c r="E97" t="n">
         <v>100</v>
@@ -2385,13 +2385,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>132</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>3.20979319507627e-07</v>
+        <v>1.041578197360177e-08</v>
       </c>
       <c r="E98" t="n">
         <v>100</v>
@@ -2405,13 +2405,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>130.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>3.20979319507627e-07</v>
+        <v>1.041578197360177e-08</v>
       </c>
       <c r="E99" t="n">
         <v>100</v>
@@ -2425,19 +2425,19 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>128</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>3.160491637103639e-07</v>
+        <v>1.041578197360177e-08</v>
       </c>
       <c r="E100" t="n">
         <v>100</v>
       </c>
       <c r="F100" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
     </row>
     <row r="101">
@@ -2445,19 +2445,19 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>128</v>
+        <v>84.8</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>3.150488453465457e-07</v>
+        <v>1.041578197360177e-08</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
       </c>
       <c r="F101" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
     </row>
     <row r="102">
@@ -2465,19 +2465,19 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>128</v>
+        <v>84.8</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>3.150488453465457e-07</v>
+        <v>1.041578197360177e-08</v>
       </c>
       <c r="E102" t="n">
         <v>100</v>
       </c>
       <c r="F102" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
     </row>
     <row r="103">
@@ -2485,19 +2485,19 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>128</v>
+        <v>84.8</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>2.844969048311424e-07</v>
+        <v>1.041578197360177e-08</v>
       </c>
       <c r="E103" t="n">
         <v>100</v>
       </c>
       <c r="F103" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="104">
@@ -2505,19 +2505,19 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>128</v>
+        <v>84.8</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>2.836615021734082e-07</v>
+        <v>1.041578197360177e-08</v>
       </c>
       <c r="E104" t="n">
         <v>100</v>
       </c>
       <c r="F104" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="105">
@@ -2525,19 +2525,19 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>128</v>
+        <v>84.8</v>
       </c>
       <c r="C105" t="n">
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>2.836615021734082e-07</v>
+        <v>1.041578197360177e-08</v>
       </c>
       <c r="E105" t="n">
         <v>100</v>
       </c>
       <c r="F105" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="106">
@@ -2545,19 +2545,19 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>128</v>
+        <v>84.8</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>2.836615021734082e-07</v>
+        <v>1.041578197360177e-08</v>
       </c>
       <c r="E106" t="n">
         <v>100</v>
       </c>
       <c r="F106" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="107">
@@ -2565,19 +2565,19 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>128</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>2.836615021734082e-07</v>
+        <v>9.740923048290284e-09</v>
       </c>
       <c r="E107" t="n">
         <v>100</v>
       </c>
       <c r="F107" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="108">
@@ -2585,19 +2585,19 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>128</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>2.836615021734082e-07</v>
+        <v>9.740923048290284e-09</v>
       </c>
       <c r="E108" t="n">
         <v>100</v>
       </c>
       <c r="F108" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="109">
@@ -2605,13 +2605,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>128</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>2.836615021734082e-07</v>
+        <v>9.740923048290284e-09</v>
       </c>
       <c r="E109" t="n">
         <v>100</v>
@@ -2625,13 +2625,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>127.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C110" t="n">
         <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>2.836615021734082e-07</v>
+        <v>9.740923048290284e-09</v>
       </c>
       <c r="E110" t="n">
         <v>100</v>
@@ -2645,13 +2645,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>127.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C111" t="n">
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>2.836615021734082e-07</v>
+        <v>9.740923048290284e-09</v>
       </c>
       <c r="E111" t="n">
         <v>100</v>
@@ -2665,13 +2665,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>127.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C112" t="n">
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>2.836615021734082e-07</v>
+        <v>9.61394557849437e-09</v>
       </c>
       <c r="E112" t="n">
         <v>100</v>
@@ -2685,13 +2685,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>127.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>2.827324287739504e-07</v>
+        <v>9.61394557849437e-09</v>
       </c>
       <c r="E113" t="n">
         <v>100</v>
@@ -2705,13 +2705,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>127.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>2.827324287739504e-07</v>
+        <v>9.61394557849437e-09</v>
       </c>
       <c r="E114" t="n">
         <v>100</v>
@@ -2725,13 +2725,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>127.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>2.827324287739504e-07</v>
+        <v>9.61394557849437e-09</v>
       </c>
       <c r="E115" t="n">
         <v>100</v>
@@ -2745,13 +2745,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>127.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>2.827324287739504e-07</v>
+        <v>9.61394557849437e-09</v>
       </c>
       <c r="E116" t="n">
         <v>100</v>
@@ -2765,13 +2765,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>127.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C117" t="n">
         <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>2.827324287739504e-07</v>
+        <v>9.61394557849437e-09</v>
       </c>
       <c r="E117" t="n">
         <v>100</v>
@@ -2785,13 +2785,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>127.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>2.827324287739504e-07</v>
+        <v>9.61394557849437e-09</v>
       </c>
       <c r="E118" t="n">
         <v>100</v>
@@ -2805,13 +2805,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>127.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>2.787237199252311e-07</v>
+        <v>9.61394557849437e-09</v>
       </c>
       <c r="E119" t="n">
         <v>100</v>
@@ -2825,13 +2825,13 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>127.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>2.787237199252311e-07</v>
+        <v>9.61394557849437e-09</v>
       </c>
       <c r="E120" t="n">
         <v>100</v>
@@ -2845,13 +2845,13 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>127.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>2.787237199252311e-07</v>
+        <v>9.61394557849437e-09</v>
       </c>
       <c r="E121" t="n">
         <v>100</v>
@@ -2865,13 +2865,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>125.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C122" t="n">
         <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>2.787237199252311e-07</v>
+        <v>9.61394557849437e-09</v>
       </c>
       <c r="E122" t="n">
         <v>100</v>
@@ -2885,13 +2885,13 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>125.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>2.787237199252311e-07</v>
+        <v>8.588180658313927e-09</v>
       </c>
       <c r="E123" t="n">
         <v>100</v>
@@ -2905,13 +2905,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>124.8</v>
+        <v>69.60000000000001</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>2.787237199252311e-07</v>
+        <v>8.588180658313927e-09</v>
       </c>
       <c r="E124" t="n">
         <v>100</v>
@@ -2925,13 +2925,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>124.8</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>2.669473911975726e-07</v>
+        <v>7.020497382863692e-09</v>
       </c>
       <c r="E125" t="n">
         <v>100</v>
@@ -2945,13 +2945,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>124.8</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>2.669473911975726e-07</v>
+        <v>7.020497382863692e-09</v>
       </c>
       <c r="E126" t="n">
         <v>100</v>
@@ -2965,13 +2965,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>116</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>2.669473911975726e-07</v>
+        <v>7.020497382863692e-09</v>
       </c>
       <c r="E127" t="n">
         <v>100</v>
@@ -2985,13 +2985,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>116</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C128" t="n">
         <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>2.669473911975726e-07</v>
+        <v>7.020497382863692e-09</v>
       </c>
       <c r="E128" t="n">
         <v>100</v>
@@ -3005,13 +3005,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>116</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>2.626496183771041e-07</v>
+        <v>7.020497382863692e-09</v>
       </c>
       <c r="E129" t="n">
         <v>100</v>
@@ -3025,13 +3025,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>116</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>2.626496183771041e-07</v>
+        <v>7.020497382863692e-09</v>
       </c>
       <c r="E130" t="n">
         <v>100</v>
@@ -3045,13 +3045,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>116</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>2.626496183771041e-07</v>
+        <v>6.754343513682899e-09</v>
       </c>
       <c r="E131" t="n">
         <v>100</v>
@@ -3065,13 +3065,13 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>116</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>2.278915606177882e-07</v>
+        <v>6.754343513682899e-09</v>
       </c>
       <c r="E132" t="n">
         <v>100</v>
@@ -3085,13 +3085,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>115.2</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>2.278915606177882e-07</v>
+        <v>6.002142905139493e-09</v>
       </c>
       <c r="E133" t="n">
         <v>100</v>
@@ -3105,13 +3105,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>115.2</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>2.241717965258785e-07</v>
+        <v>5.439367358209741e-09</v>
       </c>
       <c r="E134" t="n">
         <v>100</v>
@@ -3125,13 +3125,13 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>115.2</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>2.241717965258785e-07</v>
+        <v>5.439367358209741e-09</v>
       </c>
       <c r="E135" t="n">
         <v>100</v>
@@ -3145,13 +3145,13 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>115.2</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>2.241717965258785e-07</v>
+        <v>5.439367358209741e-09</v>
       </c>
       <c r="E136" t="n">
         <v>100</v>
@@ -3165,13 +3165,13 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>115.2</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>2.241717965258785e-07</v>
+        <v>5.439367358209741e-09</v>
       </c>
       <c r="E137" t="n">
         <v>100</v>
@@ -3185,13 +3185,13 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>115.2</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>2.241717965258785e-07</v>
+        <v>5.439367358209741e-09</v>
       </c>
       <c r="E138" t="n">
         <v>100</v>
@@ -3205,13 +3205,13 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>108.4</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>2.241717965258785e-07</v>
+        <v>5.439367358209741e-09</v>
       </c>
       <c r="E139" t="n">
         <v>100</v>
@@ -3225,13 +3225,13 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>108.4</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>2.241717965258785e-07</v>
+        <v>5.439367358209741e-09</v>
       </c>
       <c r="E140" t="n">
         <v>100</v>
@@ -3245,13 +3245,13 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>108.4</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>2.241717965258785e-07</v>
+        <v>5.439367358209741e-09</v>
       </c>
       <c r="E141" t="n">
         <v>100</v>
@@ -3265,13 +3265,13 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>108.4</v>
+        <v>61.6</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>1.872924148576742e-07</v>
+        <v>5.439367358209741e-09</v>
       </c>
       <c r="E142" t="n">
         <v>100</v>
@@ -3285,13 +3285,13 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>108.4</v>
+        <v>57.6</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>1.872924148576742e-07</v>
+        <v>5.439367358209741e-09</v>
       </c>
       <c r="E143" t="n">
         <v>100</v>
@@ -3305,13 +3305,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>108.4</v>
+        <v>57.6</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>1.872924148576742e-07</v>
+        <v>5.439367358209741e-09</v>
       </c>
       <c r="E144" t="n">
         <v>100</v>
@@ -3325,13 +3325,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>108.4</v>
+        <v>57.6</v>
       </c>
       <c r="C145" t="n">
         <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>1.821199682895607e-07</v>
+        <v>5.439367358209741e-09</v>
       </c>
       <c r="E145" t="n">
         <v>100</v>
@@ -3345,13 +3345,13 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>108.4</v>
+        <v>57.6</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>1.76779188980786e-07</v>
+        <v>5.439367358209741e-09</v>
       </c>
       <c r="E146" t="n">
         <v>100</v>
@@ -3365,13 +3365,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>108.4</v>
+        <v>57.6</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>1.589285183113939e-07</v>
+        <v>5.439367358209741e-09</v>
       </c>
       <c r="E147" t="n">
         <v>100</v>
@@ -3385,13 +3385,13 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>108.4</v>
+        <v>57.6</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>1.589285183113939e-07</v>
+        <v>5.319615060700603e-09</v>
       </c>
       <c r="E148" t="n">
         <v>100</v>
@@ -3405,13 +3405,13 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>108.4</v>
+        <v>57.6</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>1.586533166106528e-07</v>
+        <v>5.101537252662204e-09</v>
       </c>
       <c r="E149" t="n">
         <v>100</v>
@@ -3425,13 +3425,13 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>108.4</v>
+        <v>57.6</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>1.550862881361574e-07</v>
+        <v>5.101537252662204e-09</v>
       </c>
       <c r="E150" t="n">
         <v>100</v>
@@ -3445,13 +3445,13 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>107.6</v>
+        <v>57.6</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>1.550862881361574e-07</v>
+        <v>4.874050229180545e-09</v>
       </c>
       <c r="E151" t="n">
         <v>100</v>
@@ -3465,13 +3465,13 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>107.6</v>
+        <v>57.6</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>1.550862881361574e-07</v>
+        <v>4.874050229180545e-09</v>
       </c>
       <c r="E152" t="n">
         <v>100</v>
@@ -3485,13 +3485,13 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>107.6</v>
+        <v>57.6</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>1.550862881361574e-07</v>
+        <v>4.874050229180545e-09</v>
       </c>
       <c r="E153" t="n">
         <v>100</v>
@@ -3505,13 +3505,13 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>107.6</v>
+        <v>57.6</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>1.550862881361574e-07</v>
+        <v>4.874050229180545e-09</v>
       </c>
       <c r="E154" t="n">
         <v>100</v>
@@ -3525,13 +3525,13 @@
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>107.6</v>
+        <v>57.6</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>1.550862881361574e-07</v>
+        <v>4.874050229180545e-09</v>
       </c>
       <c r="E155" t="n">
         <v>100</v>
@@ -3545,13 +3545,13 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>107.6</v>
+        <v>57.6</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>1.550862881361574e-07</v>
+        <v>4.872904996386631e-09</v>
       </c>
       <c r="E156" t="n">
         <v>100</v>
@@ -3565,13 +3565,13 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>106.8</v>
+        <v>57.6</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>1.550862881361574e-07</v>
+        <v>4.872904996386631e-09</v>
       </c>
       <c r="E157" t="n">
         <v>100</v>
@@ -3585,13 +3585,13 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>106.8</v>
+        <v>57.6</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>1.550862881361574e-07</v>
+        <v>4.70660395950877e-09</v>
       </c>
       <c r="E158" t="n">
         <v>100</v>
@@ -3605,13 +3605,13 @@
         <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>106.8</v>
+        <v>57.6</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>1.550862881361574e-07</v>
+        <v>4.384497391784858e-09</v>
       </c>
       <c r="E159" t="n">
         <v>100</v>
@@ -3625,13 +3625,13 @@
         <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>106.8</v>
+        <v>57.6</v>
       </c>
       <c r="C160" t="n">
         <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>1.397569681607506e-07</v>
+        <v>4.100944774058672e-09</v>
       </c>
       <c r="E160" t="n">
         <v>100</v>
@@ -3645,13 +3645,13 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>106.8</v>
+        <v>57.6</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>1.370504675176182e-07</v>
+        <v>4.100944774058672e-09</v>
       </c>
       <c r="E161" t="n">
         <v>100</v>
@@ -3665,13 +3665,13 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>103.6</v>
+        <v>57.6</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>1.370504675176182e-07</v>
+        <v>3.914599926890709e-09</v>
       </c>
       <c r="E162" t="n">
         <v>100</v>
@@ -3685,13 +3685,13 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>103.6</v>
+        <v>57.6</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>1.370504675176182e-07</v>
+        <v>3.914599926890709e-09</v>
       </c>
       <c r="E163" t="n">
         <v>100</v>
@@ -3705,13 +3705,13 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>103.6</v>
+        <v>57.6</v>
       </c>
       <c r="C164" t="n">
         <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>1.370504675176182e-07</v>
+        <v>3.914599926890709e-09</v>
       </c>
       <c r="E164" t="n">
         <v>100</v>
@@ -3725,13 +3725,13 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>103.6</v>
+        <v>57.6</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>1.370504675176182e-07</v>
+        <v>3.914599926890709e-09</v>
       </c>
       <c r="E165" t="n">
         <v>100</v>
@@ -3745,13 +3745,13 @@
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>103.6</v>
+        <v>57.6</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>1.370504675176182e-07</v>
+        <v>3.914599926890709e-09</v>
       </c>
       <c r="E166" t="n">
         <v>100</v>
@@ -3765,13 +3765,13 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>103.6</v>
+        <v>57.6</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>1.370504675176182e-07</v>
+        <v>3.914599926890709e-09</v>
       </c>
       <c r="E167" t="n">
         <v>100</v>
@@ -3785,13 +3785,13 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>102.8</v>
+        <v>56.8</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>1.370504675176182e-07</v>
+        <v>3.914599926890709e-09</v>
       </c>
       <c r="E168" t="n">
         <v>100</v>
@@ -3805,13 +3805,13 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>102.8</v>
+        <v>56</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>1.3699578582554e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E169" t="n">
         <v>100</v>
@@ -3825,13 +3825,13 @@
         <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>101.2</v>
+        <v>56</v>
       </c>
       <c r="C170" t="n">
         <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>1.3699578582554e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E170" t="n">
         <v>100</v>
@@ -3845,13 +3845,13 @@
         <v>169</v>
       </c>
       <c r="B171" t="n">
-        <v>101.2</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>1.3699578582554e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E171" t="n">
         <v>100</v>
@@ -3865,13 +3865,13 @@
         <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>101.2</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>1.3699578582554e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E172" t="n">
         <v>100</v>
@@ -3885,13 +3885,13 @@
         <v>171</v>
       </c>
       <c r="B173" t="n">
-        <v>101.2</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="C173" t="n">
         <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>1.3699578582554e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E173" t="n">
         <v>100</v>
@@ -3905,13 +3905,13 @@
         <v>172</v>
       </c>
       <c r="B174" t="n">
-        <v>101.2</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="C174" t="n">
         <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>1.3699578582554e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E174" t="n">
         <v>100</v>
@@ -3925,13 +3925,13 @@
         <v>173</v>
       </c>
       <c r="B175" t="n">
-        <v>101.2</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="C175" t="n">
         <v>1</v>
       </c>
       <c r="D175" t="n">
-        <v>1.3699578582554e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E175" t="n">
         <v>100</v>
@@ -3945,13 +3945,13 @@
         <v>174</v>
       </c>
       <c r="B176" t="n">
-        <v>101.2</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
       </c>
       <c r="D176" t="n">
-        <v>1.3699578582554e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E176" t="n">
         <v>100</v>
@@ -3965,13 +3965,13 @@
         <v>175</v>
       </c>
       <c r="B177" t="n">
-        <v>101.2</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>1.3699578582554e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E177" t="n">
         <v>100</v>
@@ -3985,13 +3985,13 @@
         <v>176</v>
       </c>
       <c r="B178" t="n">
-        <v>101.2</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>1.3699578582554e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E178" t="n">
         <v>100</v>
@@ -4005,13 +4005,13 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>101.2</v>
+        <v>53.6</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>1.3699578582554e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E179" t="n">
         <v>100</v>
@@ -4025,13 +4025,13 @@
         <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>101.2</v>
+        <v>53.6</v>
       </c>
       <c r="C180" t="n">
         <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>1.3699578582554e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E180" t="n">
         <v>100</v>
@@ -4045,13 +4045,13 @@
         <v>179</v>
       </c>
       <c r="B181" t="n">
-        <v>101.2</v>
+        <v>52.8</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>1.3699578582554e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E181" t="n">
         <v>100</v>
@@ -4065,13 +4065,13 @@
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>101.2</v>
+        <v>52.8</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>1.3699578582554e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E182" t="n">
         <v>100</v>
@@ -4085,13 +4085,13 @@
         <v>181</v>
       </c>
       <c r="B183" t="n">
-        <v>101.2</v>
+        <v>52</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
       </c>
       <c r="D183" t="n">
-        <v>1.368547386832188e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E183" t="n">
         <v>100</v>
@@ -4105,13 +4105,13 @@
         <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>
       </c>
       <c r="D184" t="n">
-        <v>1.368547386832188e-07</v>
+        <v>3.82638130962524e-09</v>
       </c>
       <c r="E184" t="n">
         <v>100</v>
@@ -4125,13 +4125,13 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E185" t="n">
         <v>100</v>
@@ -4145,13 +4145,13 @@
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
       </c>
       <c r="D186" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E186" t="n">
         <v>100</v>
@@ -4165,13 +4165,13 @@
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
       </c>
       <c r="D187" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E187" t="n">
         <v>100</v>
@@ -4185,13 +4185,13 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E188" t="n">
         <v>100</v>
@@ -4205,13 +4205,13 @@
         <v>187</v>
       </c>
       <c r="B189" t="n">
-        <v>100</v>
+        <v>51.2</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E189" t="n">
         <v>100</v>
@@ -4225,13 +4225,13 @@
         <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>99.2</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E190" t="n">
         <v>100</v>
@@ -4245,13 +4245,13 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>99.2</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C191" t="n">
         <v>1</v>
       </c>
       <c r="D191" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E191" t="n">
         <v>100</v>
@@ -4265,13 +4265,13 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>99.2</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C192" t="n">
         <v>1</v>
       </c>
       <c r="D192" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E192" t="n">
         <v>100</v>
@@ -4285,13 +4285,13 @@
         <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>99.2</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C193" t="n">
         <v>1</v>
       </c>
       <c r="D193" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E193" t="n">
         <v>100</v>
@@ -4305,13 +4305,13 @@
         <v>192</v>
       </c>
       <c r="B194" t="n">
-        <v>99.2</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
       </c>
       <c r="D194" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E194" t="n">
         <v>100</v>
@@ -4325,13 +4325,13 @@
         <v>193</v>
       </c>
       <c r="B195" t="n">
-        <v>99.2</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C195" t="n">
         <v>1</v>
       </c>
       <c r="D195" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E195" t="n">
         <v>100</v>
@@ -4345,13 +4345,13 @@
         <v>194</v>
       </c>
       <c r="B196" t="n">
-        <v>99.2</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C196" t="n">
         <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E196" t="n">
         <v>100</v>
@@ -4365,13 +4365,13 @@
         <v>195</v>
       </c>
       <c r="B197" t="n">
-        <v>92</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E197" t="n">
         <v>100</v>
@@ -4385,13 +4385,13 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>92</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C198" t="n">
         <v>1</v>
       </c>
       <c r="D198" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E198" t="n">
         <v>100</v>
@@ -4405,13 +4405,13 @@
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>92</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C199" t="n">
         <v>1</v>
       </c>
       <c r="D199" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E199" t="n">
         <v>100</v>
@@ -4425,13 +4425,13 @@
         <v>198</v>
       </c>
       <c r="B200" t="n">
-        <v>92</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C200" t="n">
         <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E200" t="n">
         <v>100</v>
@@ -4445,13 +4445,13 @@
         <v>199</v>
       </c>
       <c r="B201" t="n">
-        <v>92</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C201" t="n">
         <v>1</v>
       </c>
       <c r="D201" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E201" t="n">
         <v>100</v>
@@ -4465,13 +4465,13 @@
         <v>200</v>
       </c>
       <c r="B202" t="n">
-        <v>92</v>
+        <v>48.8</v>
       </c>
       <c r="C202" t="n">
         <v>1</v>
       </c>
       <c r="D202" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E202" t="n">
         <v>100</v>
@@ -4485,13 +4485,13 @@
         <v>201</v>
       </c>
       <c r="B203" t="n">
-        <v>92</v>
+        <v>48.8</v>
       </c>
       <c r="C203" t="n">
         <v>1</v>
       </c>
       <c r="D203" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E203" t="n">
         <v>100</v>
@@ -4505,13 +4505,13 @@
         <v>202</v>
       </c>
       <c r="B204" t="n">
-        <v>92</v>
+        <v>48.8</v>
       </c>
       <c r="C204" t="n">
         <v>1</v>
       </c>
       <c r="D204" t="n">
-        <v>1.115408238425328e-07</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E204" t="n">
         <v>100</v>
@@ -4525,13 +4525,13 @@
         <v>203</v>
       </c>
       <c r="B205" t="n">
-        <v>92</v>
+        <v>48.8</v>
       </c>
       <c r="C205" t="n">
         <v>1</v>
       </c>
       <c r="D205" t="n">
-        <v>9.982515372290115e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E205" t="n">
         <v>100</v>
@@ -4545,13 +4545,13 @@
         <v>204</v>
       </c>
       <c r="B206" t="n">
-        <v>92</v>
+        <v>48.8</v>
       </c>
       <c r="C206" t="n">
         <v>1</v>
       </c>
       <c r="D206" t="n">
-        <v>9.982515372290115e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E206" t="n">
         <v>100</v>
@@ -4565,13 +4565,13 @@
         <v>205</v>
       </c>
       <c r="B207" t="n">
-        <v>92</v>
+        <v>48.8</v>
       </c>
       <c r="C207" t="n">
         <v>1</v>
       </c>
       <c r="D207" t="n">
-        <v>9.982515372290115e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E207" t="n">
         <v>100</v>
@@ -4585,13 +4585,13 @@
         <v>206</v>
       </c>
       <c r="B208" t="n">
-        <v>92</v>
+        <v>48.8</v>
       </c>
       <c r="C208" t="n">
         <v>1</v>
       </c>
       <c r="D208" t="n">
-        <v>9.982515372290115e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E208" t="n">
         <v>100</v>
@@ -4605,13 +4605,13 @@
         <v>207</v>
       </c>
       <c r="B209" t="n">
-        <v>92</v>
+        <v>48.8</v>
       </c>
       <c r="C209" t="n">
         <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>9.982515372290115e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E209" t="n">
         <v>100</v>
@@ -4625,13 +4625,13 @@
         <v>208</v>
       </c>
       <c r="B210" t="n">
-        <v>92</v>
+        <v>48.8</v>
       </c>
       <c r="C210" t="n">
         <v>1</v>
       </c>
       <c r="D210" t="n">
-        <v>9.982515372290115e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E210" t="n">
         <v>100</v>
@@ -4645,13 +4645,13 @@
         <v>209</v>
       </c>
       <c r="B211" t="n">
-        <v>92</v>
+        <v>48.8</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
       </c>
       <c r="D211" t="n">
-        <v>9.982515372290115e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E211" t="n">
         <v>100</v>
@@ -4665,13 +4665,13 @@
         <v>210</v>
       </c>
       <c r="B212" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
       </c>
       <c r="D212" t="n">
-        <v>9.982515372290115e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E212" t="n">
         <v>100</v>
@@ -4685,13 +4685,13 @@
         <v>211</v>
       </c>
       <c r="B213" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="C213" t="n">
         <v>1</v>
       </c>
       <c r="D213" t="n">
-        <v>9.982515372290115e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E213" t="n">
         <v>100</v>
@@ -4705,13 +4705,13 @@
         <v>212</v>
       </c>
       <c r="B214" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="C214" t="n">
         <v>1</v>
       </c>
       <c r="D214" t="n">
-        <v>9.914663158100975e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E214" t="n">
         <v>100</v>
@@ -4725,13 +4725,13 @@
         <v>213</v>
       </c>
       <c r="B215" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="C215" t="n">
         <v>1</v>
       </c>
       <c r="D215" t="n">
-        <v>9.696017059847426e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E215" t="n">
         <v>100</v>
@@ -4745,13 +4745,13 @@
         <v>214</v>
       </c>
       <c r="B216" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="C216" t="n">
         <v>1</v>
       </c>
       <c r="D216" t="n">
-        <v>9.696017059847426e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E216" t="n">
         <v>100</v>
@@ -4765,13 +4765,13 @@
         <v>215</v>
       </c>
       <c r="B217" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
       </c>
       <c r="D217" t="n">
-        <v>9.696017059847426e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E217" t="n">
         <v>100</v>
@@ -4785,13 +4785,13 @@
         <v>216</v>
       </c>
       <c r="B218" t="n">
-        <v>92</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>9.696017059847426e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E218" t="n">
         <v>100</v>
@@ -4805,13 +4805,13 @@
         <v>217</v>
       </c>
       <c r="B219" t="n">
-        <v>86.80000000000001</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C219" t="n">
         <v>1</v>
       </c>
       <c r="D219" t="n">
-        <v>9.696017059847426e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E219" t="n">
         <v>100</v>
@@ -4825,13 +4825,13 @@
         <v>218</v>
       </c>
       <c r="B220" t="n">
-        <v>86.80000000000001</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>9.696017059847426e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E220" t="n">
         <v>100</v>
@@ -4845,13 +4845,13 @@
         <v>219</v>
       </c>
       <c r="B221" t="n">
-        <v>86.80000000000001</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C221" t="n">
         <v>1</v>
       </c>
       <c r="D221" t="n">
-        <v>9.696017059847426e-08</v>
+        <v>3.776458439754372e-09</v>
       </c>
       <c r="E221" t="n">
         <v>100</v>
@@ -4865,13 +4865,13 @@
         <v>220</v>
       </c>
       <c r="B222" t="n">
-        <v>86.80000000000001</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C222" t="n">
         <v>1</v>
       </c>
       <c r="D222" t="n">
-        <v>9.696017059847426e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E222" t="n">
         <v>100</v>
@@ -4885,13 +4885,13 @@
         <v>221</v>
       </c>
       <c r="B223" t="n">
-        <v>86.80000000000001</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C223" t="n">
         <v>1</v>
       </c>
       <c r="D223" t="n">
-        <v>9.696017059847426e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E223" t="n">
         <v>100</v>
@@ -4905,13 +4905,13 @@
         <v>222</v>
       </c>
       <c r="B224" t="n">
-        <v>85.2</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C224" t="n">
         <v>1</v>
       </c>
       <c r="D224" t="n">
-        <v>9.696017059847426e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E224" t="n">
         <v>100</v>
@@ -4925,13 +4925,13 @@
         <v>223</v>
       </c>
       <c r="B225" t="n">
-        <v>85.2</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C225" t="n">
         <v>1</v>
       </c>
       <c r="D225" t="n">
-        <v>9.608988911481229e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E225" t="n">
         <v>100</v>
@@ -4945,13 +4945,13 @@
         <v>224</v>
       </c>
       <c r="B226" t="n">
-        <v>85.2</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C226" t="n">
         <v>1</v>
       </c>
       <c r="D226" t="n">
-        <v>8.188023149620006e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E226" t="n">
         <v>100</v>
@@ -4965,13 +4965,13 @@
         <v>225</v>
       </c>
       <c r="B227" t="n">
-        <v>84.80000000000001</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C227" t="n">
         <v>1</v>
       </c>
       <c r="D227" t="n">
-        <v>8.188023149620006e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E227" t="n">
         <v>100</v>
@@ -4985,13 +4985,13 @@
         <v>226</v>
       </c>
       <c r="B228" t="n">
-        <v>82.40000000000001</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C228" t="n">
         <v>1</v>
       </c>
       <c r="D228" t="n">
-        <v>8.188023149620006e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E228" t="n">
         <v>100</v>
@@ -5005,13 +5005,13 @@
         <v>227</v>
       </c>
       <c r="B229" t="n">
-        <v>82.40000000000001</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C229" t="n">
         <v>1</v>
       </c>
       <c r="D229" t="n">
-        <v>8.188023149620006e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E229" t="n">
         <v>100</v>
@@ -5025,13 +5025,13 @@
         <v>228</v>
       </c>
       <c r="B230" t="n">
-        <v>82.40000000000001</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C230" t="n">
         <v>1</v>
       </c>
       <c r="D230" t="n">
-        <v>8.188023149620006e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E230" t="n">
         <v>100</v>
@@ -5045,13 +5045,13 @@
         <v>229</v>
       </c>
       <c r="B231" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C231" t="n">
         <v>1</v>
       </c>
       <c r="D231" t="n">
-        <v>8.188023149620006e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E231" t="n">
         <v>100</v>
@@ -5065,13 +5065,13 @@
         <v>230</v>
       </c>
       <c r="B232" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C232" t="n">
         <v>1</v>
       </c>
       <c r="D232" t="n">
-        <v>8.188023149620006e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E232" t="n">
         <v>100</v>
@@ -5085,13 +5085,13 @@
         <v>231</v>
       </c>
       <c r="B233" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C233" t="n">
         <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>8.188023149620006e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E233" t="n">
         <v>100</v>
@@ -5105,13 +5105,13 @@
         <v>232</v>
       </c>
       <c r="B234" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C234" t="n">
         <v>1</v>
       </c>
       <c r="D234" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E234" t="n">
         <v>100</v>
@@ -5125,13 +5125,13 @@
         <v>233</v>
       </c>
       <c r="B235" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C235" t="n">
         <v>1</v>
       </c>
       <c r="D235" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E235" t="n">
         <v>100</v>
@@ -5145,13 +5145,13 @@
         <v>234</v>
       </c>
       <c r="B236" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C236" t="n">
         <v>1</v>
       </c>
       <c r="D236" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E236" t="n">
         <v>100</v>
@@ -5165,13 +5165,13 @@
         <v>235</v>
       </c>
       <c r="B237" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C237" t="n">
         <v>1</v>
       </c>
       <c r="D237" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E237" t="n">
         <v>100</v>
@@ -5185,13 +5185,13 @@
         <v>236</v>
       </c>
       <c r="B238" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C238" t="n">
         <v>1</v>
       </c>
       <c r="D238" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E238" t="n">
         <v>100</v>
@@ -5205,13 +5205,13 @@
         <v>237</v>
       </c>
       <c r="B239" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C239" t="n">
         <v>1</v>
       </c>
       <c r="D239" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E239" t="n">
         <v>100</v>
@@ -5225,13 +5225,13 @@
         <v>238</v>
       </c>
       <c r="B240" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C240" t="n">
         <v>1</v>
       </c>
       <c r="D240" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E240" t="n">
         <v>100</v>
@@ -5245,13 +5245,13 @@
         <v>239</v>
       </c>
       <c r="B241" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C241" t="n">
         <v>1</v>
       </c>
       <c r="D241" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E241" t="n">
         <v>100</v>
@@ -5265,13 +5265,13 @@
         <v>240</v>
       </c>
       <c r="B242" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C242" t="n">
         <v>1</v>
       </c>
       <c r="D242" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E242" t="n">
         <v>100</v>
@@ -5285,13 +5285,13 @@
         <v>241</v>
       </c>
       <c r="B243" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C243" t="n">
         <v>1</v>
       </c>
       <c r="D243" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E243" t="n">
         <v>100</v>
@@ -5305,13 +5305,13 @@
         <v>242</v>
       </c>
       <c r="B244" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C244" t="n">
         <v>1</v>
       </c>
       <c r="D244" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E244" t="n">
         <v>100</v>
@@ -5325,13 +5325,13 @@
         <v>243</v>
       </c>
       <c r="B245" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C245" t="n">
         <v>1</v>
       </c>
       <c r="D245" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E245" t="n">
         <v>100</v>
@@ -5345,13 +5345,13 @@
         <v>244</v>
       </c>
       <c r="B246" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C246" t="n">
         <v>1</v>
       </c>
       <c r="D246" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E246" t="n">
         <v>100</v>
@@ -5365,13 +5365,13 @@
         <v>245</v>
       </c>
       <c r="B247" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C247" t="n">
         <v>1</v>
       </c>
       <c r="D247" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E247" t="n">
         <v>100</v>
@@ -5385,13 +5385,13 @@
         <v>246</v>
       </c>
       <c r="B248" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C248" t="n">
         <v>1</v>
       </c>
       <c r="D248" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E248" t="n">
         <v>100</v>
@@ -5405,13 +5405,13 @@
         <v>247</v>
       </c>
       <c r="B249" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C249" t="n">
         <v>1</v>
       </c>
       <c r="D249" t="n">
-        <v>7.160181573115977e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E249" t="n">
         <v>100</v>
@@ -5425,13 +5425,13 @@
         <v>248</v>
       </c>
       <c r="B250" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C250" t="n">
         <v>1</v>
       </c>
       <c r="D250" t="n">
-        <v>6.433568017923635e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E250" t="n">
         <v>100</v>
@@ -5445,13 +5445,13 @@
         <v>249</v>
       </c>
       <c r="B251" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C251" t="n">
         <v>1</v>
       </c>
       <c r="D251" t="n">
-        <v>6.433568017923635e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E251" t="n">
         <v>100</v>
@@ -5465,13 +5465,13 @@
         <v>250</v>
       </c>
       <c r="B252" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C252" t="n">
         <v>1</v>
       </c>
       <c r="D252" t="n">
-        <v>6.433568017923635e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E252" t="n">
         <v>100</v>
@@ -5485,13 +5485,13 @@
         <v>251</v>
       </c>
       <c r="B253" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C253" t="n">
         <v>1</v>
       </c>
       <c r="D253" t="n">
-        <v>6.433568017923635e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E253" t="n">
         <v>100</v>
@@ -5505,13 +5505,13 @@
         <v>252</v>
       </c>
       <c r="B254" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C254" t="n">
         <v>1</v>
       </c>
       <c r="D254" t="n">
-        <v>6.433568017923635e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E254" t="n">
         <v>100</v>
@@ -5525,13 +5525,13 @@
         <v>253</v>
       </c>
       <c r="B255" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C255" t="n">
         <v>1</v>
       </c>
       <c r="D255" t="n">
-        <v>6.433568017923635e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E255" t="n">
         <v>100</v>
@@ -5545,13 +5545,13 @@
         <v>254</v>
       </c>
       <c r="B256" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C256" t="n">
         <v>1</v>
       </c>
       <c r="D256" t="n">
-        <v>6.433568017923635e-08</v>
+        <v>3.771667808574105e-09</v>
       </c>
       <c r="E256" t="n">
         <v>100</v>
@@ -5565,13 +5565,13 @@
         <v>255</v>
       </c>
       <c r="B257" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C257" t="n">
         <v>1</v>
       </c>
       <c r="D257" t="n">
-        <v>6.433568017923635e-08</v>
+        <v>3.728879669141288e-09</v>
       </c>
       <c r="E257" t="n">
         <v>100</v>
@@ -5585,13 +5585,13 @@
         <v>256</v>
       </c>
       <c r="B258" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C258" t="n">
         <v>1</v>
       </c>
       <c r="D258" t="n">
-        <v>6.433568017923635e-08</v>
+        <v>3.728879669141288e-09</v>
       </c>
       <c r="E258" t="n">
         <v>100</v>
@@ -5605,13 +5605,13 @@
         <v>257</v>
       </c>
       <c r="B259" t="n">
-        <v>80</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C259" t="n">
         <v>1</v>
       </c>
       <c r="D259" t="n">
-        <v>6.433568017923635e-08</v>
+        <v>3.728879669141288e-09</v>
       </c>
       <c r="E259" t="n">
         <v>100</v>
@@ -5625,13 +5625,13 @@
         <v>258</v>
       </c>
       <c r="B260" t="n">
-        <v>80</v>
+        <v>45.6</v>
       </c>
       <c r="C260" t="n">
         <v>1</v>
       </c>
       <c r="D260" t="n">
-        <v>6.433568017923635e-08</v>
+        <v>3.728879669141288e-09</v>
       </c>
       <c r="E260" t="n">
         <v>100</v>
@@ -5645,13 +5645,13 @@
         <v>259</v>
       </c>
       <c r="B261" t="n">
-        <v>80</v>
+        <v>45.6</v>
       </c>
       <c r="C261" t="n">
         <v>1</v>
       </c>
       <c r="D261" t="n">
-        <v>6.433568017923635e-08</v>
+        <v>3.728879669141288e-09</v>
       </c>
       <c r="E261" t="n">
         <v>100</v>
@@ -5665,13 +5665,13 @@
         <v>260</v>
       </c>
       <c r="B262" t="n">
-        <v>80</v>
+        <v>45.6</v>
       </c>
       <c r="C262" t="n">
         <v>1</v>
       </c>
       <c r="D262" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E262" t="n">
         <v>100</v>
@@ -5685,13 +5685,13 @@
         <v>261</v>
       </c>
       <c r="B263" t="n">
-        <v>80</v>
+        <v>45.6</v>
       </c>
       <c r="C263" t="n">
         <v>1</v>
       </c>
       <c r="D263" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E263" t="n">
         <v>100</v>
@@ -5705,13 +5705,13 @@
         <v>262</v>
       </c>
       <c r="B264" t="n">
-        <v>80</v>
+        <v>45.6</v>
       </c>
       <c r="C264" t="n">
         <v>1</v>
       </c>
       <c r="D264" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E264" t="n">
         <v>100</v>
@@ -5725,13 +5725,13 @@
         <v>263</v>
       </c>
       <c r="B265" t="n">
-        <v>80</v>
+        <v>45.6</v>
       </c>
       <c r="C265" t="n">
         <v>1</v>
       </c>
       <c r="D265" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E265" t="n">
         <v>100</v>
@@ -5745,13 +5745,13 @@
         <v>264</v>
       </c>
       <c r="B266" t="n">
-        <v>80</v>
+        <v>45.6</v>
       </c>
       <c r="C266" t="n">
         <v>1</v>
       </c>
       <c r="D266" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E266" t="n">
         <v>100</v>
@@ -5765,13 +5765,13 @@
         <v>265</v>
       </c>
       <c r="B267" t="n">
-        <v>80</v>
+        <v>45.6</v>
       </c>
       <c r="C267" t="n">
         <v>1</v>
       </c>
       <c r="D267" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E267" t="n">
         <v>100</v>
@@ -5785,13 +5785,13 @@
         <v>266</v>
       </c>
       <c r="B268" t="n">
-        <v>80</v>
+        <v>45.6</v>
       </c>
       <c r="C268" t="n">
         <v>1</v>
       </c>
       <c r="D268" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E268" t="n">
         <v>100</v>
@@ -5805,13 +5805,13 @@
         <v>267</v>
       </c>
       <c r="B269" t="n">
-        <v>80</v>
+        <v>45.6</v>
       </c>
       <c r="C269" t="n">
         <v>1</v>
       </c>
       <c r="D269" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E269" t="n">
         <v>100</v>
@@ -5825,13 +5825,13 @@
         <v>268</v>
       </c>
       <c r="B270" t="n">
-        <v>80</v>
+        <v>45.6</v>
       </c>
       <c r="C270" t="n">
         <v>1</v>
       </c>
       <c r="D270" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E270" t="n">
         <v>100</v>
@@ -5845,13 +5845,13 @@
         <v>269</v>
       </c>
       <c r="B271" t="n">
-        <v>79.2</v>
+        <v>45.6</v>
       </c>
       <c r="C271" t="n">
         <v>1</v>
       </c>
       <c r="D271" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E271" t="n">
         <v>100</v>
@@ -5865,13 +5865,13 @@
         <v>270</v>
       </c>
       <c r="B272" t="n">
-        <v>79.2</v>
+        <v>45.6</v>
       </c>
       <c r="C272" t="n">
         <v>1</v>
       </c>
       <c r="D272" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E272" t="n">
         <v>100</v>
@@ -5885,13 +5885,13 @@
         <v>271</v>
       </c>
       <c r="B273" t="n">
-        <v>79.2</v>
+        <v>45.6</v>
       </c>
       <c r="C273" t="n">
         <v>1</v>
       </c>
       <c r="D273" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E273" t="n">
         <v>100</v>
@@ -5905,13 +5905,13 @@
         <v>272</v>
       </c>
       <c r="B274" t="n">
-        <v>79.2</v>
+        <v>45.6</v>
       </c>
       <c r="C274" t="n">
         <v>1</v>
       </c>
       <c r="D274" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E274" t="n">
         <v>100</v>
@@ -5925,13 +5925,13 @@
         <v>273</v>
       </c>
       <c r="B275" t="n">
-        <v>77.2</v>
+        <v>45.6</v>
       </c>
       <c r="C275" t="n">
         <v>1</v>
       </c>
       <c r="D275" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E275" t="n">
         <v>100</v>
@@ -5945,13 +5945,13 @@
         <v>274</v>
       </c>
       <c r="B276" t="n">
-        <v>77.2</v>
+        <v>45.6</v>
       </c>
       <c r="C276" t="n">
         <v>1</v>
       </c>
       <c r="D276" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E276" t="n">
         <v>100</v>
@@ -5965,13 +5965,13 @@
         <v>275</v>
       </c>
       <c r="B277" t="n">
-        <v>77.2</v>
+        <v>44.8</v>
       </c>
       <c r="C277" t="n">
         <v>1</v>
       </c>
       <c r="D277" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E277" t="n">
         <v>100</v>
@@ -5985,13 +5985,13 @@
         <v>276</v>
       </c>
       <c r="B278" t="n">
-        <v>77.2</v>
+        <v>44.8</v>
       </c>
       <c r="C278" t="n">
         <v>1</v>
       </c>
       <c r="D278" t="n">
-        <v>6.33855112967051e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E278" t="n">
         <v>100</v>
@@ -6005,13 +6005,13 @@
         <v>277</v>
       </c>
       <c r="B279" t="n">
-        <v>77.2</v>
+        <v>44.8</v>
       </c>
       <c r="C279" t="n">
         <v>1</v>
       </c>
       <c r="D279" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.654270428346982e-09</v>
       </c>
       <c r="E279" t="n">
         <v>100</v>
@@ -6025,13 +6025,13 @@
         <v>278</v>
       </c>
       <c r="B280" t="n">
-        <v>77.2</v>
+        <v>44.8</v>
       </c>
       <c r="C280" t="n">
         <v>1</v>
       </c>
       <c r="D280" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.573992381841009e-09</v>
       </c>
       <c r="E280" t="n">
         <v>100</v>
@@ -6045,13 +6045,13 @@
         <v>279</v>
       </c>
       <c r="B281" t="n">
-        <v>77.2</v>
+        <v>44.8</v>
       </c>
       <c r="C281" t="n">
         <v>1</v>
       </c>
       <c r="D281" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.573992381841009e-09</v>
       </c>
       <c r="E281" t="n">
         <v>100</v>
@@ -6065,13 +6065,13 @@
         <v>280</v>
       </c>
       <c r="B282" t="n">
-        <v>77.2</v>
+        <v>44.8</v>
       </c>
       <c r="C282" t="n">
         <v>1</v>
       </c>
       <c r="D282" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.573992381841009e-09</v>
       </c>
       <c r="E282" t="n">
         <v>100</v>
@@ -6085,13 +6085,13 @@
         <v>281</v>
       </c>
       <c r="B283" t="n">
-        <v>77.2</v>
+        <v>44.8</v>
       </c>
       <c r="C283" t="n">
         <v>1</v>
       </c>
       <c r="D283" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.573992381841009e-09</v>
       </c>
       <c r="E283" t="n">
         <v>100</v>
@@ -6105,13 +6105,13 @@
         <v>282</v>
       </c>
       <c r="B284" t="n">
-        <v>77.2</v>
+        <v>44.8</v>
       </c>
       <c r="C284" t="n">
         <v>1</v>
       </c>
       <c r="D284" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.573992381841009e-09</v>
       </c>
       <c r="E284" t="n">
         <v>100</v>
@@ -6125,13 +6125,13 @@
         <v>283</v>
       </c>
       <c r="B285" t="n">
-        <v>77.2</v>
+        <v>44.8</v>
       </c>
       <c r="C285" t="n">
         <v>1</v>
       </c>
       <c r="D285" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.573992381841009e-09</v>
       </c>
       <c r="E285" t="n">
         <v>100</v>
@@ -6145,13 +6145,13 @@
         <v>284</v>
       </c>
       <c r="B286" t="n">
-        <v>72.80000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="C286" t="n">
         <v>1</v>
       </c>
       <c r="D286" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.573992381841009e-09</v>
       </c>
       <c r="E286" t="n">
         <v>100</v>
@@ -6165,13 +6165,13 @@
         <v>285</v>
       </c>
       <c r="B287" t="n">
-        <v>72.80000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="C287" t="n">
         <v>1</v>
       </c>
       <c r="D287" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.573992381841009e-09</v>
       </c>
       <c r="E287" t="n">
         <v>100</v>
@@ -6185,13 +6185,13 @@
         <v>286</v>
       </c>
       <c r="B288" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C288" t="n">
         <v>1</v>
       </c>
       <c r="D288" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.573992381841009e-09</v>
       </c>
       <c r="E288" t="n">
         <v>100</v>
@@ -6205,13 +6205,13 @@
         <v>287</v>
       </c>
       <c r="B289" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C289" t="n">
         <v>1</v>
       </c>
       <c r="D289" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.418917169520402e-09</v>
       </c>
       <c r="E289" t="n">
         <v>100</v>
@@ -6225,13 +6225,13 @@
         <v>288</v>
       </c>
       <c r="B290" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C290" t="n">
         <v>1</v>
       </c>
       <c r="D290" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.418917169520402e-09</v>
       </c>
       <c r="E290" t="n">
         <v>100</v>
@@ -6245,13 +6245,13 @@
         <v>289</v>
       </c>
       <c r="B291" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C291" t="n">
         <v>1</v>
       </c>
       <c r="D291" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.418917169520402e-09</v>
       </c>
       <c r="E291" t="n">
         <v>100</v>
@@ -6265,13 +6265,13 @@
         <v>290</v>
       </c>
       <c r="B292" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C292" t="n">
         <v>1</v>
       </c>
       <c r="D292" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.341093170075882e-09</v>
       </c>
       <c r="E292" t="n">
         <v>100</v>
@@ -6285,13 +6285,13 @@
         <v>291</v>
       </c>
       <c r="B293" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C293" t="n">
         <v>1</v>
       </c>
       <c r="D293" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.341093170075882e-09</v>
       </c>
       <c r="E293" t="n">
         <v>100</v>
@@ -6305,13 +6305,13 @@
         <v>292</v>
       </c>
       <c r="B294" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C294" t="n">
         <v>1</v>
       </c>
       <c r="D294" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.341093170075882e-09</v>
       </c>
       <c r="E294" t="n">
         <v>100</v>
@@ -6325,13 +6325,13 @@
         <v>293</v>
       </c>
       <c r="B295" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C295" t="n">
         <v>1</v>
       </c>
       <c r="D295" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.341093170075882e-09</v>
       </c>
       <c r="E295" t="n">
         <v>100</v>
@@ -6345,13 +6345,13 @@
         <v>294</v>
       </c>
       <c r="B296" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C296" t="n">
         <v>1</v>
       </c>
       <c r="D296" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.341093170075882e-09</v>
       </c>
       <c r="E296" t="n">
         <v>100</v>
@@ -6365,13 +6365,13 @@
         <v>295</v>
       </c>
       <c r="B297" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C297" t="n">
         <v>1</v>
       </c>
       <c r="D297" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.341093170075882e-09</v>
       </c>
       <c r="E297" t="n">
         <v>100</v>
@@ -6385,13 +6385,13 @@
         <v>296</v>
       </c>
       <c r="B298" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C298" t="n">
         <v>1</v>
       </c>
       <c r="D298" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.341093170075882e-09</v>
       </c>
       <c r="E298" t="n">
         <v>100</v>
@@ -6405,13 +6405,13 @@
         <v>297</v>
       </c>
       <c r="B299" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C299" t="n">
         <v>1</v>
       </c>
       <c r="D299" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.264146769912705e-09</v>
       </c>
       <c r="E299" t="n">
         <v>100</v>
@@ -6425,13 +6425,13 @@
         <v>298</v>
       </c>
       <c r="B300" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C300" t="n">
         <v>1</v>
       </c>
       <c r="D300" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.264146769912705e-09</v>
       </c>
       <c r="E300" t="n">
         <v>100</v>
@@ -6445,13 +6445,13 @@
         <v>299</v>
       </c>
       <c r="B301" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C301" t="n">
         <v>1</v>
       </c>
       <c r="D301" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.264146769912705e-09</v>
       </c>
       <c r="E301" t="n">
         <v>100</v>
@@ -6465,13 +6465,13 @@
         <v>300</v>
       </c>
       <c r="B302" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C302" t="n">
         <v>1</v>
       </c>
       <c r="D302" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.264146769912705e-09</v>
       </c>
       <c r="E302" t="n">
         <v>100</v>
@@ -6485,13 +6485,13 @@
         <v>301</v>
       </c>
       <c r="B303" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C303" t="n">
         <v>1</v>
       </c>
       <c r="D303" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>3.264146769912705e-09</v>
       </c>
       <c r="E303" t="n">
         <v>100</v>
@@ -6505,13 +6505,13 @@
         <v>302</v>
       </c>
       <c r="B304" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C304" t="n">
         <v>1</v>
       </c>
       <c r="D304" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E304" t="n">
         <v>100</v>
@@ -6525,13 +6525,13 @@
         <v>303</v>
       </c>
       <c r="B305" t="n">
-        <v>69.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="C305" t="n">
         <v>1</v>
       </c>
       <c r="D305" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E305" t="n">
         <v>100</v>
@@ -6545,13 +6545,13 @@
         <v>304</v>
       </c>
       <c r="B306" t="n">
-        <v>69.59999999999999</v>
+        <v>44</v>
       </c>
       <c r="C306" t="n">
         <v>1</v>
       </c>
       <c r="D306" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E306" t="n">
         <v>100</v>
@@ -6565,13 +6565,13 @@
         <v>305</v>
       </c>
       <c r="B307" t="n">
-        <v>69.59999999999999</v>
+        <v>44</v>
       </c>
       <c r="C307" t="n">
         <v>1</v>
       </c>
       <c r="D307" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E307" t="n">
         <v>100</v>
@@ -6585,13 +6585,13 @@
         <v>306</v>
       </c>
       <c r="B308" t="n">
-        <v>69.59999999999999</v>
+        <v>44</v>
       </c>
       <c r="C308" t="n">
         <v>1</v>
       </c>
       <c r="D308" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E308" t="n">
         <v>100</v>
@@ -6605,13 +6605,13 @@
         <v>307</v>
       </c>
       <c r="B309" t="n">
-        <v>69.59999999999999</v>
+        <v>44</v>
       </c>
       <c r="C309" t="n">
         <v>1</v>
       </c>
       <c r="D309" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E309" t="n">
         <v>100</v>
@@ -6625,13 +6625,13 @@
         <v>308</v>
       </c>
       <c r="B310" t="n">
-        <v>69.59999999999999</v>
+        <v>44</v>
       </c>
       <c r="C310" t="n">
         <v>1</v>
       </c>
       <c r="D310" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E310" t="n">
         <v>100</v>
@@ -6645,13 +6645,13 @@
         <v>309</v>
       </c>
       <c r="B311" t="n">
-        <v>69.59999999999999</v>
+        <v>44</v>
       </c>
       <c r="C311" t="n">
         <v>1</v>
       </c>
       <c r="D311" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E311" t="n">
         <v>100</v>
@@ -6665,13 +6665,13 @@
         <v>310</v>
       </c>
       <c r="B312" t="n">
-        <v>69.59999999999999</v>
+        <v>44</v>
       </c>
       <c r="C312" t="n">
         <v>1</v>
       </c>
       <c r="D312" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E312" t="n">
         <v>100</v>
@@ -6685,13 +6685,13 @@
         <v>311</v>
       </c>
       <c r="B313" t="n">
-        <v>69.59999999999999</v>
+        <v>44</v>
       </c>
       <c r="C313" t="n">
         <v>1</v>
       </c>
       <c r="D313" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E313" t="n">
         <v>100</v>
@@ -6705,13 +6705,13 @@
         <v>312</v>
       </c>
       <c r="B314" t="n">
-        <v>69.59999999999999</v>
+        <v>44</v>
       </c>
       <c r="C314" t="n">
         <v>1</v>
       </c>
       <c r="D314" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E314" t="n">
         <v>100</v>
@@ -6725,13 +6725,13 @@
         <v>313</v>
       </c>
       <c r="B315" t="n">
-        <v>69.59999999999999</v>
+        <v>44</v>
       </c>
       <c r="C315" t="n">
         <v>1</v>
       </c>
       <c r="D315" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E315" t="n">
         <v>100</v>
@@ -6745,13 +6745,13 @@
         <v>314</v>
       </c>
       <c r="B316" t="n">
-        <v>69.59999999999999</v>
+        <v>44</v>
       </c>
       <c r="C316" t="n">
         <v>1</v>
       </c>
       <c r="D316" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E316" t="n">
         <v>100</v>
@@ -6765,13 +6765,13 @@
         <v>315</v>
       </c>
       <c r="B317" t="n">
-        <v>69.59999999999999</v>
+        <v>44</v>
       </c>
       <c r="C317" t="n">
         <v>1</v>
       </c>
       <c r="D317" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E317" t="n">
         <v>100</v>
@@ -6785,13 +6785,13 @@
         <v>316</v>
       </c>
       <c r="B318" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C318" t="n">
         <v>1</v>
       </c>
       <c r="D318" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E318" t="n">
         <v>100</v>
@@ -6805,13 +6805,13 @@
         <v>317</v>
       </c>
       <c r="B319" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C319" t="n">
         <v>1</v>
       </c>
       <c r="D319" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E319" t="n">
         <v>100</v>
@@ -6825,13 +6825,13 @@
         <v>318</v>
       </c>
       <c r="B320" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C320" t="n">
         <v>1</v>
       </c>
       <c r="D320" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E320" t="n">
         <v>100</v>
@@ -6845,13 +6845,13 @@
         <v>319</v>
       </c>
       <c r="B321" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C321" t="n">
         <v>1</v>
       </c>
       <c r="D321" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E321" t="n">
         <v>100</v>
@@ -6865,13 +6865,13 @@
         <v>320</v>
       </c>
       <c r="B322" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C322" t="n">
         <v>1</v>
       </c>
       <c r="D322" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E322" t="n">
         <v>100</v>
@@ -6885,13 +6885,13 @@
         <v>321</v>
       </c>
       <c r="B323" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C323" t="n">
         <v>1</v>
       </c>
       <c r="D323" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E323" t="n">
         <v>100</v>
@@ -6905,13 +6905,13 @@
         <v>322</v>
       </c>
       <c r="B324" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C324" t="n">
         <v>1</v>
       </c>
       <c r="D324" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E324" t="n">
         <v>100</v>
@@ -6925,13 +6925,13 @@
         <v>323</v>
       </c>
       <c r="B325" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C325" t="n">
         <v>1</v>
       </c>
       <c r="D325" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E325" t="n">
         <v>100</v>
@@ -6945,13 +6945,13 @@
         <v>324</v>
       </c>
       <c r="B326" t="n">
-        <v>63.6</v>
+        <v>44</v>
       </c>
       <c r="C326" t="n">
         <v>1</v>
       </c>
       <c r="D326" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E326" t="n">
         <v>100</v>
@@ -6965,13 +6965,13 @@
         <v>325</v>
       </c>
       <c r="B327" t="n">
-        <v>63.6</v>
+        <v>44</v>
       </c>
       <c r="C327" t="n">
         <v>1</v>
       </c>
       <c r="D327" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E327" t="n">
         <v>100</v>
@@ -6985,13 +6985,13 @@
         <v>326</v>
       </c>
       <c r="B328" t="n">
-        <v>63.6</v>
+        <v>44</v>
       </c>
       <c r="C328" t="n">
         <v>1</v>
       </c>
       <c r="D328" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E328" t="n">
         <v>100</v>
@@ -7005,13 +7005,13 @@
         <v>327</v>
       </c>
       <c r="B329" t="n">
-        <v>63.6</v>
+        <v>44</v>
       </c>
       <c r="C329" t="n">
         <v>1</v>
       </c>
       <c r="D329" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E329" t="n">
         <v>100</v>
@@ -7025,13 +7025,13 @@
         <v>328</v>
       </c>
       <c r="B330" t="n">
-        <v>63.6</v>
+        <v>44</v>
       </c>
       <c r="C330" t="n">
         <v>1</v>
       </c>
       <c r="D330" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E330" t="n">
         <v>100</v>
@@ -7045,13 +7045,13 @@
         <v>329</v>
       </c>
       <c r="B331" t="n">
-        <v>63.6</v>
+        <v>44</v>
       </c>
       <c r="C331" t="n">
         <v>1</v>
       </c>
       <c r="D331" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E331" t="n">
         <v>100</v>
@@ -7065,13 +7065,13 @@
         <v>330</v>
       </c>
       <c r="B332" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C332" t="n">
         <v>1</v>
       </c>
       <c r="D332" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E332" t="n">
         <v>100</v>
@@ -7085,13 +7085,13 @@
         <v>331</v>
       </c>
       <c r="B333" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C333" t="n">
         <v>1</v>
       </c>
       <c r="D333" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.840943391588845e-09</v>
       </c>
       <c r="E333" t="n">
         <v>100</v>
@@ -7105,13 +7105,13 @@
         <v>332</v>
       </c>
       <c r="B334" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C334" t="n">
         <v>1</v>
       </c>
       <c r="D334" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.56646097111198e-09</v>
       </c>
       <c r="E334" t="n">
         <v>100</v>
@@ -7125,13 +7125,13 @@
         <v>333</v>
       </c>
       <c r="B335" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C335" t="n">
         <v>1</v>
       </c>
       <c r="D335" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.56646097111198e-09</v>
       </c>
       <c r="E335" t="n">
         <v>100</v>
@@ -7145,13 +7145,13 @@
         <v>334</v>
       </c>
       <c r="B336" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C336" t="n">
         <v>1</v>
       </c>
       <c r="D336" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.56646097111198e-09</v>
       </c>
       <c r="E336" t="n">
         <v>100</v>
@@ -7165,13 +7165,13 @@
         <v>335</v>
       </c>
       <c r="B337" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C337" t="n">
         <v>1</v>
       </c>
       <c r="D337" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.56646097111198e-09</v>
       </c>
       <c r="E337" t="n">
         <v>100</v>
@@ -7185,13 +7185,13 @@
         <v>336</v>
       </c>
       <c r="B338" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C338" t="n">
         <v>1</v>
       </c>
       <c r="D338" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.56646097111198e-09</v>
       </c>
       <c r="E338" t="n">
         <v>100</v>
@@ -7205,13 +7205,13 @@
         <v>337</v>
       </c>
       <c r="B339" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C339" t="n">
         <v>1</v>
       </c>
       <c r="D339" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.56646097111198e-09</v>
       </c>
       <c r="E339" t="n">
         <v>100</v>
@@ -7225,13 +7225,13 @@
         <v>338</v>
       </c>
       <c r="B340" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C340" t="n">
         <v>1</v>
       </c>
       <c r="D340" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.56646097111198e-09</v>
       </c>
       <c r="E340" t="n">
         <v>100</v>
@@ -7245,13 +7245,13 @@
         <v>339</v>
       </c>
       <c r="B341" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C341" t="n">
         <v>1</v>
       </c>
       <c r="D341" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.56646097111198e-09</v>
       </c>
       <c r="E341" t="n">
         <v>100</v>
@@ -7265,13 +7265,13 @@
         <v>340</v>
       </c>
       <c r="B342" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C342" t="n">
         <v>1</v>
       </c>
       <c r="D342" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.56646097111198e-09</v>
       </c>
       <c r="E342" t="n">
         <v>100</v>
@@ -7285,13 +7285,13 @@
         <v>341</v>
       </c>
       <c r="B343" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C343" t="n">
         <v>1</v>
       </c>
       <c r="D343" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.56646097111198e-09</v>
       </c>
       <c r="E343" t="n">
         <v>100</v>
@@ -7305,13 +7305,13 @@
         <v>342</v>
       </c>
       <c r="B344" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C344" t="n">
         <v>1</v>
       </c>
       <c r="D344" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.410850634694344e-09</v>
       </c>
       <c r="E344" t="n">
         <v>100</v>
@@ -7325,13 +7325,13 @@
         <v>343</v>
       </c>
       <c r="B345" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C345" t="n">
         <v>1</v>
       </c>
       <c r="D345" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.410850634694344e-09</v>
       </c>
       <c r="E345" t="n">
         <v>100</v>
@@ -7345,13 +7345,13 @@
         <v>344</v>
       </c>
       <c r="B346" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C346" t="n">
         <v>1</v>
       </c>
       <c r="D346" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.410850634694344e-09</v>
       </c>
       <c r="E346" t="n">
         <v>100</v>
@@ -7365,13 +7365,13 @@
         <v>345</v>
       </c>
       <c r="B347" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C347" t="n">
         <v>1</v>
       </c>
       <c r="D347" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.410850634694344e-09</v>
       </c>
       <c r="E347" t="n">
         <v>100</v>
@@ -7385,13 +7385,13 @@
         <v>346</v>
       </c>
       <c r="B348" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C348" t="n">
         <v>1</v>
       </c>
       <c r="D348" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.410850634694344e-09</v>
       </c>
       <c r="E348" t="n">
         <v>100</v>
@@ -7405,13 +7405,13 @@
         <v>347</v>
       </c>
       <c r="B349" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C349" t="n">
         <v>1</v>
       </c>
       <c r="D349" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.410850634694344e-09</v>
       </c>
       <c r="E349" t="n">
         <v>100</v>
@@ -7425,13 +7425,13 @@
         <v>348</v>
       </c>
       <c r="B350" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C350" t="n">
         <v>1</v>
       </c>
       <c r="D350" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.410850634694344e-09</v>
       </c>
       <c r="E350" t="n">
         <v>100</v>
@@ -7445,13 +7445,13 @@
         <v>349</v>
       </c>
       <c r="B351" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C351" t="n">
         <v>1</v>
       </c>
       <c r="D351" t="n">
-        <v>5.695488751581031e-08</v>
+        <v>2.410850634694344e-09</v>
       </c>
       <c r="E351" t="n">
         <v>100</v>
@@ -7465,13 +7465,13 @@
         <v>350</v>
       </c>
       <c r="B352" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C352" t="n">
         <v>1</v>
       </c>
       <c r="D352" t="n">
-        <v>5.618795314092187e-08</v>
+        <v>2.410850634694344e-09</v>
       </c>
       <c r="E352" t="n">
         <v>100</v>
@@ -7485,13 +7485,13 @@
         <v>351</v>
       </c>
       <c r="B353" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C353" t="n">
         <v>1</v>
       </c>
       <c r="D353" t="n">
-        <v>5.618795314092187e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E353" t="n">
         <v>100</v>
@@ -7505,13 +7505,13 @@
         <v>352</v>
       </c>
       <c r="B354" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C354" t="n">
         <v>1</v>
       </c>
       <c r="D354" t="n">
-        <v>5.618795314092187e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E354" t="n">
         <v>100</v>
@@ -7525,13 +7525,13 @@
         <v>353</v>
       </c>
       <c r="B355" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C355" t="n">
         <v>1</v>
       </c>
       <c r="D355" t="n">
-        <v>5.007992302212609e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E355" t="n">
         <v>100</v>
@@ -7545,13 +7545,13 @@
         <v>354</v>
       </c>
       <c r="B356" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C356" t="n">
         <v>1</v>
       </c>
       <c r="D356" t="n">
-        <v>5.007992302212609e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E356" t="n">
         <v>100</v>
@@ -7565,13 +7565,13 @@
         <v>355</v>
       </c>
       <c r="B357" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C357" t="n">
         <v>1</v>
       </c>
       <c r="D357" t="n">
-        <v>5.007992302212609e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E357" t="n">
         <v>100</v>
@@ -7585,13 +7585,13 @@
         <v>356</v>
       </c>
       <c r="B358" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C358" t="n">
         <v>1</v>
       </c>
       <c r="D358" t="n">
-        <v>4.863641202299056e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E358" t="n">
         <v>100</v>
@@ -7605,13 +7605,13 @@
         <v>357</v>
       </c>
       <c r="B359" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C359" t="n">
         <v>1</v>
       </c>
       <c r="D359" t="n">
-        <v>4.863641202299056e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E359" t="n">
         <v>100</v>
@@ -7625,13 +7625,13 @@
         <v>358</v>
       </c>
       <c r="B360" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C360" t="n">
         <v>1</v>
       </c>
       <c r="D360" t="n">
-        <v>4.863641202299056e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E360" t="n">
         <v>100</v>
@@ -7645,13 +7645,13 @@
         <v>359</v>
       </c>
       <c r="B361" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C361" t="n">
         <v>1</v>
       </c>
       <c r="D361" t="n">
-        <v>4.863641202299056e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E361" t="n">
         <v>100</v>
@@ -7665,13 +7665,13 @@
         <v>360</v>
       </c>
       <c r="B362" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C362" t="n">
         <v>1</v>
       </c>
       <c r="D362" t="n">
-        <v>4.863641202299056e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E362" t="n">
         <v>100</v>
@@ -7685,13 +7685,13 @@
         <v>361</v>
       </c>
       <c r="B363" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C363" t="n">
         <v>1</v>
       </c>
       <c r="D363" t="n">
-        <v>4.863641202299056e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E363" t="n">
         <v>100</v>
@@ -7705,13 +7705,13 @@
         <v>362</v>
       </c>
       <c r="B364" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C364" t="n">
         <v>1</v>
       </c>
       <c r="D364" t="n">
-        <v>4.863641202299056e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E364" t="n">
         <v>100</v>
@@ -7725,13 +7725,13 @@
         <v>363</v>
       </c>
       <c r="B365" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C365" t="n">
         <v>1</v>
       </c>
       <c r="D365" t="n">
-        <v>4.863641202299056e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E365" t="n">
         <v>100</v>
@@ -7745,13 +7745,13 @@
         <v>364</v>
       </c>
       <c r="B366" t="n">
-        <v>57.6</v>
+        <v>44</v>
       </c>
       <c r="C366" t="n">
         <v>1</v>
       </c>
       <c r="D366" t="n">
-        <v>4.863641202299056e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E366" t="n">
         <v>100</v>
@@ -7765,13 +7765,13 @@
         <v>365</v>
       </c>
       <c r="B367" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C367" t="n">
         <v>1</v>
       </c>
       <c r="D367" t="n">
-        <v>2.685596050651654e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E367" t="n">
         <v>100</v>
@@ -7785,13 +7785,13 @@
         <v>366</v>
       </c>
       <c r="B368" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C368" t="n">
         <v>1</v>
       </c>
       <c r="D368" t="n">
-        <v>2.685596050651654e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E368" t="n">
         <v>100</v>
@@ -7805,13 +7805,13 @@
         <v>367</v>
       </c>
       <c r="B369" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C369" t="n">
         <v>1</v>
       </c>
       <c r="D369" t="n">
-        <v>2.685596050651654e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E369" t="n">
         <v>100</v>
@@ -7825,13 +7825,13 @@
         <v>368</v>
       </c>
       <c r="B370" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C370" t="n">
         <v>1</v>
       </c>
       <c r="D370" t="n">
-        <v>2.685596050651654e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E370" t="n">
         <v>100</v>
@@ -7845,13 +7845,13 @@
         <v>369</v>
       </c>
       <c r="B371" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C371" t="n">
         <v>1</v>
       </c>
       <c r="D371" t="n">
-        <v>2.624322097883322e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E371" t="n">
         <v>100</v>
@@ -7865,13 +7865,13 @@
         <v>370</v>
       </c>
       <c r="B372" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C372" t="n">
         <v>1</v>
       </c>
       <c r="D372" t="n">
-        <v>2.624322097883322e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E372" t="n">
         <v>100</v>
@@ -7885,13 +7885,13 @@
         <v>371</v>
       </c>
       <c r="B373" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C373" t="n">
         <v>1</v>
       </c>
       <c r="D373" t="n">
-        <v>2.624322097883322e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E373" t="n">
         <v>100</v>
@@ -7905,13 +7905,13 @@
         <v>372</v>
       </c>
       <c r="B374" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C374" t="n">
         <v>1</v>
       </c>
       <c r="D374" t="n">
-        <v>2.581238031311892e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E374" t="n">
         <v>100</v>
@@ -7925,13 +7925,13 @@
         <v>373</v>
       </c>
       <c r="B375" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C375" t="n">
         <v>1</v>
       </c>
       <c r="D375" t="n">
-        <v>2.581238031311892e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E375" t="n">
         <v>100</v>
@@ -7945,13 +7945,13 @@
         <v>374</v>
       </c>
       <c r="B376" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C376" t="n">
         <v>1</v>
       </c>
       <c r="D376" t="n">
-        <v>2.581238031311892e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E376" t="n">
         <v>100</v>
@@ -7965,13 +7965,13 @@
         <v>375</v>
       </c>
       <c r="B377" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C377" t="n">
         <v>1</v>
       </c>
       <c r="D377" t="n">
-        <v>2.568045116202853e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E377" t="n">
         <v>100</v>
@@ -7985,13 +7985,13 @@
         <v>376</v>
       </c>
       <c r="B378" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C378" t="n">
         <v>1</v>
       </c>
       <c r="D378" t="n">
-        <v>2.568045116202853e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E378" t="n">
         <v>100</v>
@@ -8005,13 +8005,13 @@
         <v>377</v>
       </c>
       <c r="B379" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C379" t="n">
         <v>1</v>
       </c>
       <c r="D379" t="n">
-        <v>2.568045116202853e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E379" t="n">
         <v>100</v>
@@ -8025,13 +8025,13 @@
         <v>378</v>
       </c>
       <c r="B380" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C380" t="n">
         <v>1</v>
       </c>
       <c r="D380" t="n">
-        <v>2.568045116202853e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E380" t="n">
         <v>100</v>
@@ -8045,13 +8045,13 @@
         <v>379</v>
       </c>
       <c r="B381" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C381" t="n">
         <v>1</v>
       </c>
       <c r="D381" t="n">
-        <v>2.568045116202853e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E381" t="n">
         <v>100</v>
@@ -8065,13 +8065,13 @@
         <v>380</v>
       </c>
       <c r="B382" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C382" t="n">
         <v>1</v>
       </c>
       <c r="D382" t="n">
-        <v>2.568045116202853e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E382" t="n">
         <v>100</v>
@@ -8085,13 +8085,13 @@
         <v>381</v>
       </c>
       <c r="B383" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C383" t="n">
         <v>1</v>
       </c>
       <c r="D383" t="n">
-        <v>2.568045116202853e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E383" t="n">
         <v>100</v>
@@ -8105,13 +8105,13 @@
         <v>382</v>
       </c>
       <c r="B384" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C384" t="n">
         <v>1</v>
       </c>
       <c r="D384" t="n">
-        <v>2.568045116202853e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E384" t="n">
         <v>100</v>
@@ -8125,13 +8125,13 @@
         <v>383</v>
       </c>
       <c r="B385" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C385" t="n">
         <v>1</v>
       </c>
       <c r="D385" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E385" t="n">
         <v>100</v>
@@ -8145,13 +8145,13 @@
         <v>384</v>
       </c>
       <c r="B386" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C386" t="n">
         <v>1</v>
       </c>
       <c r="D386" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E386" t="n">
         <v>100</v>
@@ -8165,13 +8165,13 @@
         <v>385</v>
       </c>
       <c r="B387" t="n">
-        <v>57.6</v>
+        <v>43.2</v>
       </c>
       <c r="C387" t="n">
         <v>1</v>
       </c>
       <c r="D387" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E387" t="n">
         <v>100</v>
@@ -8185,13 +8185,13 @@
         <v>386</v>
       </c>
       <c r="B388" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C388" t="n">
         <v>1</v>
       </c>
       <c r="D388" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E388" t="n">
         <v>100</v>
@@ -8205,13 +8205,13 @@
         <v>387</v>
       </c>
       <c r="B389" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C389" t="n">
         <v>1</v>
       </c>
       <c r="D389" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E389" t="n">
         <v>100</v>
@@ -8225,13 +8225,13 @@
         <v>388</v>
       </c>
       <c r="B390" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C390" t="n">
         <v>1</v>
       </c>
       <c r="D390" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E390" t="n">
         <v>100</v>
@@ -8245,13 +8245,13 @@
         <v>389</v>
       </c>
       <c r="B391" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C391" t="n">
         <v>1</v>
       </c>
       <c r="D391" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E391" t="n">
         <v>100</v>
@@ -8265,13 +8265,13 @@
         <v>390</v>
       </c>
       <c r="B392" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C392" t="n">
         <v>1</v>
       </c>
       <c r="D392" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E392" t="n">
         <v>100</v>
@@ -8285,13 +8285,13 @@
         <v>391</v>
       </c>
       <c r="B393" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C393" t="n">
         <v>1</v>
       </c>
       <c r="D393" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E393" t="n">
         <v>100</v>
@@ -8305,13 +8305,13 @@
         <v>392</v>
       </c>
       <c r="B394" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C394" t="n">
         <v>1</v>
       </c>
       <c r="D394" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E394" t="n">
         <v>100</v>
@@ -8325,13 +8325,13 @@
         <v>393</v>
       </c>
       <c r="B395" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C395" t="n">
         <v>1</v>
       </c>
       <c r="D395" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E395" t="n">
         <v>100</v>
@@ -8345,13 +8345,13 @@
         <v>394</v>
       </c>
       <c r="B396" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C396" t="n">
         <v>1</v>
       </c>
       <c r="D396" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E396" t="n">
         <v>100</v>
@@ -8365,13 +8365,13 @@
         <v>395</v>
       </c>
       <c r="B397" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C397" t="n">
         <v>1</v>
       </c>
       <c r="D397" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E397" t="n">
         <v>100</v>
@@ -8385,13 +8385,13 @@
         <v>396</v>
       </c>
       <c r="B398" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C398" t="n">
         <v>1</v>
       </c>
       <c r="D398" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E398" t="n">
         <v>100</v>
@@ -8405,13 +8405,13 @@
         <v>397</v>
       </c>
       <c r="B399" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C399" t="n">
         <v>1</v>
       </c>
       <c r="D399" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E399" t="n">
         <v>100</v>
@@ -8425,13 +8425,13 @@
         <v>398</v>
       </c>
       <c r="B400" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C400" t="n">
         <v>1</v>
       </c>
       <c r="D400" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E400" t="n">
         <v>100</v>
@@ -8445,13 +8445,13 @@
         <v>399</v>
       </c>
       <c r="B401" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C401" t="n">
         <v>1</v>
       </c>
       <c r="D401" t="n">
-        <v>2.474232753148073e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E401" t="n">
         <v>100</v>
@@ -8465,13 +8465,13 @@
         <v>400</v>
       </c>
       <c r="B402" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C402" t="n">
         <v>1</v>
       </c>
       <c r="D402" t="n">
-        <v>2.399489785115948e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E402" t="n">
         <v>100</v>
@@ -8485,13 +8485,13 @@
         <v>401</v>
       </c>
       <c r="B403" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C403" t="n">
         <v>1</v>
       </c>
       <c r="D403" t="n">
-        <v>2.399489785115948e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E403" t="n">
         <v>100</v>
@@ -8505,13 +8505,13 @@
         <v>402</v>
       </c>
       <c r="B404" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C404" t="n">
         <v>1</v>
       </c>
       <c r="D404" t="n">
-        <v>2.399489785115948e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E404" t="n">
         <v>100</v>
@@ -8525,13 +8525,13 @@
         <v>403</v>
       </c>
       <c r="B405" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C405" t="n">
         <v>1</v>
       </c>
       <c r="D405" t="n">
-        <v>2.399489785115948e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E405" t="n">
         <v>100</v>
@@ -8545,13 +8545,13 @@
         <v>404</v>
       </c>
       <c r="B406" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C406" t="n">
         <v>1</v>
       </c>
       <c r="D406" t="n">
-        <v>2.399489785115948e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E406" t="n">
         <v>100</v>
@@ -8565,13 +8565,13 @@
         <v>405</v>
       </c>
       <c r="B407" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C407" t="n">
         <v>1</v>
       </c>
       <c r="D407" t="n">
-        <v>2.399489785115948e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E407" t="n">
         <v>100</v>
@@ -8585,13 +8585,13 @@
         <v>406</v>
       </c>
       <c r="B408" t="n">
-        <v>57.6</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C408" t="n">
         <v>1</v>
       </c>
       <c r="D408" t="n">
-        <v>2.399489785115948e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E408" t="n">
         <v>100</v>
@@ -8605,13 +8605,13 @@
         <v>407</v>
       </c>
       <c r="B409" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C409" t="n">
         <v>1</v>
       </c>
       <c r="D409" t="n">
-        <v>2.307667167834728e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E409" t="n">
         <v>100</v>
@@ -8625,13 +8625,13 @@
         <v>408</v>
       </c>
       <c r="B410" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C410" t="n">
         <v>1</v>
       </c>
       <c r="D410" t="n">
-        <v>2.307667167834728e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E410" t="n">
         <v>100</v>
@@ -8645,13 +8645,13 @@
         <v>409</v>
       </c>
       <c r="B411" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C411" t="n">
         <v>1</v>
       </c>
       <c r="D411" t="n">
-        <v>2.307667167834728e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E411" t="n">
         <v>100</v>
@@ -8665,13 +8665,13 @@
         <v>410</v>
       </c>
       <c r="B412" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C412" t="n">
         <v>1</v>
       </c>
       <c r="D412" t="n">
-        <v>2.278713643654961e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E412" t="n">
         <v>100</v>
@@ -8685,13 +8685,13 @@
         <v>411</v>
       </c>
       <c r="B413" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C413" t="n">
         <v>1</v>
       </c>
       <c r="D413" t="n">
-        <v>2.278713643654961e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E413" t="n">
         <v>100</v>
@@ -8705,13 +8705,13 @@
         <v>412</v>
       </c>
       <c r="B414" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C414" t="n">
         <v>1</v>
       </c>
       <c r="D414" t="n">
-        <v>2.278713643654961e-08</v>
+        <v>2.259067506083117e-09</v>
       </c>
       <c r="E414" t="n">
         <v>100</v>
@@ -8725,13 +8725,13 @@
         <v>413</v>
       </c>
       <c r="B415" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C415" t="n">
         <v>1</v>
       </c>
       <c r="D415" t="n">
-        <v>2.278713643654961e-08</v>
+        <v>2.017035857269175e-09</v>
       </c>
       <c r="E415" t="n">
         <v>100</v>
@@ -8745,13 +8745,13 @@
         <v>414</v>
       </c>
       <c r="B416" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C416" t="n">
         <v>1</v>
       </c>
       <c r="D416" t="n">
-        <v>2.278713643654961e-08</v>
+        <v>2.017035857269175e-09</v>
       </c>
       <c r="E416" t="n">
         <v>100</v>
@@ -8765,13 +8765,13 @@
         <v>415</v>
       </c>
       <c r="B417" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C417" t="n">
         <v>1</v>
       </c>
       <c r="D417" t="n">
-        <v>2.278713643654961e-08</v>
+        <v>2.017035857269175e-09</v>
       </c>
       <c r="E417" t="n">
         <v>100</v>
@@ -8785,13 +8785,13 @@
         <v>416</v>
       </c>
       <c r="B418" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C418" t="n">
         <v>1</v>
       </c>
       <c r="D418" t="n">
-        <v>2.278713643654961e-08</v>
+        <v>2.017035857269175e-09</v>
       </c>
       <c r="E418" t="n">
         <v>100</v>
@@ -8805,13 +8805,13 @@
         <v>417</v>
       </c>
       <c r="B419" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C419" t="n">
         <v>1</v>
       </c>
       <c r="D419" t="n">
-        <v>2.278713643654961e-08</v>
+        <v>2.017035857269175e-09</v>
       </c>
       <c r="E419" t="n">
         <v>100</v>
@@ -8825,13 +8825,13 @@
         <v>418</v>
       </c>
       <c r="B420" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C420" t="n">
         <v>1</v>
       </c>
       <c r="D420" t="n">
-        <v>2.278713643654961e-08</v>
+        <v>2.017035857269175e-09</v>
       </c>
       <c r="E420" t="n">
         <v>100</v>
@@ -8845,13 +8845,13 @@
         <v>419</v>
       </c>
       <c r="B421" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C421" t="n">
         <v>1</v>
       </c>
       <c r="D421" t="n">
-        <v>2.278713643654961e-08</v>
+        <v>2.017035857269175e-09</v>
       </c>
       <c r="E421" t="n">
         <v>100</v>
@@ -8865,13 +8865,13 @@
         <v>420</v>
       </c>
       <c r="B422" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C422" t="n">
         <v>1</v>
       </c>
       <c r="D422" t="n">
-        <v>2.278713643654961e-08</v>
+        <v>1.955866602749126e-09</v>
       </c>
       <c r="E422" t="n">
         <v>100</v>
@@ -8885,13 +8885,13 @@
         <v>421</v>
       </c>
       <c r="B423" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C423" t="n">
         <v>1</v>
       </c>
       <c r="D423" t="n">
-        <v>1.773745850249995e-08</v>
+        <v>1.955866602749126e-09</v>
       </c>
       <c r="E423" t="n">
         <v>100</v>
@@ -8905,13 +8905,13 @@
         <v>422</v>
       </c>
       <c r="B424" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C424" t="n">
         <v>1</v>
       </c>
       <c r="D424" t="n">
-        <v>1.773745850249995e-08</v>
+        <v>1.955866602749126e-09</v>
       </c>
       <c r="E424" t="n">
         <v>100</v>
@@ -8925,13 +8925,13 @@
         <v>423</v>
       </c>
       <c r="B425" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C425" t="n">
         <v>1</v>
       </c>
       <c r="D425" t="n">
-        <v>1.773745850249995e-08</v>
+        <v>1.955866602749126e-09</v>
       </c>
       <c r="E425" t="n">
         <v>100</v>
@@ -8945,13 +8945,13 @@
         <v>424</v>
       </c>
       <c r="B426" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C426" t="n">
         <v>1</v>
       </c>
       <c r="D426" t="n">
-        <v>1.773745850249995e-08</v>
+        <v>1.955866602749126e-09</v>
       </c>
       <c r="E426" t="n">
         <v>100</v>
@@ -8965,13 +8965,13 @@
         <v>425</v>
       </c>
       <c r="B427" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C427" t="n">
         <v>1</v>
       </c>
       <c r="D427" t="n">
-        <v>1.773745850249995e-08</v>
+        <v>1.955866602749126e-09</v>
       </c>
       <c r="E427" t="n">
         <v>100</v>
@@ -8985,13 +8985,13 @@
         <v>426</v>
       </c>
       <c r="B428" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C428" t="n">
         <v>1</v>
       </c>
       <c r="D428" t="n">
-        <v>1.701669823074246e-08</v>
+        <v>1.955866602749126e-09</v>
       </c>
       <c r="E428" t="n">
         <v>100</v>
@@ -9005,13 +9005,13 @@
         <v>427</v>
       </c>
       <c r="B429" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C429" t="n">
         <v>1</v>
       </c>
       <c r="D429" t="n">
-        <v>1.692168624851986e-08</v>
+        <v>1.955866602749126e-09</v>
       </c>
       <c r="E429" t="n">
         <v>100</v>
@@ -9025,13 +9025,13 @@
         <v>428</v>
       </c>
       <c r="B430" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C430" t="n">
         <v>1</v>
       </c>
       <c r="D430" t="n">
-        <v>1.692168624851986e-08</v>
+        <v>1.955866602749126e-09</v>
       </c>
       <c r="E430" t="n">
         <v>100</v>
@@ -9045,13 +9045,13 @@
         <v>429</v>
       </c>
       <c r="B431" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C431" t="n">
         <v>1</v>
       </c>
       <c r="D431" t="n">
-        <v>1.692168624851986e-08</v>
+        <v>1.955866602749126e-09</v>
       </c>
       <c r="E431" t="n">
         <v>100</v>
@@ -9065,13 +9065,13 @@
         <v>430</v>
       </c>
       <c r="B432" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C432" t="n">
         <v>1</v>
       </c>
       <c r="D432" t="n">
-        <v>1.692168624851986e-08</v>
+        <v>1.955866602749126e-09</v>
       </c>
       <c r="E432" t="n">
         <v>100</v>
@@ -9085,13 +9085,13 @@
         <v>431</v>
       </c>
       <c r="B433" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C433" t="n">
         <v>1</v>
       </c>
       <c r="D433" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.586917636782343e-09</v>
       </c>
       <c r="E433" t="n">
         <v>100</v>
@@ -9105,13 +9105,13 @@
         <v>432</v>
       </c>
       <c r="B434" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C434" t="n">
         <v>1</v>
       </c>
       <c r="D434" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.586917636782343e-09</v>
       </c>
       <c r="E434" t="n">
         <v>100</v>
@@ -9125,13 +9125,13 @@
         <v>433</v>
       </c>
       <c r="B435" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C435" t="n">
         <v>1</v>
       </c>
       <c r="D435" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.586917636782343e-09</v>
       </c>
       <c r="E435" t="n">
         <v>100</v>
@@ -9145,13 +9145,13 @@
         <v>434</v>
       </c>
       <c r="B436" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C436" t="n">
         <v>1</v>
       </c>
       <c r="D436" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.586917636782343e-09</v>
       </c>
       <c r="E436" t="n">
         <v>100</v>
@@ -9165,13 +9165,13 @@
         <v>435</v>
       </c>
       <c r="B437" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C437" t="n">
         <v>1</v>
       </c>
       <c r="D437" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.586917636782343e-09</v>
       </c>
       <c r="E437" t="n">
         <v>100</v>
@@ -9185,13 +9185,13 @@
         <v>436</v>
       </c>
       <c r="B438" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C438" t="n">
         <v>1</v>
       </c>
       <c r="D438" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.586917636782343e-09</v>
       </c>
       <c r="E438" t="n">
         <v>100</v>
@@ -9205,13 +9205,13 @@
         <v>437</v>
       </c>
       <c r="B439" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C439" t="n">
         <v>1</v>
       </c>
       <c r="D439" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.552721219597908e-09</v>
       </c>
       <c r="E439" t="n">
         <v>100</v>
@@ -9225,13 +9225,13 @@
         <v>438</v>
       </c>
       <c r="B440" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C440" t="n">
         <v>1</v>
       </c>
       <c r="D440" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.552721219597908e-09</v>
       </c>
       <c r="E440" t="n">
         <v>100</v>
@@ -9245,13 +9245,13 @@
         <v>439</v>
       </c>
       <c r="B441" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C441" t="n">
         <v>1</v>
       </c>
       <c r="D441" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.552721219597908e-09</v>
       </c>
       <c r="E441" t="n">
         <v>100</v>
@@ -9265,13 +9265,13 @@
         <v>440</v>
       </c>
       <c r="B442" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C442" t="n">
         <v>1</v>
       </c>
       <c r="D442" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.552721219597908e-09</v>
       </c>
       <c r="E442" t="n">
         <v>100</v>
@@ -9285,13 +9285,13 @@
         <v>441</v>
       </c>
       <c r="B443" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C443" t="n">
         <v>1</v>
       </c>
       <c r="D443" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E443" t="n">
         <v>100</v>
@@ -9305,13 +9305,13 @@
         <v>442</v>
       </c>
       <c r="B444" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C444" t="n">
         <v>1</v>
       </c>
       <c r="D444" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E444" t="n">
         <v>100</v>
@@ -9325,13 +9325,13 @@
         <v>443</v>
       </c>
       <c r="B445" t="n">
-        <v>56.8</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C445" t="n">
         <v>1</v>
       </c>
       <c r="D445" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E445" t="n">
         <v>100</v>
@@ -9345,13 +9345,13 @@
         <v>444</v>
       </c>
       <c r="B446" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C446" t="n">
         <v>1</v>
       </c>
       <c r="D446" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E446" t="n">
         <v>100</v>
@@ -9365,13 +9365,13 @@
         <v>445</v>
       </c>
       <c r="B447" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C447" t="n">
         <v>1</v>
       </c>
       <c r="D447" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E447" t="n">
         <v>100</v>
@@ -9385,13 +9385,13 @@
         <v>446</v>
       </c>
       <c r="B448" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C448" t="n">
         <v>1</v>
       </c>
       <c r="D448" t="n">
-        <v>1.683042013480306e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E448" t="n">
         <v>100</v>
@@ -9405,13 +9405,13 @@
         <v>447</v>
       </c>
       <c r="B449" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C449" t="n">
         <v>1</v>
       </c>
       <c r="D449" t="n">
-        <v>1.254070322086232e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E449" t="n">
         <v>100</v>
@@ -9425,13 +9425,13 @@
         <v>448</v>
       </c>
       <c r="B450" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C450" t="n">
         <v>1</v>
       </c>
       <c r="D450" t="n">
-        <v>1.254070322086232e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E450" t="n">
         <v>100</v>
@@ -9445,13 +9445,13 @@
         <v>449</v>
       </c>
       <c r="B451" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C451" t="n">
         <v>1</v>
       </c>
       <c r="D451" t="n">
-        <v>1.254070322086232e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E451" t="n">
         <v>100</v>
@@ -9465,13 +9465,13 @@
         <v>450</v>
       </c>
       <c r="B452" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C452" t="n">
         <v>1</v>
       </c>
       <c r="D452" t="n">
-        <v>1.254070322086232e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E452" t="n">
         <v>100</v>
@@ -9485,13 +9485,13 @@
         <v>451</v>
       </c>
       <c r="B453" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C453" t="n">
         <v>1</v>
       </c>
       <c r="D453" t="n">
-        <v>1.254070322086232e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E453" t="n">
         <v>100</v>
@@ -9505,13 +9505,13 @@
         <v>452</v>
       </c>
       <c r="B454" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C454" t="n">
         <v>1</v>
       </c>
       <c r="D454" t="n">
-        <v>1.254070322086232e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E454" t="n">
         <v>100</v>
@@ -9525,13 +9525,13 @@
         <v>453</v>
       </c>
       <c r="B455" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C455" t="n">
         <v>1</v>
       </c>
       <c r="D455" t="n">
-        <v>1.254070322086232e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E455" t="n">
         <v>100</v>
@@ -9545,13 +9545,13 @@
         <v>454</v>
       </c>
       <c r="B456" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C456" t="n">
         <v>1</v>
       </c>
       <c r="D456" t="n">
-        <v>1.254070322086232e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E456" t="n">
         <v>100</v>
@@ -9565,13 +9565,13 @@
         <v>455</v>
       </c>
       <c r="B457" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C457" t="n">
         <v>1</v>
       </c>
       <c r="D457" t="n">
-        <v>1.254070322086232e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E457" t="n">
         <v>100</v>
@@ -9585,13 +9585,13 @@
         <v>456</v>
       </c>
       <c r="B458" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C458" t="n">
         <v>1</v>
       </c>
       <c r="D458" t="n">
-        <v>1.254070322086232e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E458" t="n">
         <v>100</v>
@@ -9605,13 +9605,13 @@
         <v>457</v>
       </c>
       <c r="B459" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C459" t="n">
         <v>1</v>
       </c>
       <c r="D459" t="n">
-        <v>1.254070322086232e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E459" t="n">
         <v>100</v>
@@ -9625,13 +9625,13 @@
         <v>458</v>
       </c>
       <c r="B460" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C460" t="n">
         <v>1</v>
       </c>
       <c r="D460" t="n">
-        <v>1.254070322086232e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E460" t="n">
         <v>100</v>
@@ -9645,13 +9645,13 @@
         <v>459</v>
       </c>
       <c r="B461" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C461" t="n">
         <v>1</v>
       </c>
       <c r="D461" t="n">
-        <v>1.254070322086232e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E461" t="n">
         <v>100</v>
@@ -9665,13 +9665,13 @@
         <v>460</v>
       </c>
       <c r="B462" t="n">
-        <v>56</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C462" t="n">
         <v>1</v>
       </c>
       <c r="D462" t="n">
-        <v>1.254070322086232e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E462" t="n">
         <v>100</v>
@@ -9685,13 +9685,13 @@
         <v>461</v>
       </c>
       <c r="B463" t="n">
-        <v>55.2</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C463" t="n">
         <v>1</v>
       </c>
       <c r="D463" t="n">
-        <v>1.175619956332174e-08</v>
+        <v>1.433378936389457e-09</v>
       </c>
       <c r="E463" t="n">
         <v>100</v>
@@ -9705,13 +9705,13 @@
         <v>462</v>
       </c>
       <c r="B464" t="n">
-        <v>55.2</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C464" t="n">
         <v>1</v>
       </c>
       <c r="D464" t="n">
-        <v>1.175619956332174e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E464" t="n">
         <v>100</v>
@@ -9725,13 +9725,13 @@
         <v>463</v>
       </c>
       <c r="B465" t="n">
-        <v>55.2</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C465" t="n">
         <v>1</v>
       </c>
       <c r="D465" t="n">
-        <v>1.175619956332174e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E465" t="n">
         <v>100</v>
@@ -9745,13 +9745,13 @@
         <v>464</v>
       </c>
       <c r="B466" t="n">
-        <v>55.2</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C466" t="n">
         <v>1</v>
       </c>
       <c r="D466" t="n">
-        <v>1.175619956332174e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E466" t="n">
         <v>100</v>
@@ -9765,13 +9765,13 @@
         <v>465</v>
       </c>
       <c r="B467" t="n">
-        <v>55.2</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C467" t="n">
         <v>1</v>
       </c>
       <c r="D467" t="n">
-        <v>1.175619956332174e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E467" t="n">
         <v>100</v>
@@ -9785,13 +9785,13 @@
         <v>466</v>
       </c>
       <c r="B468" t="n">
-        <v>55.2</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C468" t="n">
         <v>1</v>
       </c>
       <c r="D468" t="n">
-        <v>1.175619956332174e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E468" t="n">
         <v>100</v>
@@ -9805,13 +9805,13 @@
         <v>467</v>
       </c>
       <c r="B469" t="n">
-        <v>55.2</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C469" t="n">
         <v>1</v>
       </c>
       <c r="D469" t="n">
-        <v>1.175619956332174e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E469" t="n">
         <v>100</v>
@@ -9825,13 +9825,13 @@
         <v>468</v>
       </c>
       <c r="B470" t="n">
-        <v>55.2</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C470" t="n">
         <v>1</v>
       </c>
       <c r="D470" t="n">
-        <v>1.175619956332174e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E470" t="n">
         <v>100</v>
@@ -9845,13 +9845,13 @@
         <v>469</v>
       </c>
       <c r="B471" t="n">
-        <v>55.2</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C471" t="n">
         <v>1</v>
       </c>
       <c r="D471" t="n">
-        <v>1.175619956332174e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E471" t="n">
         <v>100</v>
@@ -9865,13 +9865,13 @@
         <v>470</v>
       </c>
       <c r="B472" t="n">
-        <v>55.2</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C472" t="n">
         <v>1</v>
       </c>
       <c r="D472" t="n">
-        <v>1.175619956332174e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E472" t="n">
         <v>100</v>
@@ -9885,13 +9885,13 @@
         <v>471</v>
       </c>
       <c r="B473" t="n">
-        <v>55.2</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C473" t="n">
         <v>1</v>
       </c>
       <c r="D473" t="n">
-        <v>1.085875172942678e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E473" t="n">
         <v>100</v>
@@ -9905,13 +9905,13 @@
         <v>472</v>
       </c>
       <c r="B474" t="n">
-        <v>55.2</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C474" t="n">
         <v>1</v>
       </c>
       <c r="D474" t="n">
-        <v>1.085875172942678e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E474" t="n">
         <v>100</v>
@@ -9925,13 +9925,13 @@
         <v>473</v>
       </c>
       <c r="B475" t="n">
-        <v>55.2</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C475" t="n">
         <v>1</v>
       </c>
       <c r="D475" t="n">
-        <v>1.085875172942678e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E475" t="n">
         <v>100</v>
@@ -9945,13 +9945,13 @@
         <v>474</v>
       </c>
       <c r="B476" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C476" t="n">
         <v>1</v>
       </c>
       <c r="D476" t="n">
-        <v>1.085875172942678e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E476" t="n">
         <v>100</v>
@@ -9965,13 +9965,13 @@
         <v>475</v>
       </c>
       <c r="B477" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C477" t="n">
         <v>1</v>
       </c>
       <c r="D477" t="n">
-        <v>1.085875172942678e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E477" t="n">
         <v>100</v>
@@ -9985,13 +9985,13 @@
         <v>476</v>
       </c>
       <c r="B478" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C478" t="n">
         <v>1</v>
       </c>
       <c r="D478" t="n">
-        <v>1.085875172942678e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E478" t="n">
         <v>100</v>
@@ -10005,13 +10005,13 @@
         <v>477</v>
       </c>
       <c r="B479" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C479" t="n">
         <v>1</v>
       </c>
       <c r="D479" t="n">
-        <v>1.085875172942678e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E479" t="n">
         <v>100</v>
@@ -10025,13 +10025,13 @@
         <v>478</v>
       </c>
       <c r="B480" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C480" t="n">
         <v>1</v>
       </c>
       <c r="D480" t="n">
-        <v>1.085875172942678e-08</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E480" t="n">
         <v>100</v>
@@ -10045,13 +10045,13 @@
         <v>479</v>
       </c>
       <c r="B481" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C481" t="n">
         <v>1</v>
       </c>
       <c r="D481" t="n">
-        <v>9.294336766831113e-09</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E481" t="n">
         <v>100</v>
@@ -10065,13 +10065,13 @@
         <v>480</v>
       </c>
       <c r="B482" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C482" t="n">
         <v>1</v>
       </c>
       <c r="D482" t="n">
-        <v>9.294336766831113e-09</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E482" t="n">
         <v>100</v>
@@ -10085,13 +10085,13 @@
         <v>481</v>
       </c>
       <c r="B483" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C483" t="n">
         <v>1</v>
       </c>
       <c r="D483" t="n">
-        <v>9.294336766831113e-09</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E483" t="n">
         <v>100</v>
@@ -10105,13 +10105,13 @@
         <v>482</v>
       </c>
       <c r="B484" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C484" t="n">
         <v>1</v>
       </c>
       <c r="D484" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E484" t="n">
         <v>100</v>
@@ -10125,13 +10125,13 @@
         <v>483</v>
       </c>
       <c r="B485" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C485" t="n">
         <v>1</v>
       </c>
       <c r="D485" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E485" t="n">
         <v>100</v>
@@ -10145,13 +10145,13 @@
         <v>484</v>
       </c>
       <c r="B486" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C486" t="n">
         <v>1</v>
       </c>
       <c r="D486" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E486" t="n">
         <v>100</v>
@@ -10165,13 +10165,13 @@
         <v>485</v>
       </c>
       <c r="B487" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C487" t="n">
         <v>1</v>
       </c>
       <c r="D487" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E487" t="n">
         <v>100</v>
@@ -10185,13 +10185,13 @@
         <v>486</v>
       </c>
       <c r="B488" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C488" t="n">
         <v>1</v>
       </c>
       <c r="D488" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E488" t="n">
         <v>100</v>
@@ -10205,13 +10205,13 @@
         <v>487</v>
       </c>
       <c r="B489" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C489" t="n">
         <v>1</v>
       </c>
       <c r="D489" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E489" t="n">
         <v>100</v>
@@ -10225,13 +10225,13 @@
         <v>488</v>
       </c>
       <c r="B490" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C490" t="n">
         <v>1</v>
       </c>
       <c r="D490" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E490" t="n">
         <v>100</v>
@@ -10245,13 +10245,13 @@
         <v>489</v>
       </c>
       <c r="B491" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C491" t="n">
         <v>1</v>
       </c>
       <c r="D491" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.274133498989139e-09</v>
       </c>
       <c r="E491" t="n">
         <v>100</v>
@@ -10265,13 +10265,13 @@
         <v>490</v>
       </c>
       <c r="B492" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C492" t="n">
         <v>1</v>
       </c>
       <c r="D492" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.183621452945349e-09</v>
       </c>
       <c r="E492" t="n">
         <v>100</v>
@@ -10285,13 +10285,13 @@
         <v>491</v>
       </c>
       <c r="B493" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C493" t="n">
         <v>1</v>
       </c>
       <c r="D493" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.183621452945349e-09</v>
       </c>
       <c r="E493" t="n">
         <v>100</v>
@@ -10305,13 +10305,13 @@
         <v>492</v>
       </c>
       <c r="B494" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C494" t="n">
         <v>1</v>
       </c>
       <c r="D494" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.183621452945349e-09</v>
       </c>
       <c r="E494" t="n">
         <v>100</v>
@@ -10325,13 +10325,13 @@
         <v>493</v>
       </c>
       <c r="B495" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C495" t="n">
         <v>1</v>
       </c>
       <c r="D495" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.183621452945349e-09</v>
       </c>
       <c r="E495" t="n">
         <v>100</v>
@@ -10345,13 +10345,13 @@
         <v>494</v>
       </c>
       <c r="B496" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C496" t="n">
         <v>1</v>
       </c>
       <c r="D496" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.183621452945349e-09</v>
       </c>
       <c r="E496" t="n">
         <v>100</v>
@@ -10365,13 +10365,13 @@
         <v>495</v>
       </c>
       <c r="B497" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C497" t="n">
         <v>1</v>
       </c>
       <c r="D497" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.183621452945349e-09</v>
       </c>
       <c r="E497" t="n">
         <v>100</v>
@@ -10385,13 +10385,13 @@
         <v>496</v>
       </c>
       <c r="B498" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C498" t="n">
         <v>1</v>
       </c>
       <c r="D498" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.183621452945349e-09</v>
       </c>
       <c r="E498" t="n">
         <v>100</v>
@@ -10405,13 +10405,13 @@
         <v>497</v>
       </c>
       <c r="B499" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C499" t="n">
         <v>1</v>
       </c>
       <c r="D499" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.183621452945349e-09</v>
       </c>
       <c r="E499" t="n">
         <v>100</v>
@@ -10425,13 +10425,13 @@
         <v>498</v>
       </c>
       <c r="B500" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C500" t="n">
         <v>1</v>
       </c>
       <c r="D500" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.183621452945349e-09</v>
       </c>
       <c r="E500" t="n">
         <v>100</v>
@@ -10445,13 +10445,13 @@
         <v>499</v>
       </c>
       <c r="B501" t="n">
-        <v>54.40000000000001</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="C501" t="n">
         <v>1</v>
       </c>
       <c r="D501" t="n">
-        <v>9.116529126098811e-09</v>
+        <v>1.183621452945349e-09</v>
       </c>
       <c r="E501" t="n">
         <v>100</v>

--- a/results/tables/NSGA-II收敛曲线数据.xlsx
+++ b/results/tables/NSGA-II收敛曲线数据.xlsx
@@ -465,19 +465,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>720</v>
+        <v>569.2</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.52757981448728e-06</v>
+        <v>7.797993134887886e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -485,19 +485,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>640.4</v>
+        <v>472</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.52757981448728e-06</v>
+        <v>7.797993134887886e-06</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -505,19 +505,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>640.4</v>
+        <v>450</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.52757981448728e-06</v>
+        <v>6.691582398705945e-06</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -525,19 +525,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>613.6</v>
+        <v>450</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.57323545212612e-06</v>
+        <v>6.392635378826699e-06</v>
       </c>
       <c r="E5" t="n">
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -545,19 +545,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>613.6</v>
+        <v>433.6</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.195127106333026e-06</v>
+        <v>4.891131014752381e-06</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +565,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>547.6</v>
+        <v>352.8</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.195127106333026e-06</v>
+        <v>4.891131014752381e-06</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -585,19 +585,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>476.4</v>
+        <v>352.8</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.471897504185953e-06</v>
+        <v>3.809989140259977e-06</v>
       </c>
       <c r="E8" t="n">
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -605,19 +605,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>437.6</v>
+        <v>337.2</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.266807171719807e-06</v>
+        <v>3.809989140259977e-06</v>
       </c>
       <c r="E9" t="n">
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -625,19 +625,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>409.6</v>
+        <v>309.2</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.082125089661989e-06</v>
+        <v>3.345280248258281e-06</v>
       </c>
       <c r="E10" t="n">
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -645,19 +645,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>404</v>
+        <v>309.2</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.082125089661989e-06</v>
+        <v>3.345280248258281e-06</v>
       </c>
       <c r="E11" t="n">
         <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -665,19 +665,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>404</v>
+        <v>309.2</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.009671983906521e-06</v>
+        <v>2.839667670565944e-06</v>
       </c>
       <c r="E12" t="n">
         <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -685,19 +685,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>387.2</v>
+        <v>309.2</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.279397308833682e-07</v>
+        <v>2.839667670565944e-06</v>
       </c>
       <c r="E13" t="n">
         <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -705,19 +705,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>387.2</v>
+        <v>290</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.279397308833682e-07</v>
+        <v>2.839667670565944e-06</v>
       </c>
       <c r="E14" t="n">
         <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -725,19 +725,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>308.8</v>
+        <v>288.4</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.044692053261508e-07</v>
+        <v>2.792005624464202e-06</v>
       </c>
       <c r="E15" t="n">
         <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -745,19 +745,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>307.6</v>
+        <v>286.8</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.441628669664438e-07</v>
+        <v>2.287078172509298e-06</v>
       </c>
       <c r="E16" t="n">
         <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -765,19 +765,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>306.4</v>
+        <v>286.8</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.441628669664438e-07</v>
+        <v>2.114926663462821e-06</v>
       </c>
       <c r="E17" t="n">
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -785,19 +785,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>304</v>
+        <v>256.4</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.397055178436672e-07</v>
+        <v>1.618154822167502e-06</v>
       </c>
       <c r="E18" t="n">
         <v>100</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -805,19 +805,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>304</v>
+        <v>247.6</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>5.044189592783209e-07</v>
+        <v>1.527545549847799e-06</v>
       </c>
       <c r="E19" t="n">
         <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -825,19 +825,19 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>234.4</v>
+        <v>247.6</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.135265505844914e-07</v>
+        <v>1.485525042415912e-06</v>
       </c>
       <c r="E20" t="n">
         <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -845,19 +845,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>234.4</v>
+        <v>227.2</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.135265505844914e-07</v>
+        <v>1.47985645392389e-06</v>
       </c>
       <c r="E21" t="n">
         <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
@@ -865,19 +865,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>234.4</v>
+        <v>227.2</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3.023214077983883e-07</v>
+        <v>1.47985645392389e-06</v>
       </c>
       <c r="E22" t="n">
         <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
@@ -885,19 +885,19 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>232</v>
+        <v>227.2</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.43875738348402e-07</v>
+        <v>1.213169032719108e-06</v>
       </c>
       <c r="E23" t="n">
         <v>100</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">
@@ -905,19 +905,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>232</v>
+        <v>227.2</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.433491484122306e-07</v>
+        <v>1.154261141240873e-06</v>
       </c>
       <c r="E24" t="n">
         <v>100</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25">
@@ -925,19 +925,19 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>225.6</v>
+        <v>183.2</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.375765677362542e-07</v>
+        <v>1.035065445580918e-06</v>
       </c>
       <c r="E25" t="n">
         <v>100</v>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26">
@@ -945,19 +945,19 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>213.6</v>
+        <v>182</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2.123197052013852e-07</v>
+        <v>9.31751099136083e-07</v>
       </c>
       <c r="E26" t="n">
         <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27">
@@ -965,19 +965,19 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>213.6</v>
+        <v>182</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1.44247253917167e-07</v>
+        <v>8.603020421276528e-07</v>
       </c>
       <c r="E27" t="n">
         <v>100</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28">
@@ -985,19 +985,19 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>209.6</v>
+        <v>182</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1.44247253917167e-07</v>
+        <v>8.603020421276528e-07</v>
       </c>
       <c r="E28" t="n">
         <v>100</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
@@ -1005,19 +1005,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>206.4</v>
+        <v>182</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1.128053844568153e-07</v>
+        <v>8.603020421276528e-07</v>
       </c>
       <c r="E29" t="n">
         <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30">
@@ -1025,19 +1025,19 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>206.4</v>
+        <v>182</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1.128053844568153e-07</v>
+        <v>8.596480971041227e-07</v>
       </c>
       <c r="E30" t="n">
         <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31">
@@ -1045,19 +1045,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>176.8</v>
+        <v>182</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1.063961123608777e-07</v>
+        <v>7.873438463242397e-07</v>
       </c>
       <c r="E31" t="n">
         <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32">
@@ -1065,19 +1065,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>176.8</v>
+        <v>160.8</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>1.063961123608777e-07</v>
+        <v>7.873438463242397e-07</v>
       </c>
       <c r="E32" t="n">
         <v>100</v>
       </c>
       <c r="F32" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33">
@@ -1085,19 +1085,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>176.8</v>
+        <v>160.8</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>1.063961123608777e-07</v>
+        <v>7.873438463242397e-07</v>
       </c>
       <c r="E33" t="n">
         <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>14</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34">
@@ -1105,19 +1105,19 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>176.8</v>
+        <v>152</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>8.587000618987618e-08</v>
+        <v>7.15080761878153e-07</v>
       </c>
       <c r="E34" t="n">
         <v>100</v>
       </c>
       <c r="F34" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35">
@@ -1125,19 +1125,19 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>176.8</v>
+        <v>136</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>8.399519212444371e-08</v>
+        <v>7.15080761878153e-07</v>
       </c>
       <c r="E35" t="n">
         <v>100</v>
       </c>
       <c r="F35" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36">
@@ -1145,19 +1145,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>162.8</v>
+        <v>136</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>6.719094292343583e-08</v>
+        <v>7.15080761878153e-07</v>
       </c>
       <c r="E36" t="n">
         <v>100</v>
       </c>
       <c r="F36" t="n">
-        <v>12</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37">
@@ -1165,19 +1165,19 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>162.8</v>
+        <v>136</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>3.597703584219106e-08</v>
+        <v>5.515277938513438e-07</v>
       </c>
       <c r="E37" t="n">
         <v>100</v>
       </c>
       <c r="F37" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38">
@@ -1185,19 +1185,19 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>162.8</v>
+        <v>133.6</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>3.597628196986462e-08</v>
+        <v>5.497085990036402e-07</v>
       </c>
       <c r="E38" t="n">
         <v>100</v>
       </c>
       <c r="F38" t="n">
-        <v>13</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39">
@@ -1205,19 +1205,19 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>162.8</v>
+        <v>133.6</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>3.54485911262395e-08</v>
+        <v>5.497085990036402e-07</v>
       </c>
       <c r="E39" t="n">
         <v>100</v>
       </c>
       <c r="F39" t="n">
-        <v>17</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40">
@@ -1225,19 +1225,19 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>155.2</v>
+        <v>133.6</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>3.54485911262395e-08</v>
+        <v>5.467224135032937e-07</v>
       </c>
       <c r="E40" t="n">
         <v>100</v>
       </c>
       <c r="F40" t="n">
-        <v>21</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41">
@@ -1245,19 +1245,19 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>155.2</v>
+        <v>133.6</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>3.54485911262395e-08</v>
+        <v>5.467224135032937e-07</v>
       </c>
       <c r="E41" t="n">
         <v>100</v>
       </c>
       <c r="F41" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42">
@@ -1265,19 +1265,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>152</v>
+        <v>133.6</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>3.54485911262395e-08</v>
+        <v>5.379030046172804e-07</v>
       </c>
       <c r="E42" t="n">
         <v>100</v>
       </c>
       <c r="F42" t="n">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43">
@@ -1285,19 +1285,19 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>148.8</v>
+        <v>132.8</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>3.54485911262395e-08</v>
+        <v>5.379030046172804e-07</v>
       </c>
       <c r="E43" t="n">
         <v>100</v>
       </c>
       <c r="F43" t="n">
-        <v>27</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44">
@@ -1305,19 +1305,19 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>148.8</v>
+        <v>132.8</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>3.278501778554797e-08</v>
+        <v>5.379030046172804e-07</v>
       </c>
       <c r="E44" t="n">
         <v>100</v>
       </c>
       <c r="F44" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
@@ -1325,19 +1325,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>146.8</v>
+        <v>132.8</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>3.278501778554797e-08</v>
+        <v>5.015506200305298e-07</v>
       </c>
       <c r="E45" t="n">
         <v>100</v>
       </c>
       <c r="F45" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
@@ -1345,19 +1345,19 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>146.8</v>
+        <v>124</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>3.278501778554797e-08</v>
+        <v>4.977583532653162e-07</v>
       </c>
       <c r="E46" t="n">
         <v>100</v>
       </c>
       <c r="F46" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47">
@@ -1365,19 +1365,19 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>122.4</v>
+        <v>123.2</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>3.278501778554797e-08</v>
+        <v>4.977583532653162e-07</v>
       </c>
       <c r="E47" t="n">
         <v>100</v>
       </c>
       <c r="F47" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
@@ -1385,19 +1385,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>122.4</v>
+        <v>123.2</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>3.253169665327161e-08</v>
+        <v>4.745732319719034e-07</v>
       </c>
       <c r="E48" t="n">
         <v>100</v>
       </c>
       <c r="F48" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49">
@@ -1405,19 +1405,19 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>122.4</v>
+        <v>123.2</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>3.251384413961448e-08</v>
+        <v>4.745732319719034e-07</v>
       </c>
       <c r="E49" t="n">
         <v>100</v>
       </c>
       <c r="F49" t="n">
-        <v>19</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50">
@@ -1431,13 +1431,13 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>3.076892824447345e-08</v>
+        <v>4.745732319719034e-07</v>
       </c>
       <c r="E50" t="n">
         <v>100</v>
       </c>
       <c r="F50" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51">
@@ -1451,13 +1451,13 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>3.076892824447345e-08</v>
+        <v>4.714514125571499e-07</v>
       </c>
       <c r="E51" t="n">
         <v>100</v>
       </c>
       <c r="F51" t="n">
-        <v>26</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52">
@@ -1465,19 +1465,19 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>118.4</v>
+        <v>120</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>3.076892824447345e-08</v>
+        <v>4.714514125571499e-07</v>
       </c>
       <c r="E52" t="n">
         <v>100</v>
       </c>
       <c r="F52" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53">
@@ -1485,19 +1485,19 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>118.4</v>
+        <v>120</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>2.869806251667129e-08</v>
+        <v>4.714514125571499e-07</v>
       </c>
       <c r="E53" t="n">
         <v>100</v>
       </c>
       <c r="F53" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
@@ -1505,19 +1505,19 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>118.4</v>
+        <v>120</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>2.869806251667129e-08</v>
+        <v>4.45411246433355e-07</v>
       </c>
       <c r="E54" t="n">
         <v>100</v>
       </c>
       <c r="F54" t="n">
-        <v>29</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55">
@@ -1525,19 +1525,19 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>112.4</v>
+        <v>112</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>2.621347007927886e-08</v>
+        <v>4.45411246433355e-07</v>
       </c>
       <c r="E55" t="n">
         <v>100</v>
       </c>
       <c r="F55" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56">
@@ -1545,19 +1545,19 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>110.8</v>
+        <v>110.4</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>2.599017697217961e-08</v>
+        <v>4.441467522333997e-07</v>
       </c>
       <c r="E56" t="n">
         <v>100</v>
       </c>
       <c r="F56" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57">
@@ -1565,19 +1565,19 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>110.8</v>
+        <v>110.4</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>2.599017697217961e-08</v>
+        <v>4.441467522333997e-07</v>
       </c>
       <c r="E57" t="n">
         <v>100</v>
       </c>
       <c r="F57" t="n">
-        <v>41</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58">
@@ -1585,19 +1585,19 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>107.2</v>
+        <v>110.4</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>2.369202573732287e-08</v>
+        <v>3.554121191627374e-07</v>
       </c>
       <c r="E58" t="n">
         <v>100</v>
       </c>
       <c r="F58" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59">
@@ -1605,19 +1605,19 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>107.2</v>
+        <v>110.4</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>2.369202573732287e-08</v>
+        <v>3.554121191627374e-07</v>
       </c>
       <c r="E59" t="n">
         <v>100</v>
       </c>
       <c r="F59" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60">
@@ -1625,19 +1625,19 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>107.2</v>
+        <v>110.4</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>2.369202573732287e-08</v>
+        <v>3.214584187580269e-07</v>
       </c>
       <c r="E60" t="n">
         <v>100</v>
       </c>
       <c r="F60" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61">
@@ -1645,19 +1645,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>107.2</v>
+        <v>110.4</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>2.314577505056094e-08</v>
+        <v>3.214584187580269e-07</v>
       </c>
       <c r="E61" t="n">
         <v>100</v>
       </c>
       <c r="F61" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62">
@@ -1665,19 +1665,19 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>107.2</v>
+        <v>110.4</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>2.314577505056094e-08</v>
+        <v>3.214584187580269e-07</v>
       </c>
       <c r="E62" t="n">
         <v>100</v>
       </c>
       <c r="F62" t="n">
-        <v>47</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63">
@@ -1685,19 +1685,19 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>107.2</v>
+        <v>110.4</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>2.070911041437778e-08</v>
+        <v>3.214584187580269e-07</v>
       </c>
       <c r="E63" t="n">
         <v>100</v>
       </c>
       <c r="F63" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
@@ -1705,19 +1705,19 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>107.2</v>
+        <v>110.4</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>2.070911041437778e-08</v>
+        <v>3.214584187580269e-07</v>
       </c>
       <c r="E64" t="n">
         <v>100</v>
       </c>
       <c r="F64" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65">
@@ -1725,19 +1725,19 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>107.2</v>
+        <v>100</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>2.070911041437778e-08</v>
+        <v>3.214584187580269e-07</v>
       </c>
       <c r="E65" t="n">
         <v>100</v>
       </c>
       <c r="F65" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66">
@@ -1745,19 +1745,19 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>2.070911041437778e-08</v>
+        <v>3.214584187580269e-07</v>
       </c>
       <c r="E66" t="n">
         <v>100</v>
       </c>
       <c r="F66" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67">
@@ -1765,19 +1765,19 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>2.070911041437778e-08</v>
+        <v>3.214584187580269e-07</v>
       </c>
       <c r="E67" t="n">
         <v>100</v>
       </c>
       <c r="F67" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68">
@@ -1785,19 +1785,19 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>2.070911041437778e-08</v>
+        <v>3.214584187580269e-07</v>
       </c>
       <c r="E68" t="n">
         <v>100</v>
       </c>
       <c r="F68" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69">
@@ -1805,19 +1805,19 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>2.070911041437778e-08</v>
+        <v>3.214584187580269e-07</v>
       </c>
       <c r="E69" t="n">
         <v>100</v>
       </c>
       <c r="F69" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70">
@@ -1825,19 +1825,19 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>97.60000000000001</v>
+        <v>96.80000000000001</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>2.070911041437778e-08</v>
+        <v>3.214584187580269e-07</v>
       </c>
       <c r="E70" t="n">
         <v>100</v>
       </c>
       <c r="F70" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71">
@@ -1845,19 +1845,19 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>94.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>2.047238052127635e-08</v>
+        <v>3.214584187580269e-07</v>
       </c>
       <c r="E71" t="n">
         <v>100</v>
       </c>
       <c r="F71" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72">
@@ -1865,19 +1865,19 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>94.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>1.715010907710132e-08</v>
+        <v>2.986469355464858e-07</v>
       </c>
       <c r="E72" t="n">
         <v>100</v>
       </c>
       <c r="F72" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73">
@@ -1885,19 +1885,19 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>94.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>1.715010907710132e-08</v>
+        <v>2.986469355464858e-07</v>
       </c>
       <c r="E73" t="n">
         <v>100</v>
       </c>
       <c r="F73" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74">
@@ -1905,19 +1905,19 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>94.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>1.715010907710132e-08</v>
+        <v>2.986469355464858e-07</v>
       </c>
       <c r="E74" t="n">
         <v>100</v>
       </c>
       <c r="F74" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75">
@@ -1925,13 +1925,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>93.60000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>1.715010907710132e-08</v>
+        <v>2.970555843064157e-07</v>
       </c>
       <c r="E75" t="n">
         <v>100</v>
@@ -1945,13 +1945,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>93.60000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>1.715010907710132e-08</v>
+        <v>2.955626061726577e-07</v>
       </c>
       <c r="E76" t="n">
         <v>100</v>
@@ -1965,13 +1965,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>93.60000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>1.715010907710132e-08</v>
+        <v>2.955626061726577e-07</v>
       </c>
       <c r="E77" t="n">
         <v>100</v>
@@ -1985,19 +1985,19 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>93.60000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>1.715010907710132e-08</v>
+        <v>2.95355553323234e-07</v>
       </c>
       <c r="E78" t="n">
         <v>100</v>
       </c>
       <c r="F78" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79">
@@ -2005,19 +2005,19 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>93.60000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>1.7000334739631e-08</v>
+        <v>2.95355553323234e-07</v>
       </c>
       <c r="E79" t="n">
         <v>100</v>
       </c>
       <c r="F79" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80">
@@ -2025,19 +2025,19 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>93.60000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>1.218520298075702e-08</v>
+        <v>2.95355553323234e-07</v>
       </c>
       <c r="E80" t="n">
         <v>100</v>
       </c>
       <c r="F80" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81">
@@ -2045,19 +2045,19 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>93.60000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>1.218520298075702e-08</v>
+        <v>2.95355553323234e-07</v>
       </c>
       <c r="E81" t="n">
         <v>100</v>
       </c>
       <c r="F81" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82">
@@ -2065,19 +2065,19 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>93.60000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>1.218520298075702e-08</v>
+        <v>2.387807995046099e-07</v>
       </c>
       <c r="E82" t="n">
         <v>100</v>
       </c>
       <c r="F82" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="83">
@@ -2085,19 +2085,19 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>93.60000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1.218520298075702e-08</v>
+        <v>2.385135721041509e-07</v>
       </c>
       <c r="E83" t="n">
         <v>100</v>
       </c>
       <c r="F83" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84">
@@ -2105,19 +2105,19 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>93.60000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>1.218520298075702e-08</v>
+        <v>1.399780405022426e-07</v>
       </c>
       <c r="E84" t="n">
         <v>100</v>
       </c>
       <c r="F84" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85">
@@ -2125,19 +2125,19 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>93.60000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>1.218520298075702e-08</v>
+        <v>1.399780405022426e-07</v>
       </c>
       <c r="E85" t="n">
         <v>100</v>
       </c>
       <c r="F85" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="86">
@@ -2145,19 +2145,19 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>88</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>1.218520298075702e-08</v>
+        <v>1.399780405022426e-07</v>
       </c>
       <c r="E86" t="n">
         <v>100</v>
       </c>
       <c r="F86" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87">
@@ -2165,19 +2165,19 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>88</v>
+        <v>81.60000000000001</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>1.218520298075702e-08</v>
+        <v>1.24138057801381e-07</v>
       </c>
       <c r="E87" t="n">
         <v>100</v>
       </c>
       <c r="F87" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88">
@@ -2185,19 +2185,19 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>88</v>
+        <v>81.60000000000001</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>1.218520298075702e-08</v>
+        <v>1.24138057801381e-07</v>
       </c>
       <c r="E88" t="n">
         <v>100</v>
       </c>
       <c r="F88" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89">
@@ -2205,19 +2205,19 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>88</v>
+        <v>81.60000000000001</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>1.218520298075702e-08</v>
+        <v>1.24138057801381e-07</v>
       </c>
       <c r="E89" t="n">
         <v>100</v>
       </c>
       <c r="F89" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90">
@@ -2225,13 +2225,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>88</v>
+        <v>81.60000000000001</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>1.061321176722244e-08</v>
+        <v>1.105854665604966e-07</v>
       </c>
       <c r="E90" t="n">
         <v>100</v>
@@ -2245,13 +2245,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>87.2</v>
+        <v>81.60000000000001</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1.061321176722244e-08</v>
+        <v>1.105854665604966e-07</v>
       </c>
       <c r="E91" t="n">
         <v>100</v>
@@ -2265,19 +2265,19 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>87.2</v>
+        <v>81.60000000000001</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1.061321176722244e-08</v>
+        <v>1.105854665604966e-07</v>
       </c>
       <c r="E92" t="n">
         <v>100</v>
       </c>
       <c r="F92" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93">
@@ -2285,13 +2285,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>87.2</v>
+        <v>81.60000000000001</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>1.061321176722244e-08</v>
+        <v>1.105854665604966e-07</v>
       </c>
       <c r="E93" t="n">
         <v>100</v>
@@ -2305,13 +2305,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>87.2</v>
+        <v>81.60000000000001</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>1.041578197360177e-08</v>
+        <v>1.101014160548989e-07</v>
       </c>
       <c r="E94" t="n">
         <v>100</v>
@@ -2325,13 +2325,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>87.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1.041578197360177e-08</v>
+        <v>1.101014160548989e-07</v>
       </c>
       <c r="E95" t="n">
         <v>100</v>
@@ -2345,13 +2345,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>87.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>1.041578197360177e-08</v>
+        <v>1.101014160548989e-07</v>
       </c>
       <c r="E96" t="n">
         <v>100</v>
@@ -2365,13 +2365,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>87.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>1.041578197360177e-08</v>
+        <v>9.743852210063326e-08</v>
       </c>
       <c r="E97" t="n">
         <v>100</v>
@@ -2385,13 +2385,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>86.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>1.041578197360177e-08</v>
+        <v>9.743852210063326e-08</v>
       </c>
       <c r="E98" t="n">
         <v>100</v>
@@ -2405,13 +2405,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>86.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>1.041578197360177e-08</v>
+        <v>9.743852210063326e-08</v>
       </c>
       <c r="E99" t="n">
         <v>100</v>
@@ -2425,19 +2425,19 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>86.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>1.041578197360177e-08</v>
+        <v>9.743852210063326e-08</v>
       </c>
       <c r="E100" t="n">
         <v>100</v>
       </c>
       <c r="F100" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101">
@@ -2445,19 +2445,19 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>84.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>1.041578197360177e-08</v>
+        <v>9.743852210063326e-08</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
       </c>
       <c r="F101" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102">
@@ -2465,19 +2465,19 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>84.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>1.041578197360177e-08</v>
+        <v>9.743852210063326e-08</v>
       </c>
       <c r="E102" t="n">
         <v>100</v>
       </c>
       <c r="F102" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103">
@@ -2485,19 +2485,19 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>84.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>1.041578197360177e-08</v>
+        <v>9.68071006517393e-08</v>
       </c>
       <c r="E103" t="n">
         <v>100</v>
       </c>
       <c r="F103" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104">
@@ -2505,19 +2505,19 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>84.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>1.041578197360177e-08</v>
+        <v>9.68071006517393e-08</v>
       </c>
       <c r="E104" t="n">
         <v>100</v>
       </c>
       <c r="F104" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105">
@@ -2525,19 +2525,19 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>84.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C105" t="n">
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>1.041578197360177e-08</v>
+        <v>9.68071006517393e-08</v>
       </c>
       <c r="E105" t="n">
         <v>100</v>
       </c>
       <c r="F105" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106">
@@ -2545,19 +2545,19 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>84.8</v>
+        <v>77.60000000000001</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>1.041578197360177e-08</v>
+        <v>9.68071006517393e-08</v>
       </c>
       <c r="E106" t="n">
         <v>100</v>
       </c>
       <c r="F106" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107">
@@ -2565,19 +2565,19 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>82.40000000000001</v>
+        <v>77.60000000000001</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>9.740923048290284e-09</v>
+        <v>9.68071006517393e-08</v>
       </c>
       <c r="E107" t="n">
         <v>100</v>
       </c>
       <c r="F107" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108">
@@ -2585,19 +2585,19 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>82.40000000000001</v>
+        <v>77.60000000000001</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>9.740923048290284e-09</v>
+        <v>9.68071006517393e-08</v>
       </c>
       <c r="E108" t="n">
         <v>100</v>
       </c>
       <c r="F108" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109">
@@ -2605,13 +2605,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>82.40000000000001</v>
+        <v>77.60000000000001</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>9.740923048290284e-09</v>
+        <v>9.68071006517393e-08</v>
       </c>
       <c r="E109" t="n">
         <v>100</v>
@@ -2625,13 +2625,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>82.40000000000001</v>
+        <v>77.60000000000001</v>
       </c>
       <c r="C110" t="n">
         <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>9.740923048290284e-09</v>
+        <v>9.68071006517393e-08</v>
       </c>
       <c r="E110" t="n">
         <v>100</v>
@@ -2645,13 +2645,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>82.40000000000001</v>
+        <v>77.60000000000001</v>
       </c>
       <c r="C111" t="n">
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>9.740923048290284e-09</v>
+        <v>9.611143526282454e-08</v>
       </c>
       <c r="E111" t="n">
         <v>100</v>
@@ -2665,13 +2665,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>82.40000000000001</v>
+        <v>77.60000000000001</v>
       </c>
       <c r="C112" t="n">
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>9.61394557849437e-09</v>
+        <v>9.611143526282454e-08</v>
       </c>
       <c r="E112" t="n">
         <v>100</v>
@@ -2685,13 +2685,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>78.40000000000001</v>
+        <v>77.60000000000001</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>9.61394557849437e-09</v>
+        <v>8.933592646132085e-08</v>
       </c>
       <c r="E113" t="n">
         <v>100</v>
@@ -2705,13 +2705,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>70.40000000000001</v>
+        <v>77.60000000000001</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>9.61394557849437e-09</v>
+        <v>8.933592646132085e-08</v>
       </c>
       <c r="E114" t="n">
         <v>100</v>
@@ -2725,13 +2725,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>70.40000000000001</v>
+        <v>76.80000000000001</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>9.61394557849437e-09</v>
+        <v>8.933592646132085e-08</v>
       </c>
       <c r="E115" t="n">
         <v>100</v>
@@ -2745,13 +2745,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>70.40000000000001</v>
+        <v>76.80000000000001</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>9.61394557849437e-09</v>
+        <v>8.933592646132085e-08</v>
       </c>
       <c r="E116" t="n">
         <v>100</v>
@@ -2765,13 +2765,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>70.40000000000001</v>
+        <v>76.80000000000001</v>
       </c>
       <c r="C117" t="n">
         <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>9.61394557849437e-09</v>
+        <v>8.933592646132085e-08</v>
       </c>
       <c r="E117" t="n">
         <v>100</v>
@@ -2785,13 +2785,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>70.40000000000001</v>
+        <v>76.80000000000001</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>9.61394557849437e-09</v>
+        <v>8.933592646132085e-08</v>
       </c>
       <c r="E118" t="n">
         <v>100</v>
@@ -2805,13 +2805,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>70.40000000000001</v>
+        <v>76.80000000000001</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>9.61394557849437e-09</v>
+        <v>8.933592646132085e-08</v>
       </c>
       <c r="E119" t="n">
         <v>100</v>
@@ -2825,13 +2825,13 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>70.40000000000001</v>
+        <v>76.80000000000001</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>9.61394557849437e-09</v>
+        <v>8.933592646132085e-08</v>
       </c>
       <c r="E120" t="n">
         <v>100</v>
@@ -2845,13 +2845,13 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>70.40000000000001</v>
+        <v>76.80000000000001</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>9.61394557849437e-09</v>
+        <v>8.25219436288397e-08</v>
       </c>
       <c r="E121" t="n">
         <v>100</v>
@@ -2865,13 +2865,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>70.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="C122" t="n">
         <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>9.61394557849437e-09</v>
+        <v>8.175492182109784e-08</v>
       </c>
       <c r="E122" t="n">
         <v>100</v>
@@ -2885,13 +2885,13 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>70.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>8.588180658313927e-09</v>
+        <v>8.175492182109784e-08</v>
       </c>
       <c r="E123" t="n">
         <v>100</v>
@@ -2905,13 +2905,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>69.60000000000001</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>8.588180658313927e-09</v>
+        <v>8.175492182109784e-08</v>
       </c>
       <c r="E124" t="n">
         <v>100</v>
@@ -2925,13 +2925,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>65.60000000000001</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>7.020497382863692e-09</v>
+        <v>8.175492182109784e-08</v>
       </c>
       <c r="E125" t="n">
         <v>100</v>
@@ -2945,13 +2945,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>65.60000000000001</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>7.020497382863692e-09</v>
+        <v>8.175492182109784e-08</v>
       </c>
       <c r="E126" t="n">
         <v>100</v>
@@ -2965,13 +2965,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>65.60000000000001</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>7.020497382863692e-09</v>
+        <v>7.923335428755631e-08</v>
       </c>
       <c r="E127" t="n">
         <v>100</v>
@@ -2985,13 +2985,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>65.60000000000001</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="C128" t="n">
         <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>7.020497382863692e-09</v>
+        <v>7.923335428755631e-08</v>
       </c>
       <c r="E128" t="n">
         <v>100</v>
@@ -3005,13 +3005,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>65.60000000000001</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>7.020497382863692e-09</v>
+        <v>7.792826093962181e-08</v>
       </c>
       <c r="E129" t="n">
         <v>100</v>
@@ -3025,13 +3025,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>65.60000000000001</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>7.020497382863692e-09</v>
+        <v>7.792826093962181e-08</v>
       </c>
       <c r="E130" t="n">
         <v>100</v>
@@ -3045,13 +3045,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>65.60000000000001</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>6.754343513682899e-09</v>
+        <v>7.792826093962181e-08</v>
       </c>
       <c r="E131" t="n">
         <v>100</v>
@@ -3065,13 +3065,13 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>65.60000000000001</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>6.754343513682899e-09</v>
+        <v>7.792826093962181e-08</v>
       </c>
       <c r="E132" t="n">
         <v>100</v>
@@ -3085,13 +3085,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>65.60000000000001</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>6.002142905139493e-09</v>
+        <v>6.826651651878448e-08</v>
       </c>
       <c r="E133" t="n">
         <v>100</v>
@@ -3105,13 +3105,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>65.60000000000001</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>5.439367358209741e-09</v>
+        <v>6.826651651878448e-08</v>
       </c>
       <c r="E134" t="n">
         <v>100</v>
@@ -3125,13 +3125,13 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>65.60000000000001</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>5.439367358209741e-09</v>
+        <v>6.826651651878448e-08</v>
       </c>
       <c r="E135" t="n">
         <v>100</v>
@@ -3145,13 +3145,13 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>65.60000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>5.439367358209741e-09</v>
+        <v>6.826651651878448e-08</v>
       </c>
       <c r="E136" t="n">
         <v>100</v>
@@ -3165,13 +3165,13 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>65.60000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>5.439367358209741e-09</v>
+        <v>6.826651651878448e-08</v>
       </c>
       <c r="E137" t="n">
         <v>100</v>
@@ -3185,13 +3185,13 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>65.60000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>5.439367358209741e-09</v>
+        <v>5.844478064335318e-08</v>
       </c>
       <c r="E138" t="n">
         <v>100</v>
@@ -3205,13 +3205,13 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>65.60000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>5.439367358209741e-09</v>
+        <v>5.844478064335318e-08</v>
       </c>
       <c r="E139" t="n">
         <v>100</v>
@@ -3225,13 +3225,13 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>65.60000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>5.439367358209741e-09</v>
+        <v>5.844478064335318e-08</v>
       </c>
       <c r="E140" t="n">
         <v>100</v>
@@ -3245,13 +3245,13 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>65.60000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>5.439367358209741e-09</v>
+        <v>5.844478064335318e-08</v>
       </c>
       <c r="E141" t="n">
         <v>100</v>
@@ -3265,13 +3265,13 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>61.6</v>
+        <v>72.8</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>5.439367358209741e-09</v>
+        <v>5.844478064335318e-08</v>
       </c>
       <c r="E142" t="n">
         <v>100</v>
@@ -3285,13 +3285,13 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>57.6</v>
+        <v>72.8</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>5.439367358209741e-09</v>
+        <v>5.844478064335318e-08</v>
       </c>
       <c r="E143" t="n">
         <v>100</v>
@@ -3305,13 +3305,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>57.6</v>
+        <v>72.8</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>5.439367358209741e-09</v>
+        <v>5.844478064335318e-08</v>
       </c>
       <c r="E144" t="n">
         <v>100</v>
@@ -3325,13 +3325,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>57.6</v>
+        <v>72.8</v>
       </c>
       <c r="C145" t="n">
         <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>5.439367358209741e-09</v>
+        <v>5.844478064335318e-08</v>
       </c>
       <c r="E145" t="n">
         <v>100</v>
@@ -3345,13 +3345,13 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>57.6</v>
+        <v>72.8</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>5.439367358209741e-09</v>
+        <v>5.844478064335318e-08</v>
       </c>
       <c r="E146" t="n">
         <v>100</v>
@@ -3365,13 +3365,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>57.6</v>
+        <v>72.8</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>5.439367358209741e-09</v>
+        <v>5.844478064335318e-08</v>
       </c>
       <c r="E147" t="n">
         <v>100</v>
@@ -3385,13 +3385,13 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>57.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>5.319615060700603e-09</v>
+        <v>5.844478064335318e-08</v>
       </c>
       <c r="E148" t="n">
         <v>100</v>
@@ -3405,13 +3405,13 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>57.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>5.101537252662204e-09</v>
+        <v>5.844478064335318e-08</v>
       </c>
       <c r="E149" t="n">
         <v>100</v>
@@ -3425,13 +3425,13 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>57.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>5.101537252662204e-09</v>
+        <v>5.844478064335318e-08</v>
       </c>
       <c r="E150" t="n">
         <v>100</v>
@@ -3445,13 +3445,13 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>57.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>4.874050229180545e-09</v>
+        <v>5.815742621568132e-08</v>
       </c>
       <c r="E151" t="n">
         <v>100</v>
@@ -3465,13 +3465,13 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>57.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>4.874050229180545e-09</v>
+        <v>5.815742621568132e-08</v>
       </c>
       <c r="E152" t="n">
         <v>100</v>
@@ -3485,13 +3485,13 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>57.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>4.874050229180545e-09</v>
+        <v>5.506875429627605e-08</v>
       </c>
       <c r="E153" t="n">
         <v>100</v>
@@ -3505,13 +3505,13 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>57.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>4.874050229180545e-09</v>
+        <v>5.506875429627605e-08</v>
       </c>
       <c r="E154" t="n">
         <v>100</v>
@@ -3525,13 +3525,13 @@
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>57.6</v>
+        <v>68.8</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>4.874050229180545e-09</v>
+        <v>5.506875429627605e-08</v>
       </c>
       <c r="E155" t="n">
         <v>100</v>
@@ -3545,13 +3545,13 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>57.6</v>
+        <v>68.8</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>4.872904996386631e-09</v>
+        <v>5.506875429627605e-08</v>
       </c>
       <c r="E156" t="n">
         <v>100</v>
@@ -3565,13 +3565,13 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>57.6</v>
+        <v>68.8</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>4.872904996386631e-09</v>
+        <v>5.506875429627605e-08</v>
       </c>
       <c r="E157" t="n">
         <v>100</v>
@@ -3585,13 +3585,13 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>57.6</v>
+        <v>68.8</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>4.70660395950877e-09</v>
+        <v>5.506875429627605e-08</v>
       </c>
       <c r="E158" t="n">
         <v>100</v>
@@ -3605,13 +3605,13 @@
         <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>57.6</v>
+        <v>68.8</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>4.384497391784858e-09</v>
+        <v>5.506875429627605e-08</v>
       </c>
       <c r="E159" t="n">
         <v>100</v>
@@ -3625,13 +3625,13 @@
         <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>57.6</v>
+        <v>68.8</v>
       </c>
       <c r="C160" t="n">
         <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>4.100944774058672e-09</v>
+        <v>5.506875429627605e-08</v>
       </c>
       <c r="E160" t="n">
         <v>100</v>
@@ -3645,13 +3645,13 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>57.6</v>
+        <v>68.8</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>4.100944774058672e-09</v>
+        <v>5.506875429627605e-08</v>
       </c>
       <c r="E161" t="n">
         <v>100</v>
@@ -3665,13 +3665,13 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>57.6</v>
+        <v>68.8</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>3.914599926890709e-09</v>
+        <v>5.506875429627605e-08</v>
       </c>
       <c r="E162" t="n">
         <v>100</v>
@@ -3685,13 +3685,13 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>57.6</v>
+        <v>68.8</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>3.914599926890709e-09</v>
+        <v>5.506875429627605e-08</v>
       </c>
       <c r="E163" t="n">
         <v>100</v>
@@ -3705,13 +3705,13 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>57.6</v>
+        <v>68</v>
       </c>
       <c r="C164" t="n">
         <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>3.914599926890709e-09</v>
+        <v>5.506875429627605e-08</v>
       </c>
       <c r="E164" t="n">
         <v>100</v>
@@ -3725,13 +3725,13 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>57.6</v>
+        <v>68</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>3.914599926890709e-09</v>
+        <v>5.506875429627605e-08</v>
       </c>
       <c r="E165" t="n">
         <v>100</v>
@@ -3745,13 +3745,13 @@
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>57.6</v>
+        <v>68</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>3.914599926890709e-09</v>
+        <v>5.506875429627605e-08</v>
       </c>
       <c r="E166" t="n">
         <v>100</v>
@@ -3765,13 +3765,13 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>57.6</v>
+        <v>68</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>3.914599926890709e-09</v>
+        <v>4.933997613899728e-08</v>
       </c>
       <c r="E167" t="n">
         <v>100</v>
@@ -3785,13 +3785,13 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>56.8</v>
+        <v>68</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>3.914599926890709e-09</v>
+        <v>4.933997613899728e-08</v>
       </c>
       <c r="E168" t="n">
         <v>100</v>
@@ -3805,13 +3805,13 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>56</v>
+        <v>64.8</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.933997613899728e-08</v>
       </c>
       <c r="E169" t="n">
         <v>100</v>
@@ -3825,13 +3825,13 @@
         <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>56</v>
+        <v>64.8</v>
       </c>
       <c r="C170" t="n">
         <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.933997613899728e-08</v>
       </c>
       <c r="E170" t="n">
         <v>100</v>
@@ -3845,13 +3845,13 @@
         <v>169</v>
       </c>
       <c r="B171" t="n">
-        <v>54.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.933997613899728e-08</v>
       </c>
       <c r="E171" t="n">
         <v>100</v>
@@ -3865,13 +3865,13 @@
         <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>54.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.933997613899728e-08</v>
       </c>
       <c r="E172" t="n">
         <v>100</v>
@@ -3885,13 +3885,13 @@
         <v>171</v>
       </c>
       <c r="B173" t="n">
-        <v>54.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C173" t="n">
         <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.933997613899728e-08</v>
       </c>
       <c r="E173" t="n">
         <v>100</v>
@@ -3905,13 +3905,13 @@
         <v>172</v>
       </c>
       <c r="B174" t="n">
-        <v>54.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C174" t="n">
         <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.933997613899728e-08</v>
       </c>
       <c r="E174" t="n">
         <v>100</v>
@@ -3925,13 +3925,13 @@
         <v>173</v>
       </c>
       <c r="B175" t="n">
-        <v>54.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C175" t="n">
         <v>1</v>
       </c>
       <c r="D175" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.933997613899728e-08</v>
       </c>
       <c r="E175" t="n">
         <v>100</v>
@@ -3945,13 +3945,13 @@
         <v>174</v>
       </c>
       <c r="B176" t="n">
-        <v>54.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
       </c>
       <c r="D176" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.933997613899728e-08</v>
       </c>
       <c r="E176" t="n">
         <v>100</v>
@@ -3965,13 +3965,13 @@
         <v>175</v>
       </c>
       <c r="B177" t="n">
-        <v>54.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.933997613899728e-08</v>
       </c>
       <c r="E177" t="n">
         <v>100</v>
@@ -3985,13 +3985,13 @@
         <v>176</v>
       </c>
       <c r="B178" t="n">
-        <v>54.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.933997613899728e-08</v>
       </c>
       <c r="E178" t="n">
         <v>100</v>
@@ -4005,13 +4005,13 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>53.6</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.933997613899728e-08</v>
       </c>
       <c r="E179" t="n">
         <v>100</v>
@@ -4025,13 +4025,13 @@
         <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>53.6</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C180" t="n">
         <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.933997613899728e-08</v>
       </c>
       <c r="E180" t="n">
         <v>100</v>
@@ -4045,13 +4045,13 @@
         <v>179</v>
       </c>
       <c r="B181" t="n">
-        <v>52.8</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.635474916766106e-08</v>
       </c>
       <c r="E181" t="n">
         <v>100</v>
@@ -4065,13 +4065,13 @@
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>52.8</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.635474916766106e-08</v>
       </c>
       <c r="E182" t="n">
         <v>100</v>
@@ -4085,13 +4085,13 @@
         <v>181</v>
       </c>
       <c r="B183" t="n">
-        <v>52</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
       </c>
       <c r="D183" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.370628442560898e-08</v>
       </c>
       <c r="E183" t="n">
         <v>100</v>
@@ -4105,13 +4105,13 @@
         <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>52</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>
       </c>
       <c r="D184" t="n">
-        <v>3.82638130962524e-09</v>
+        <v>4.370628442560898e-08</v>
       </c>
       <c r="E184" t="n">
         <v>100</v>
@@ -4125,13 +4125,13 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>52</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.370628442560898e-08</v>
       </c>
       <c r="E185" t="n">
         <v>100</v>
@@ -4145,13 +4145,13 @@
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>52</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
       </c>
       <c r="D186" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.370628442560898e-08</v>
       </c>
       <c r="E186" t="n">
         <v>100</v>
@@ -4165,13 +4165,13 @@
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>52</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
       </c>
       <c r="D187" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.370628442560898e-08</v>
       </c>
       <c r="E187" t="n">
         <v>100</v>
@@ -4185,13 +4185,13 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>52</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.370628442560898e-08</v>
       </c>
       <c r="E188" t="n">
         <v>100</v>
@@ -4205,13 +4205,13 @@
         <v>187</v>
       </c>
       <c r="B189" t="n">
-        <v>51.2</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.370628442560898e-08</v>
       </c>
       <c r="E189" t="n">
         <v>100</v>
@@ -4225,13 +4225,13 @@
         <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>50.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.370628442560898e-08</v>
       </c>
       <c r="E190" t="n">
         <v>100</v>
@@ -4245,13 +4245,13 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>50.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C191" t="n">
         <v>1</v>
       </c>
       <c r="D191" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.370628442560898e-08</v>
       </c>
       <c r="E191" t="n">
         <v>100</v>
@@ -4265,13 +4265,13 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>50.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C192" t="n">
         <v>1</v>
       </c>
       <c r="D192" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.370628442560898e-08</v>
       </c>
       <c r="E192" t="n">
         <v>100</v>
@@ -4285,13 +4285,13 @@
         <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>50.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C193" t="n">
         <v>1</v>
       </c>
       <c r="D193" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.21520834094959e-08</v>
       </c>
       <c r="E193" t="n">
         <v>100</v>
@@ -4305,13 +4305,13 @@
         <v>192</v>
       </c>
       <c r="B194" t="n">
-        <v>50.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
       </c>
       <c r="D194" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.21520834094959e-08</v>
       </c>
       <c r="E194" t="n">
         <v>100</v>
@@ -4325,13 +4325,13 @@
         <v>193</v>
       </c>
       <c r="B195" t="n">
-        <v>50.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C195" t="n">
         <v>1</v>
       </c>
       <c r="D195" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.21520834094959e-08</v>
       </c>
       <c r="E195" t="n">
         <v>100</v>
@@ -4345,13 +4345,13 @@
         <v>194</v>
       </c>
       <c r="B196" t="n">
-        <v>50.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C196" t="n">
         <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.21520834094959e-08</v>
       </c>
       <c r="E196" t="n">
         <v>100</v>
@@ -4365,13 +4365,13 @@
         <v>195</v>
       </c>
       <c r="B197" t="n">
-        <v>50.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.21520834094959e-08</v>
       </c>
       <c r="E197" t="n">
         <v>100</v>
@@ -4385,13 +4385,13 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>50.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C198" t="n">
         <v>1</v>
       </c>
       <c r="D198" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.21520834094959e-08</v>
       </c>
       <c r="E198" t="n">
         <v>100</v>
@@ -4405,13 +4405,13 @@
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>50.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C199" t="n">
         <v>1</v>
       </c>
       <c r="D199" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.21520834094959e-08</v>
       </c>
       <c r="E199" t="n">
         <v>100</v>
@@ -4425,13 +4425,13 @@
         <v>198</v>
       </c>
       <c r="B200" t="n">
-        <v>50.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C200" t="n">
         <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.21520834094959e-08</v>
       </c>
       <c r="E200" t="n">
         <v>100</v>
@@ -4445,13 +4445,13 @@
         <v>199</v>
       </c>
       <c r="B201" t="n">
-        <v>50.40000000000001</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C201" t="n">
         <v>1</v>
       </c>
       <c r="D201" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.21520834094959e-08</v>
       </c>
       <c r="E201" t="n">
         <v>100</v>
@@ -4465,13 +4465,13 @@
         <v>200</v>
       </c>
       <c r="B202" t="n">
-        <v>48.8</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C202" t="n">
         <v>1</v>
       </c>
       <c r="D202" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.129129101867925e-08</v>
       </c>
       <c r="E202" t="n">
         <v>100</v>
@@ -4485,13 +4485,13 @@
         <v>201</v>
       </c>
       <c r="B203" t="n">
-        <v>48.8</v>
+        <v>58.40000000000001</v>
       </c>
       <c r="C203" t="n">
         <v>1</v>
       </c>
       <c r="D203" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.129129101867925e-08</v>
       </c>
       <c r="E203" t="n">
         <v>100</v>
@@ -4505,13 +4505,13 @@
         <v>202</v>
       </c>
       <c r="B204" t="n">
-        <v>48.8</v>
+        <v>56.8</v>
       </c>
       <c r="C204" t="n">
         <v>1</v>
       </c>
       <c r="D204" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.129129101867925e-08</v>
       </c>
       <c r="E204" t="n">
         <v>100</v>
@@ -4525,13 +4525,13 @@
         <v>203</v>
       </c>
       <c r="B205" t="n">
-        <v>48.8</v>
+        <v>56.8</v>
       </c>
       <c r="C205" t="n">
         <v>1</v>
       </c>
       <c r="D205" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.129129101867925e-08</v>
       </c>
       <c r="E205" t="n">
         <v>100</v>
@@ -4545,13 +4545,13 @@
         <v>204</v>
       </c>
       <c r="B206" t="n">
-        <v>48.8</v>
+        <v>56.8</v>
       </c>
       <c r="C206" t="n">
         <v>1</v>
       </c>
       <c r="D206" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.129129101867925e-08</v>
       </c>
       <c r="E206" t="n">
         <v>100</v>
@@ -4565,13 +4565,13 @@
         <v>205</v>
       </c>
       <c r="B207" t="n">
-        <v>48.8</v>
+        <v>56.8</v>
       </c>
       <c r="C207" t="n">
         <v>1</v>
       </c>
       <c r="D207" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.129129101867925e-08</v>
       </c>
       <c r="E207" t="n">
         <v>100</v>
@@ -4585,13 +4585,13 @@
         <v>206</v>
       </c>
       <c r="B208" t="n">
-        <v>48.8</v>
+        <v>56.8</v>
       </c>
       <c r="C208" t="n">
         <v>1</v>
       </c>
       <c r="D208" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.129129101867925e-08</v>
       </c>
       <c r="E208" t="n">
         <v>100</v>
@@ -4605,13 +4605,13 @@
         <v>207</v>
       </c>
       <c r="B209" t="n">
-        <v>48.8</v>
+        <v>56.8</v>
       </c>
       <c r="C209" t="n">
         <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.129129101867925e-08</v>
       </c>
       <c r="E209" t="n">
         <v>100</v>
@@ -4625,13 +4625,13 @@
         <v>208</v>
       </c>
       <c r="B210" t="n">
-        <v>48.8</v>
+        <v>56.8</v>
       </c>
       <c r="C210" t="n">
         <v>1</v>
       </c>
       <c r="D210" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.129129101867925e-08</v>
       </c>
       <c r="E210" t="n">
         <v>100</v>
@@ -4645,13 +4645,13 @@
         <v>209</v>
       </c>
       <c r="B211" t="n">
-        <v>48.8</v>
+        <v>56.8</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
       </c>
       <c r="D211" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>4.129129101867925e-08</v>
       </c>
       <c r="E211" t="n">
         <v>100</v>
@@ -4665,13 +4665,13 @@
         <v>210</v>
       </c>
       <c r="B212" t="n">
-        <v>48</v>
+        <v>56.8</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
       </c>
       <c r="D212" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E212" t="n">
         <v>100</v>
@@ -4685,13 +4685,13 @@
         <v>211</v>
       </c>
       <c r="B213" t="n">
-        <v>48</v>
+        <v>56.8</v>
       </c>
       <c r="C213" t="n">
         <v>1</v>
       </c>
       <c r="D213" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E213" t="n">
         <v>100</v>
@@ -4705,13 +4705,13 @@
         <v>212</v>
       </c>
       <c r="B214" t="n">
-        <v>48</v>
+        <v>56.8</v>
       </c>
       <c r="C214" t="n">
         <v>1</v>
       </c>
       <c r="D214" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E214" t="n">
         <v>100</v>
@@ -4725,13 +4725,13 @@
         <v>213</v>
       </c>
       <c r="B215" t="n">
-        <v>48</v>
+        <v>56.8</v>
       </c>
       <c r="C215" t="n">
         <v>1</v>
       </c>
       <c r="D215" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E215" t="n">
         <v>100</v>
@@ -4745,13 +4745,13 @@
         <v>214</v>
       </c>
       <c r="B216" t="n">
-        <v>48</v>
+        <v>56.8</v>
       </c>
       <c r="C216" t="n">
         <v>1</v>
       </c>
       <c r="D216" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E216" t="n">
         <v>100</v>
@@ -4765,13 +4765,13 @@
         <v>215</v>
       </c>
       <c r="B217" t="n">
-        <v>48</v>
+        <v>56.8</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
       </c>
       <c r="D217" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E217" t="n">
         <v>100</v>
@@ -4785,13 +4785,13 @@
         <v>216</v>
       </c>
       <c r="B218" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E218" t="n">
         <v>100</v>
@@ -4805,13 +4805,13 @@
         <v>217</v>
       </c>
       <c r="B219" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C219" t="n">
         <v>1</v>
       </c>
       <c r="D219" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E219" t="n">
         <v>100</v>
@@ -4825,13 +4825,13 @@
         <v>218</v>
       </c>
       <c r="B220" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E220" t="n">
         <v>100</v>
@@ -4845,13 +4845,13 @@
         <v>219</v>
       </c>
       <c r="B221" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C221" t="n">
         <v>1</v>
       </c>
       <c r="D221" t="n">
-        <v>3.776458439754372e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E221" t="n">
         <v>100</v>
@@ -4865,13 +4865,13 @@
         <v>220</v>
       </c>
       <c r="B222" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C222" t="n">
         <v>1</v>
       </c>
       <c r="D222" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E222" t="n">
         <v>100</v>
@@ -4885,13 +4885,13 @@
         <v>221</v>
       </c>
       <c r="B223" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C223" t="n">
         <v>1</v>
       </c>
       <c r="D223" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E223" t="n">
         <v>100</v>
@@ -4905,13 +4905,13 @@
         <v>222</v>
       </c>
       <c r="B224" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C224" t="n">
         <v>1</v>
       </c>
       <c r="D224" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E224" t="n">
         <v>100</v>
@@ -4925,13 +4925,13 @@
         <v>223</v>
       </c>
       <c r="B225" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C225" t="n">
         <v>1</v>
       </c>
       <c r="D225" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E225" t="n">
         <v>100</v>
@@ -4945,13 +4945,13 @@
         <v>224</v>
       </c>
       <c r="B226" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C226" t="n">
         <v>1</v>
       </c>
       <c r="D226" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E226" t="n">
         <v>100</v>
@@ -4965,13 +4965,13 @@
         <v>225</v>
       </c>
       <c r="B227" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C227" t="n">
         <v>1</v>
       </c>
       <c r="D227" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E227" t="n">
         <v>100</v>
@@ -4985,13 +4985,13 @@
         <v>226</v>
       </c>
       <c r="B228" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C228" t="n">
         <v>1</v>
       </c>
       <c r="D228" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E228" t="n">
         <v>100</v>
@@ -5005,13 +5005,13 @@
         <v>227</v>
       </c>
       <c r="B229" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C229" t="n">
         <v>1</v>
       </c>
       <c r="D229" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E229" t="n">
         <v>100</v>
@@ -5025,13 +5025,13 @@
         <v>228</v>
       </c>
       <c r="B230" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C230" t="n">
         <v>1</v>
       </c>
       <c r="D230" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E230" t="n">
         <v>100</v>
@@ -5045,13 +5045,13 @@
         <v>229</v>
       </c>
       <c r="B231" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C231" t="n">
         <v>1</v>
       </c>
       <c r="D231" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E231" t="n">
         <v>100</v>
@@ -5065,13 +5065,13 @@
         <v>230</v>
       </c>
       <c r="B232" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C232" t="n">
         <v>1</v>
       </c>
       <c r="D232" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E232" t="n">
         <v>100</v>
@@ -5085,13 +5085,13 @@
         <v>231</v>
       </c>
       <c r="B233" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C233" t="n">
         <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E233" t="n">
         <v>100</v>
@@ -5105,13 +5105,13 @@
         <v>232</v>
       </c>
       <c r="B234" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C234" t="n">
         <v>1</v>
       </c>
       <c r="D234" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E234" t="n">
         <v>100</v>
@@ -5125,13 +5125,13 @@
         <v>233</v>
       </c>
       <c r="B235" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C235" t="n">
         <v>1</v>
       </c>
       <c r="D235" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E235" t="n">
         <v>100</v>
@@ -5145,13 +5145,13 @@
         <v>234</v>
       </c>
       <c r="B236" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C236" t="n">
         <v>1</v>
       </c>
       <c r="D236" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E236" t="n">
         <v>100</v>
@@ -5165,13 +5165,13 @@
         <v>235</v>
       </c>
       <c r="B237" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C237" t="n">
         <v>1</v>
       </c>
       <c r="D237" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E237" t="n">
         <v>100</v>
@@ -5185,13 +5185,13 @@
         <v>236</v>
       </c>
       <c r="B238" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C238" t="n">
         <v>1</v>
       </c>
       <c r="D238" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.948288051038404e-08</v>
       </c>
       <c r="E238" t="n">
         <v>100</v>
@@ -5205,13 +5205,13 @@
         <v>237</v>
       </c>
       <c r="B239" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C239" t="n">
         <v>1</v>
       </c>
       <c r="D239" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.803148338058013e-08</v>
       </c>
       <c r="E239" t="n">
         <v>100</v>
@@ -5225,13 +5225,13 @@
         <v>238</v>
       </c>
       <c r="B240" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C240" t="n">
         <v>1</v>
       </c>
       <c r="D240" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.803148338058013e-08</v>
       </c>
       <c r="E240" t="n">
         <v>100</v>
@@ -5245,13 +5245,13 @@
         <v>239</v>
       </c>
       <c r="B241" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C241" t="n">
         <v>1</v>
       </c>
       <c r="D241" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.424557714932263e-08</v>
       </c>
       <c r="E241" t="n">
         <v>100</v>
@@ -5265,13 +5265,13 @@
         <v>240</v>
       </c>
       <c r="B242" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C242" t="n">
         <v>1</v>
       </c>
       <c r="D242" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.424557714932263e-08</v>
       </c>
       <c r="E242" t="n">
         <v>100</v>
@@ -5285,13 +5285,13 @@
         <v>241</v>
       </c>
       <c r="B243" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C243" t="n">
         <v>1</v>
       </c>
       <c r="D243" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.424557714932263e-08</v>
       </c>
       <c r="E243" t="n">
         <v>100</v>
@@ -5305,13 +5305,13 @@
         <v>242</v>
       </c>
       <c r="B244" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C244" t="n">
         <v>1</v>
       </c>
       <c r="D244" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.424557714932263e-08</v>
       </c>
       <c r="E244" t="n">
         <v>100</v>
@@ -5325,13 +5325,13 @@
         <v>243</v>
       </c>
       <c r="B245" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C245" t="n">
         <v>1</v>
       </c>
       <c r="D245" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.424557714932263e-08</v>
       </c>
       <c r="E245" t="n">
         <v>100</v>
@@ -5345,13 +5345,13 @@
         <v>244</v>
       </c>
       <c r="B246" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C246" t="n">
         <v>1</v>
       </c>
       <c r="D246" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.424557714932263e-08</v>
       </c>
       <c r="E246" t="n">
         <v>100</v>
@@ -5365,13 +5365,13 @@
         <v>245</v>
       </c>
       <c r="B247" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C247" t="n">
         <v>1</v>
       </c>
       <c r="D247" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.424557714932263e-08</v>
       </c>
       <c r="E247" t="n">
         <v>100</v>
@@ -5385,13 +5385,13 @@
         <v>246</v>
       </c>
       <c r="B248" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C248" t="n">
         <v>1</v>
       </c>
       <c r="D248" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.424557714932263e-08</v>
       </c>
       <c r="E248" t="n">
         <v>100</v>
@@ -5405,13 +5405,13 @@
         <v>247</v>
       </c>
       <c r="B249" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C249" t="n">
         <v>1</v>
       </c>
       <c r="D249" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.424557714932263e-08</v>
       </c>
       <c r="E249" t="n">
         <v>100</v>
@@ -5425,13 +5425,13 @@
         <v>248</v>
       </c>
       <c r="B250" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C250" t="n">
         <v>1</v>
       </c>
       <c r="D250" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.424557714932263e-08</v>
       </c>
       <c r="E250" t="n">
         <v>100</v>
@@ -5445,13 +5445,13 @@
         <v>249</v>
       </c>
       <c r="B251" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C251" t="n">
         <v>1</v>
       </c>
       <c r="D251" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.424557714932263e-08</v>
       </c>
       <c r="E251" t="n">
         <v>100</v>
@@ -5465,13 +5465,13 @@
         <v>250</v>
       </c>
       <c r="B252" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C252" t="n">
         <v>1</v>
       </c>
       <c r="D252" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.424557714932263e-08</v>
       </c>
       <c r="E252" t="n">
         <v>100</v>
@@ -5485,13 +5485,13 @@
         <v>251</v>
       </c>
       <c r="B253" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C253" t="n">
         <v>1</v>
       </c>
       <c r="D253" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>3.424557714932263e-08</v>
       </c>
       <c r="E253" t="n">
         <v>100</v>
@@ -5505,13 +5505,13 @@
         <v>252</v>
       </c>
       <c r="B254" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C254" t="n">
         <v>1</v>
       </c>
       <c r="D254" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>2.698124660605298e-08</v>
       </c>
       <c r="E254" t="n">
         <v>100</v>
@@ -5525,13 +5525,13 @@
         <v>253</v>
       </c>
       <c r="B255" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C255" t="n">
         <v>1</v>
       </c>
       <c r="D255" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>2.698124660605298e-08</v>
       </c>
       <c r="E255" t="n">
         <v>100</v>
@@ -5545,13 +5545,13 @@
         <v>254</v>
       </c>
       <c r="B256" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C256" t="n">
         <v>1</v>
       </c>
       <c r="D256" t="n">
-        <v>3.771667808574105e-09</v>
+        <v>2.698124660605298e-08</v>
       </c>
       <c r="E256" t="n">
         <v>100</v>
@@ -5565,13 +5565,13 @@
         <v>255</v>
       </c>
       <c r="B257" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C257" t="n">
         <v>1</v>
       </c>
       <c r="D257" t="n">
-        <v>3.728879669141288e-09</v>
+        <v>2.698124660605298e-08</v>
       </c>
       <c r="E257" t="n">
         <v>100</v>
@@ -5585,13 +5585,13 @@
         <v>256</v>
       </c>
       <c r="B258" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C258" t="n">
         <v>1</v>
       </c>
       <c r="D258" t="n">
-        <v>3.728879669141288e-09</v>
+        <v>2.698124660605298e-08</v>
       </c>
       <c r="E258" t="n">
         <v>100</v>
@@ -5605,13 +5605,13 @@
         <v>257</v>
       </c>
       <c r="B259" t="n">
-        <v>46.40000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C259" t="n">
         <v>1</v>
       </c>
       <c r="D259" t="n">
-        <v>3.728879669141288e-09</v>
+        <v>2.698124660605298e-08</v>
       </c>
       <c r="E259" t="n">
         <v>100</v>
@@ -5625,13 +5625,13 @@
         <v>258</v>
       </c>
       <c r="B260" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C260" t="n">
         <v>1</v>
       </c>
       <c r="D260" t="n">
-        <v>3.728879669141288e-09</v>
+        <v>2.698124660605298e-08</v>
       </c>
       <c r="E260" t="n">
         <v>100</v>
@@ -5645,13 +5645,13 @@
         <v>259</v>
       </c>
       <c r="B261" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C261" t="n">
         <v>1</v>
       </c>
       <c r="D261" t="n">
-        <v>3.728879669141288e-09</v>
+        <v>2.698124660605298e-08</v>
       </c>
       <c r="E261" t="n">
         <v>100</v>
@@ -5665,13 +5665,13 @@
         <v>260</v>
       </c>
       <c r="B262" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C262" t="n">
         <v>1</v>
       </c>
       <c r="D262" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.653005630006999e-08</v>
       </c>
       <c r="E262" t="n">
         <v>100</v>
@@ -5685,13 +5685,13 @@
         <v>261</v>
       </c>
       <c r="B263" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C263" t="n">
         <v>1</v>
       </c>
       <c r="D263" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.653005630006999e-08</v>
       </c>
       <c r="E263" t="n">
         <v>100</v>
@@ -5705,13 +5705,13 @@
         <v>262</v>
       </c>
       <c r="B264" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C264" t="n">
         <v>1</v>
       </c>
       <c r="D264" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.653005630006999e-08</v>
       </c>
       <c r="E264" t="n">
         <v>100</v>
@@ -5725,13 +5725,13 @@
         <v>263</v>
       </c>
       <c r="B265" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C265" t="n">
         <v>1</v>
       </c>
       <c r="D265" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.653005630006999e-08</v>
       </c>
       <c r="E265" t="n">
         <v>100</v>
@@ -5745,13 +5745,13 @@
         <v>264</v>
       </c>
       <c r="B266" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C266" t="n">
         <v>1</v>
       </c>
       <c r="D266" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.653005630006999e-08</v>
       </c>
       <c r="E266" t="n">
         <v>100</v>
@@ -5765,13 +5765,13 @@
         <v>265</v>
       </c>
       <c r="B267" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C267" t="n">
         <v>1</v>
       </c>
       <c r="D267" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.653005630006999e-08</v>
       </c>
       <c r="E267" t="n">
         <v>100</v>
@@ -5785,13 +5785,13 @@
         <v>266</v>
       </c>
       <c r="B268" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C268" t="n">
         <v>1</v>
       </c>
       <c r="D268" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.653005630006999e-08</v>
       </c>
       <c r="E268" t="n">
         <v>100</v>
@@ -5805,13 +5805,13 @@
         <v>267</v>
       </c>
       <c r="B269" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C269" t="n">
         <v>1</v>
       </c>
       <c r="D269" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.653005630006999e-08</v>
       </c>
       <c r="E269" t="n">
         <v>100</v>
@@ -5825,13 +5825,13 @@
         <v>268</v>
       </c>
       <c r="B270" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C270" t="n">
         <v>1</v>
       </c>
       <c r="D270" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.610066113831165e-08</v>
       </c>
       <c r="E270" t="n">
         <v>100</v>
@@ -5845,13 +5845,13 @@
         <v>269</v>
       </c>
       <c r="B271" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C271" t="n">
         <v>1</v>
       </c>
       <c r="D271" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.610066113831165e-08</v>
       </c>
       <c r="E271" t="n">
         <v>100</v>
@@ -5865,13 +5865,13 @@
         <v>270</v>
       </c>
       <c r="B272" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C272" t="n">
         <v>1</v>
       </c>
       <c r="D272" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.610066113831165e-08</v>
       </c>
       <c r="E272" t="n">
         <v>100</v>
@@ -5885,13 +5885,13 @@
         <v>271</v>
       </c>
       <c r="B273" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C273" t="n">
         <v>1</v>
       </c>
       <c r="D273" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.394202553489479e-08</v>
       </c>
       <c r="E273" t="n">
         <v>100</v>
@@ -5905,13 +5905,13 @@
         <v>272</v>
       </c>
       <c r="B274" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C274" t="n">
         <v>1</v>
       </c>
       <c r="D274" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.394202553489479e-08</v>
       </c>
       <c r="E274" t="n">
         <v>100</v>
@@ -5925,13 +5925,13 @@
         <v>273</v>
       </c>
       <c r="B275" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C275" t="n">
         <v>1</v>
       </c>
       <c r="D275" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.394202553489479e-08</v>
       </c>
       <c r="E275" t="n">
         <v>100</v>
@@ -5945,13 +5945,13 @@
         <v>274</v>
       </c>
       <c r="B276" t="n">
-        <v>45.6</v>
+        <v>56.8</v>
       </c>
       <c r="C276" t="n">
         <v>1</v>
       </c>
       <c r="D276" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.394202553489479e-08</v>
       </c>
       <c r="E276" t="n">
         <v>100</v>
@@ -5965,13 +5965,13 @@
         <v>275</v>
       </c>
       <c r="B277" t="n">
-        <v>44.8</v>
+        <v>56.8</v>
       </c>
       <c r="C277" t="n">
         <v>1</v>
       </c>
       <c r="D277" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.394202553489479e-08</v>
       </c>
       <c r="E277" t="n">
         <v>100</v>
@@ -5985,13 +5985,13 @@
         <v>276</v>
       </c>
       <c r="B278" t="n">
-        <v>44.8</v>
+        <v>56.8</v>
       </c>
       <c r="C278" t="n">
         <v>1</v>
       </c>
       <c r="D278" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.305623487004794e-08</v>
       </c>
       <c r="E278" t="n">
         <v>100</v>
@@ -6005,13 +6005,13 @@
         <v>277</v>
       </c>
       <c r="B279" t="n">
-        <v>44.8</v>
+        <v>56.8</v>
       </c>
       <c r="C279" t="n">
         <v>1</v>
       </c>
       <c r="D279" t="n">
-        <v>3.654270428346982e-09</v>
+        <v>2.305623487004794e-08</v>
       </c>
       <c r="E279" t="n">
         <v>100</v>
@@ -6025,13 +6025,13 @@
         <v>278</v>
       </c>
       <c r="B280" t="n">
-        <v>44.8</v>
+        <v>56.8</v>
       </c>
       <c r="C280" t="n">
         <v>1</v>
       </c>
       <c r="D280" t="n">
-        <v>3.573992381841009e-09</v>
+        <v>2.305623487004794e-08</v>
       </c>
       <c r="E280" t="n">
         <v>100</v>
@@ -6045,13 +6045,13 @@
         <v>279</v>
       </c>
       <c r="B281" t="n">
-        <v>44.8</v>
+        <v>56.8</v>
       </c>
       <c r="C281" t="n">
         <v>1</v>
       </c>
       <c r="D281" t="n">
-        <v>3.573992381841009e-09</v>
+        <v>2.305623487004794e-08</v>
       </c>
       <c r="E281" t="n">
         <v>100</v>
@@ -6065,13 +6065,13 @@
         <v>280</v>
       </c>
       <c r="B282" t="n">
-        <v>44.8</v>
+        <v>56.8</v>
       </c>
       <c r="C282" t="n">
         <v>1</v>
       </c>
       <c r="D282" t="n">
-        <v>3.573992381841009e-09</v>
+        <v>2.305623487004794e-08</v>
       </c>
       <c r="E282" t="n">
         <v>100</v>
@@ -6085,13 +6085,13 @@
         <v>281</v>
       </c>
       <c r="B283" t="n">
-        <v>44.8</v>
+        <v>56.8</v>
       </c>
       <c r="C283" t="n">
         <v>1</v>
       </c>
       <c r="D283" t="n">
-        <v>3.573992381841009e-09</v>
+        <v>2.305623487004794e-08</v>
       </c>
       <c r="E283" t="n">
         <v>100</v>
@@ -6105,13 +6105,13 @@
         <v>282</v>
       </c>
       <c r="B284" t="n">
-        <v>44.8</v>
+        <v>56.8</v>
       </c>
       <c r="C284" t="n">
         <v>1</v>
       </c>
       <c r="D284" t="n">
-        <v>3.573992381841009e-09</v>
+        <v>2.305623487004794e-08</v>
       </c>
       <c r="E284" t="n">
         <v>100</v>
@@ -6125,13 +6125,13 @@
         <v>283</v>
       </c>
       <c r="B285" t="n">
-        <v>44.8</v>
+        <v>56.8</v>
       </c>
       <c r="C285" t="n">
         <v>1</v>
       </c>
       <c r="D285" t="n">
-        <v>3.573992381841009e-09</v>
+        <v>2.210919528312877e-08</v>
       </c>
       <c r="E285" t="n">
         <v>100</v>
@@ -6145,13 +6145,13 @@
         <v>284</v>
       </c>
       <c r="B286" t="n">
-        <v>44.8</v>
+        <v>56.8</v>
       </c>
       <c r="C286" t="n">
         <v>1</v>
       </c>
       <c r="D286" t="n">
-        <v>3.573992381841009e-09</v>
+        <v>2.210919528312877e-08</v>
       </c>
       <c r="E286" t="n">
         <v>100</v>
@@ -6165,13 +6165,13 @@
         <v>285</v>
       </c>
       <c r="B287" t="n">
-        <v>44.8</v>
+        <v>56.8</v>
       </c>
       <c r="C287" t="n">
         <v>1</v>
       </c>
       <c r="D287" t="n">
-        <v>3.573992381841009e-09</v>
+        <v>2.192554846246147e-08</v>
       </c>
       <c r="E287" t="n">
         <v>100</v>
@@ -6185,13 +6185,13 @@
         <v>286</v>
       </c>
       <c r="B288" t="n">
-        <v>44.8</v>
+        <v>56.8</v>
       </c>
       <c r="C288" t="n">
         <v>1</v>
       </c>
       <c r="D288" t="n">
-        <v>3.573992381841009e-09</v>
+        <v>2.192554846246147e-08</v>
       </c>
       <c r="E288" t="n">
         <v>100</v>
@@ -6205,13 +6205,13 @@
         <v>287</v>
       </c>
       <c r="B289" t="n">
-        <v>44.8</v>
+        <v>56.8</v>
       </c>
       <c r="C289" t="n">
         <v>1</v>
       </c>
       <c r="D289" t="n">
-        <v>3.418917169520402e-09</v>
+        <v>2.192554846246147e-08</v>
       </c>
       <c r="E289" t="n">
         <v>100</v>
@@ -6225,13 +6225,13 @@
         <v>288</v>
       </c>
       <c r="B290" t="n">
-        <v>44.8</v>
+        <v>56.8</v>
       </c>
       <c r="C290" t="n">
         <v>1</v>
       </c>
       <c r="D290" t="n">
-        <v>3.418917169520402e-09</v>
+        <v>2.192554846246147e-08</v>
       </c>
       <c r="E290" t="n">
         <v>100</v>
@@ -6245,13 +6245,13 @@
         <v>289</v>
       </c>
       <c r="B291" t="n">
-        <v>44.8</v>
+        <v>56</v>
       </c>
       <c r="C291" t="n">
         <v>1</v>
       </c>
       <c r="D291" t="n">
-        <v>3.418917169520402e-09</v>
+        <v>2.192554846246147e-08</v>
       </c>
       <c r="E291" t="n">
         <v>100</v>
@@ -6265,13 +6265,13 @@
         <v>290</v>
       </c>
       <c r="B292" t="n">
-        <v>44.8</v>
+        <v>56</v>
       </c>
       <c r="C292" t="n">
         <v>1</v>
       </c>
       <c r="D292" t="n">
-        <v>3.341093170075882e-09</v>
+        <v>2.192554846246147e-08</v>
       </c>
       <c r="E292" t="n">
         <v>100</v>
@@ -6285,13 +6285,13 @@
         <v>291</v>
       </c>
       <c r="B293" t="n">
-        <v>44.8</v>
+        <v>56</v>
       </c>
       <c r="C293" t="n">
         <v>1</v>
       </c>
       <c r="D293" t="n">
-        <v>3.341093170075882e-09</v>
+        <v>2.172691338665494e-08</v>
       </c>
       <c r="E293" t="n">
         <v>100</v>
@@ -6305,13 +6305,13 @@
         <v>292</v>
       </c>
       <c r="B294" t="n">
-        <v>44.8</v>
+        <v>56</v>
       </c>
       <c r="C294" t="n">
         <v>1</v>
       </c>
       <c r="D294" t="n">
-        <v>3.341093170075882e-09</v>
+        <v>2.172691338665494e-08</v>
       </c>
       <c r="E294" t="n">
         <v>100</v>
@@ -6325,13 +6325,13 @@
         <v>293</v>
       </c>
       <c r="B295" t="n">
-        <v>44.8</v>
+        <v>56</v>
       </c>
       <c r="C295" t="n">
         <v>1</v>
       </c>
       <c r="D295" t="n">
-        <v>3.341093170075882e-09</v>
+        <v>2.172691338665494e-08</v>
       </c>
       <c r="E295" t="n">
         <v>100</v>
@@ -6345,13 +6345,13 @@
         <v>294</v>
       </c>
       <c r="B296" t="n">
-        <v>44.8</v>
+        <v>56</v>
       </c>
       <c r="C296" t="n">
         <v>1</v>
       </c>
       <c r="D296" t="n">
-        <v>3.341093170075882e-09</v>
+        <v>2.172691338665494e-08</v>
       </c>
       <c r="E296" t="n">
         <v>100</v>
@@ -6365,13 +6365,13 @@
         <v>295</v>
       </c>
       <c r="B297" t="n">
-        <v>44.8</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="C297" t="n">
         <v>1</v>
       </c>
       <c r="D297" t="n">
-        <v>3.341093170075882e-09</v>
+        <v>2.151676496602349e-08</v>
       </c>
       <c r="E297" t="n">
         <v>100</v>
@@ -6385,13 +6385,13 @@
         <v>296</v>
       </c>
       <c r="B298" t="n">
-        <v>44.8</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="C298" t="n">
         <v>1</v>
       </c>
       <c r="D298" t="n">
-        <v>3.341093170075882e-09</v>
+        <v>2.151676496602349e-08</v>
       </c>
       <c r="E298" t="n">
         <v>100</v>
@@ -6405,13 +6405,13 @@
         <v>297</v>
       </c>
       <c r="B299" t="n">
-        <v>44.8</v>
+        <v>53.6</v>
       </c>
       <c r="C299" t="n">
         <v>1</v>
       </c>
       <c r="D299" t="n">
-        <v>3.264146769912705e-09</v>
+        <v>2.151676496602349e-08</v>
       </c>
       <c r="E299" t="n">
         <v>100</v>
@@ -6425,13 +6425,13 @@
         <v>298</v>
       </c>
       <c r="B300" t="n">
-        <v>44.8</v>
+        <v>53.6</v>
       </c>
       <c r="C300" t="n">
         <v>1</v>
       </c>
       <c r="D300" t="n">
-        <v>3.264146769912705e-09</v>
+        <v>2.151676496602349e-08</v>
       </c>
       <c r="E300" t="n">
         <v>100</v>
@@ -6445,13 +6445,13 @@
         <v>299</v>
       </c>
       <c r="B301" t="n">
-        <v>44.8</v>
+        <v>53.6</v>
       </c>
       <c r="C301" t="n">
         <v>1</v>
       </c>
       <c r="D301" t="n">
-        <v>3.264146769912705e-09</v>
+        <v>2.151676496602349e-08</v>
       </c>
       <c r="E301" t="n">
         <v>100</v>
@@ -6465,13 +6465,13 @@
         <v>300</v>
       </c>
       <c r="B302" t="n">
-        <v>44.8</v>
+        <v>53.6</v>
       </c>
       <c r="C302" t="n">
         <v>1</v>
       </c>
       <c r="D302" t="n">
-        <v>3.264146769912705e-09</v>
+        <v>2.151676496602349e-08</v>
       </c>
       <c r="E302" t="n">
         <v>100</v>
@@ -6485,13 +6485,13 @@
         <v>301</v>
       </c>
       <c r="B303" t="n">
-        <v>44.8</v>
+        <v>53.6</v>
       </c>
       <c r="C303" t="n">
         <v>1</v>
       </c>
       <c r="D303" t="n">
-        <v>3.264146769912705e-09</v>
+        <v>2.151676496602349e-08</v>
       </c>
       <c r="E303" t="n">
         <v>100</v>
@@ -6505,13 +6505,13 @@
         <v>302</v>
       </c>
       <c r="B304" t="n">
-        <v>44.8</v>
+        <v>53.6</v>
       </c>
       <c r="C304" t="n">
         <v>1</v>
       </c>
       <c r="D304" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.151676496602349e-08</v>
       </c>
       <c r="E304" t="n">
         <v>100</v>
@@ -6525,13 +6525,13 @@
         <v>303</v>
       </c>
       <c r="B305" t="n">
-        <v>44.8</v>
+        <v>53.6</v>
       </c>
       <c r="C305" t="n">
         <v>1</v>
       </c>
       <c r="D305" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.151676496602349e-08</v>
       </c>
       <c r="E305" t="n">
         <v>100</v>
@@ -6545,13 +6545,13 @@
         <v>304</v>
       </c>
       <c r="B306" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C306" t="n">
         <v>1</v>
       </c>
       <c r="D306" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.096715326828212e-08</v>
       </c>
       <c r="E306" t="n">
         <v>100</v>
@@ -6565,13 +6565,13 @@
         <v>305</v>
       </c>
       <c r="B307" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C307" t="n">
         <v>1</v>
       </c>
       <c r="D307" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.096715326828212e-08</v>
       </c>
       <c r="E307" t="n">
         <v>100</v>
@@ -6585,13 +6585,13 @@
         <v>306</v>
       </c>
       <c r="B308" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C308" t="n">
         <v>1</v>
       </c>
       <c r="D308" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.096715326828212e-08</v>
       </c>
       <c r="E308" t="n">
         <v>100</v>
@@ -6605,13 +6605,13 @@
         <v>307</v>
       </c>
       <c r="B309" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C309" t="n">
         <v>1</v>
       </c>
       <c r="D309" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.096715326828212e-08</v>
       </c>
       <c r="E309" t="n">
         <v>100</v>
@@ -6625,13 +6625,13 @@
         <v>308</v>
       </c>
       <c r="B310" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C310" t="n">
         <v>1</v>
       </c>
       <c r="D310" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.088060268373321e-08</v>
       </c>
       <c r="E310" t="n">
         <v>100</v>
@@ -6645,13 +6645,13 @@
         <v>309</v>
       </c>
       <c r="B311" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C311" t="n">
         <v>1</v>
       </c>
       <c r="D311" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.088060268373321e-08</v>
       </c>
       <c r="E311" t="n">
         <v>100</v>
@@ -6665,13 +6665,13 @@
         <v>310</v>
       </c>
       <c r="B312" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C312" t="n">
         <v>1</v>
       </c>
       <c r="D312" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.088060268373321e-08</v>
       </c>
       <c r="E312" t="n">
         <v>100</v>
@@ -6685,13 +6685,13 @@
         <v>311</v>
       </c>
       <c r="B313" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C313" t="n">
         <v>1</v>
       </c>
       <c r="D313" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.088060268373321e-08</v>
       </c>
       <c r="E313" t="n">
         <v>100</v>
@@ -6705,13 +6705,13 @@
         <v>312</v>
       </c>
       <c r="B314" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C314" t="n">
         <v>1</v>
       </c>
       <c r="D314" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.066482400319674e-08</v>
       </c>
       <c r="E314" t="n">
         <v>100</v>
@@ -6725,13 +6725,13 @@
         <v>313</v>
       </c>
       <c r="B315" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C315" t="n">
         <v>1</v>
       </c>
       <c r="D315" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.066482400319674e-08</v>
       </c>
       <c r="E315" t="n">
         <v>100</v>
@@ -6745,13 +6745,13 @@
         <v>314</v>
       </c>
       <c r="B316" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C316" t="n">
         <v>1</v>
       </c>
       <c r="D316" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.066482400319674e-08</v>
       </c>
       <c r="E316" t="n">
         <v>100</v>
@@ -6765,13 +6765,13 @@
         <v>315</v>
       </c>
       <c r="B317" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C317" t="n">
         <v>1</v>
       </c>
       <c r="D317" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E317" t="n">
         <v>100</v>
@@ -6785,13 +6785,13 @@
         <v>316</v>
       </c>
       <c r="B318" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C318" t="n">
         <v>1</v>
       </c>
       <c r="D318" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E318" t="n">
         <v>100</v>
@@ -6805,13 +6805,13 @@
         <v>317</v>
       </c>
       <c r="B319" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C319" t="n">
         <v>1</v>
       </c>
       <c r="D319" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E319" t="n">
         <v>100</v>
@@ -6825,13 +6825,13 @@
         <v>318</v>
       </c>
       <c r="B320" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C320" t="n">
         <v>1</v>
       </c>
       <c r="D320" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E320" t="n">
         <v>100</v>
@@ -6845,13 +6845,13 @@
         <v>319</v>
       </c>
       <c r="B321" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C321" t="n">
         <v>1</v>
       </c>
       <c r="D321" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E321" t="n">
         <v>100</v>
@@ -6865,13 +6865,13 @@
         <v>320</v>
       </c>
       <c r="B322" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C322" t="n">
         <v>1</v>
       </c>
       <c r="D322" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E322" t="n">
         <v>100</v>
@@ -6885,13 +6885,13 @@
         <v>321</v>
       </c>
       <c r="B323" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C323" t="n">
         <v>1</v>
       </c>
       <c r="D323" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E323" t="n">
         <v>100</v>
@@ -6905,13 +6905,13 @@
         <v>322</v>
       </c>
       <c r="B324" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C324" t="n">
         <v>1</v>
       </c>
       <c r="D324" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E324" t="n">
         <v>100</v>
@@ -6925,13 +6925,13 @@
         <v>323</v>
       </c>
       <c r="B325" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C325" t="n">
         <v>1</v>
       </c>
       <c r="D325" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E325" t="n">
         <v>100</v>
@@ -6945,13 +6945,13 @@
         <v>324</v>
       </c>
       <c r="B326" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C326" t="n">
         <v>1</v>
       </c>
       <c r="D326" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E326" t="n">
         <v>100</v>
@@ -6965,13 +6965,13 @@
         <v>325</v>
       </c>
       <c r="B327" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C327" t="n">
         <v>1</v>
       </c>
       <c r="D327" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E327" t="n">
         <v>100</v>
@@ -6985,13 +6985,13 @@
         <v>326</v>
       </c>
       <c r="B328" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C328" t="n">
         <v>1</v>
       </c>
       <c r="D328" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E328" t="n">
         <v>100</v>
@@ -7005,13 +7005,13 @@
         <v>327</v>
       </c>
       <c r="B329" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C329" t="n">
         <v>1</v>
       </c>
       <c r="D329" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E329" t="n">
         <v>100</v>
@@ -7025,13 +7025,13 @@
         <v>328</v>
       </c>
       <c r="B330" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C330" t="n">
         <v>1</v>
       </c>
       <c r="D330" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E330" t="n">
         <v>100</v>
@@ -7045,13 +7045,13 @@
         <v>329</v>
       </c>
       <c r="B331" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C331" t="n">
         <v>1</v>
       </c>
       <c r="D331" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E331" t="n">
         <v>100</v>
@@ -7065,13 +7065,13 @@
         <v>330</v>
       </c>
       <c r="B332" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C332" t="n">
         <v>1</v>
       </c>
       <c r="D332" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E332" t="n">
         <v>100</v>
@@ -7085,13 +7085,13 @@
         <v>331</v>
       </c>
       <c r="B333" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C333" t="n">
         <v>1</v>
       </c>
       <c r="D333" t="n">
-        <v>2.840943391588845e-09</v>
+        <v>2.028714893990752e-08</v>
       </c>
       <c r="E333" t="n">
         <v>100</v>
@@ -7105,13 +7105,13 @@
         <v>332</v>
       </c>
       <c r="B334" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C334" t="n">
         <v>1</v>
       </c>
       <c r="D334" t="n">
-        <v>2.56646097111198e-09</v>
+        <v>2.021708624560771e-08</v>
       </c>
       <c r="E334" t="n">
         <v>100</v>
@@ -7125,13 +7125,13 @@
         <v>333</v>
       </c>
       <c r="B335" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C335" t="n">
         <v>1</v>
       </c>
       <c r="D335" t="n">
-        <v>2.56646097111198e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E335" t="n">
         <v>100</v>
@@ -7145,13 +7145,13 @@
         <v>334</v>
       </c>
       <c r="B336" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C336" t="n">
         <v>1</v>
       </c>
       <c r="D336" t="n">
-        <v>2.56646097111198e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E336" t="n">
         <v>100</v>
@@ -7165,13 +7165,13 @@
         <v>335</v>
       </c>
       <c r="B337" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C337" t="n">
         <v>1</v>
       </c>
       <c r="D337" t="n">
-        <v>2.56646097111198e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E337" t="n">
         <v>100</v>
@@ -7185,13 +7185,13 @@
         <v>336</v>
       </c>
       <c r="B338" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C338" t="n">
         <v>1</v>
       </c>
       <c r="D338" t="n">
-        <v>2.56646097111198e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E338" t="n">
         <v>100</v>
@@ -7205,13 +7205,13 @@
         <v>337</v>
       </c>
       <c r="B339" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C339" t="n">
         <v>1</v>
       </c>
       <c r="D339" t="n">
-        <v>2.56646097111198e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E339" t="n">
         <v>100</v>
@@ -7225,13 +7225,13 @@
         <v>338</v>
       </c>
       <c r="B340" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C340" t="n">
         <v>1</v>
       </c>
       <c r="D340" t="n">
-        <v>2.56646097111198e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E340" t="n">
         <v>100</v>
@@ -7245,13 +7245,13 @@
         <v>339</v>
       </c>
       <c r="B341" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C341" t="n">
         <v>1</v>
       </c>
       <c r="D341" t="n">
-        <v>2.56646097111198e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E341" t="n">
         <v>100</v>
@@ -7265,13 +7265,13 @@
         <v>340</v>
       </c>
       <c r="B342" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C342" t="n">
         <v>1</v>
       </c>
       <c r="D342" t="n">
-        <v>2.56646097111198e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E342" t="n">
         <v>100</v>
@@ -7285,13 +7285,13 @@
         <v>341</v>
       </c>
       <c r="B343" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C343" t="n">
         <v>1</v>
       </c>
       <c r="D343" t="n">
-        <v>2.56646097111198e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E343" t="n">
         <v>100</v>
@@ -7305,13 +7305,13 @@
         <v>342</v>
       </c>
       <c r="B344" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C344" t="n">
         <v>1</v>
       </c>
       <c r="D344" t="n">
-        <v>2.410850634694344e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E344" t="n">
         <v>100</v>
@@ -7325,13 +7325,13 @@
         <v>343</v>
       </c>
       <c r="B345" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C345" t="n">
         <v>1</v>
       </c>
       <c r="D345" t="n">
-        <v>2.410850634694344e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E345" t="n">
         <v>100</v>
@@ -7345,13 +7345,13 @@
         <v>344</v>
       </c>
       <c r="B346" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C346" t="n">
         <v>1</v>
       </c>
       <c r="D346" t="n">
-        <v>2.410850634694344e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E346" t="n">
         <v>100</v>
@@ -7365,13 +7365,13 @@
         <v>345</v>
       </c>
       <c r="B347" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C347" t="n">
         <v>1</v>
       </c>
       <c r="D347" t="n">
-        <v>2.410850634694344e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E347" t="n">
         <v>100</v>
@@ -7385,13 +7385,13 @@
         <v>346</v>
       </c>
       <c r="B348" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C348" t="n">
         <v>1</v>
       </c>
       <c r="D348" t="n">
-        <v>2.410850634694344e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E348" t="n">
         <v>100</v>
@@ -7405,13 +7405,13 @@
         <v>347</v>
       </c>
       <c r="B349" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C349" t="n">
         <v>1</v>
       </c>
       <c r="D349" t="n">
-        <v>2.410850634694344e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E349" t="n">
         <v>100</v>
@@ -7425,13 +7425,13 @@
         <v>348</v>
       </c>
       <c r="B350" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C350" t="n">
         <v>1</v>
       </c>
       <c r="D350" t="n">
-        <v>2.410850634694344e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E350" t="n">
         <v>100</v>
@@ -7445,13 +7445,13 @@
         <v>349</v>
       </c>
       <c r="B351" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C351" t="n">
         <v>1</v>
       </c>
       <c r="D351" t="n">
-        <v>2.410850634694344e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E351" t="n">
         <v>100</v>
@@ -7465,13 +7465,13 @@
         <v>350</v>
       </c>
       <c r="B352" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C352" t="n">
         <v>1</v>
       </c>
       <c r="D352" t="n">
-        <v>2.410850634694344e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E352" t="n">
         <v>100</v>
@@ -7485,13 +7485,13 @@
         <v>351</v>
       </c>
       <c r="B353" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C353" t="n">
         <v>1</v>
       </c>
       <c r="D353" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E353" t="n">
         <v>100</v>
@@ -7505,13 +7505,13 @@
         <v>352</v>
       </c>
       <c r="B354" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C354" t="n">
         <v>1</v>
       </c>
       <c r="D354" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E354" t="n">
         <v>100</v>
@@ -7525,13 +7525,13 @@
         <v>353</v>
       </c>
       <c r="B355" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C355" t="n">
         <v>1</v>
       </c>
       <c r="D355" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E355" t="n">
         <v>100</v>
@@ -7545,13 +7545,13 @@
         <v>354</v>
       </c>
       <c r="B356" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C356" t="n">
         <v>1</v>
       </c>
       <c r="D356" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E356" t="n">
         <v>100</v>
@@ -7565,13 +7565,13 @@
         <v>355</v>
       </c>
       <c r="B357" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C357" t="n">
         <v>1</v>
       </c>
       <c r="D357" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E357" t="n">
         <v>100</v>
@@ -7585,13 +7585,13 @@
         <v>356</v>
       </c>
       <c r="B358" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C358" t="n">
         <v>1</v>
       </c>
       <c r="D358" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E358" t="n">
         <v>100</v>
@@ -7605,13 +7605,13 @@
         <v>357</v>
       </c>
       <c r="B359" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C359" t="n">
         <v>1</v>
       </c>
       <c r="D359" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E359" t="n">
         <v>100</v>
@@ -7625,13 +7625,13 @@
         <v>358</v>
       </c>
       <c r="B360" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C360" t="n">
         <v>1</v>
       </c>
       <c r="D360" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E360" t="n">
         <v>100</v>
@@ -7645,13 +7645,13 @@
         <v>359</v>
       </c>
       <c r="B361" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C361" t="n">
         <v>1</v>
       </c>
       <c r="D361" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E361" t="n">
         <v>100</v>
@@ -7665,13 +7665,13 @@
         <v>360</v>
       </c>
       <c r="B362" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C362" t="n">
         <v>1</v>
       </c>
       <c r="D362" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E362" t="n">
         <v>100</v>
@@ -7685,13 +7685,13 @@
         <v>361</v>
       </c>
       <c r="B363" t="n">
-        <v>44</v>
+        <v>53.6</v>
       </c>
       <c r="C363" t="n">
         <v>1</v>
       </c>
       <c r="D363" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E363" t="n">
         <v>100</v>
@@ -7705,13 +7705,13 @@
         <v>362</v>
       </c>
       <c r="B364" t="n">
-        <v>44</v>
+        <v>52.8</v>
       </c>
       <c r="C364" t="n">
         <v>1</v>
       </c>
       <c r="D364" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E364" t="n">
         <v>100</v>
@@ -7725,13 +7725,13 @@
         <v>363</v>
       </c>
       <c r="B365" t="n">
-        <v>44</v>
+        <v>52.8</v>
       </c>
       <c r="C365" t="n">
         <v>1</v>
       </c>
       <c r="D365" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E365" t="n">
         <v>100</v>
@@ -7745,13 +7745,13 @@
         <v>364</v>
       </c>
       <c r="B366" t="n">
-        <v>44</v>
+        <v>52.8</v>
       </c>
       <c r="C366" t="n">
         <v>1</v>
       </c>
       <c r="D366" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E366" t="n">
         <v>100</v>
@@ -7765,13 +7765,13 @@
         <v>365</v>
       </c>
       <c r="B367" t="n">
-        <v>43.2</v>
+        <v>52.8</v>
       </c>
       <c r="C367" t="n">
         <v>1</v>
       </c>
       <c r="D367" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E367" t="n">
         <v>100</v>
@@ -7785,13 +7785,13 @@
         <v>366</v>
       </c>
       <c r="B368" t="n">
-        <v>43.2</v>
+        <v>52</v>
       </c>
       <c r="C368" t="n">
         <v>1</v>
       </c>
       <c r="D368" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E368" t="n">
         <v>100</v>
@@ -7805,13 +7805,13 @@
         <v>367</v>
       </c>
       <c r="B369" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C369" t="n">
         <v>1</v>
       </c>
       <c r="D369" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E369" t="n">
         <v>100</v>
@@ -7825,13 +7825,13 @@
         <v>368</v>
       </c>
       <c r="B370" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C370" t="n">
         <v>1</v>
       </c>
       <c r="D370" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E370" t="n">
         <v>100</v>
@@ -7845,13 +7845,13 @@
         <v>369</v>
       </c>
       <c r="B371" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C371" t="n">
         <v>1</v>
       </c>
       <c r="D371" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E371" t="n">
         <v>100</v>
@@ -7865,13 +7865,13 @@
         <v>370</v>
       </c>
       <c r="B372" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C372" t="n">
         <v>1</v>
       </c>
       <c r="D372" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E372" t="n">
         <v>100</v>
@@ -7885,13 +7885,13 @@
         <v>371</v>
       </c>
       <c r="B373" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C373" t="n">
         <v>1</v>
       </c>
       <c r="D373" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E373" t="n">
         <v>100</v>
@@ -7905,13 +7905,13 @@
         <v>372</v>
       </c>
       <c r="B374" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C374" t="n">
         <v>1</v>
       </c>
       <c r="D374" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E374" t="n">
         <v>100</v>
@@ -7925,13 +7925,13 @@
         <v>373</v>
       </c>
       <c r="B375" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C375" t="n">
         <v>1</v>
       </c>
       <c r="D375" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.616588098140895e-08</v>
       </c>
       <c r="E375" t="n">
         <v>100</v>
@@ -7945,13 +7945,13 @@
         <v>374</v>
       </c>
       <c r="B376" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C376" t="n">
         <v>1</v>
       </c>
       <c r="D376" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E376" t="n">
         <v>100</v>
@@ -7965,13 +7965,13 @@
         <v>375</v>
       </c>
       <c r="B377" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C377" t="n">
         <v>1</v>
       </c>
       <c r="D377" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E377" t="n">
         <v>100</v>
@@ -7985,13 +7985,13 @@
         <v>376</v>
       </c>
       <c r="B378" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C378" t="n">
         <v>1</v>
       </c>
       <c r="D378" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E378" t="n">
         <v>100</v>
@@ -8005,13 +8005,13 @@
         <v>377</v>
       </c>
       <c r="B379" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C379" t="n">
         <v>1</v>
       </c>
       <c r="D379" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E379" t="n">
         <v>100</v>
@@ -8025,13 +8025,13 @@
         <v>378</v>
       </c>
       <c r="B380" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C380" t="n">
         <v>1</v>
       </c>
       <c r="D380" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E380" t="n">
         <v>100</v>
@@ -8045,13 +8045,13 @@
         <v>379</v>
       </c>
       <c r="B381" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C381" t="n">
         <v>1</v>
       </c>
       <c r="D381" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E381" t="n">
         <v>100</v>
@@ -8065,13 +8065,13 @@
         <v>380</v>
       </c>
       <c r="B382" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C382" t="n">
         <v>1</v>
       </c>
       <c r="D382" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E382" t="n">
         <v>100</v>
@@ -8085,13 +8085,13 @@
         <v>381</v>
       </c>
       <c r="B383" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C383" t="n">
         <v>1</v>
       </c>
       <c r="D383" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E383" t="n">
         <v>100</v>
@@ -8105,13 +8105,13 @@
         <v>382</v>
       </c>
       <c r="B384" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C384" t="n">
         <v>1</v>
       </c>
       <c r="D384" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E384" t="n">
         <v>100</v>
@@ -8125,13 +8125,13 @@
         <v>383</v>
       </c>
       <c r="B385" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C385" t="n">
         <v>1</v>
       </c>
       <c r="D385" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E385" t="n">
         <v>100</v>
@@ -8145,13 +8145,13 @@
         <v>384</v>
       </c>
       <c r="B386" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C386" t="n">
         <v>1</v>
       </c>
       <c r="D386" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E386" t="n">
         <v>100</v>
@@ -8165,13 +8165,13 @@
         <v>385</v>
       </c>
       <c r="B387" t="n">
-        <v>43.2</v>
+        <v>51.2</v>
       </c>
       <c r="C387" t="n">
         <v>1</v>
       </c>
       <c r="D387" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E387" t="n">
         <v>100</v>
@@ -8185,13 +8185,13 @@
         <v>386</v>
       </c>
       <c r="B388" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C388" t="n">
         <v>1</v>
       </c>
       <c r="D388" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E388" t="n">
         <v>100</v>
@@ -8205,13 +8205,13 @@
         <v>387</v>
       </c>
       <c r="B389" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C389" t="n">
         <v>1</v>
       </c>
       <c r="D389" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E389" t="n">
         <v>100</v>
@@ -8225,13 +8225,13 @@
         <v>388</v>
       </c>
       <c r="B390" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C390" t="n">
         <v>1</v>
       </c>
       <c r="D390" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E390" t="n">
         <v>100</v>
@@ -8245,13 +8245,13 @@
         <v>389</v>
       </c>
       <c r="B391" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C391" t="n">
         <v>1</v>
       </c>
       <c r="D391" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E391" t="n">
         <v>100</v>
@@ -8265,13 +8265,13 @@
         <v>390</v>
       </c>
       <c r="B392" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C392" t="n">
         <v>1</v>
       </c>
       <c r="D392" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.395341368875648e-08</v>
       </c>
       <c r="E392" t="n">
         <v>100</v>
@@ -8285,13 +8285,13 @@
         <v>391</v>
       </c>
       <c r="B393" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C393" t="n">
         <v>1</v>
       </c>
       <c r="D393" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.103368146470471e-08</v>
       </c>
       <c r="E393" t="n">
         <v>100</v>
@@ -8305,13 +8305,13 @@
         <v>392</v>
       </c>
       <c r="B394" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C394" t="n">
         <v>1</v>
       </c>
       <c r="D394" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.103368146470471e-08</v>
       </c>
       <c r="E394" t="n">
         <v>100</v>
@@ -8325,13 +8325,13 @@
         <v>393</v>
       </c>
       <c r="B395" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C395" t="n">
         <v>1</v>
       </c>
       <c r="D395" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.103368146470471e-08</v>
       </c>
       <c r="E395" t="n">
         <v>100</v>
@@ -8345,13 +8345,13 @@
         <v>394</v>
       </c>
       <c r="B396" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C396" t="n">
         <v>1</v>
       </c>
       <c r="D396" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.103368146470471e-08</v>
       </c>
       <c r="E396" t="n">
         <v>100</v>
@@ -8365,13 +8365,13 @@
         <v>395</v>
       </c>
       <c r="B397" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C397" t="n">
         <v>1</v>
       </c>
       <c r="D397" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.103368146470471e-08</v>
       </c>
       <c r="E397" t="n">
         <v>100</v>
@@ -8385,13 +8385,13 @@
         <v>396</v>
       </c>
       <c r="B398" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C398" t="n">
         <v>1</v>
       </c>
       <c r="D398" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.103368146470471e-08</v>
       </c>
       <c r="E398" t="n">
         <v>100</v>
@@ -8405,13 +8405,13 @@
         <v>397</v>
       </c>
       <c r="B399" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C399" t="n">
         <v>1</v>
       </c>
       <c r="D399" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.103368146470471e-08</v>
       </c>
       <c r="E399" t="n">
         <v>100</v>
@@ -8425,13 +8425,13 @@
         <v>398</v>
       </c>
       <c r="B400" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C400" t="n">
         <v>1</v>
       </c>
       <c r="D400" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.045022234655297e-08</v>
       </c>
       <c r="E400" t="n">
         <v>100</v>
@@ -8445,13 +8445,13 @@
         <v>399</v>
       </c>
       <c r="B401" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C401" t="n">
         <v>1</v>
       </c>
       <c r="D401" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.045022234655297e-08</v>
       </c>
       <c r="E401" t="n">
         <v>100</v>
@@ -8465,13 +8465,13 @@
         <v>400</v>
       </c>
       <c r="B402" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C402" t="n">
         <v>1</v>
       </c>
       <c r="D402" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.045022234655297e-08</v>
       </c>
       <c r="E402" t="n">
         <v>100</v>
@@ -8485,13 +8485,13 @@
         <v>401</v>
       </c>
       <c r="B403" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C403" t="n">
         <v>1</v>
       </c>
       <c r="D403" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.045022234655297e-08</v>
       </c>
       <c r="E403" t="n">
         <v>100</v>
@@ -8505,13 +8505,13 @@
         <v>402</v>
       </c>
       <c r="B404" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C404" t="n">
         <v>1</v>
       </c>
       <c r="D404" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.045022234655297e-08</v>
       </c>
       <c r="E404" t="n">
         <v>100</v>
@@ -8525,13 +8525,13 @@
         <v>403</v>
       </c>
       <c r="B405" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C405" t="n">
         <v>1</v>
       </c>
       <c r="D405" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.045022234655297e-08</v>
       </c>
       <c r="E405" t="n">
         <v>100</v>
@@ -8545,13 +8545,13 @@
         <v>404</v>
       </c>
       <c r="B406" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C406" t="n">
         <v>1</v>
       </c>
       <c r="D406" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.045022234655297e-08</v>
       </c>
       <c r="E406" t="n">
         <v>100</v>
@@ -8565,13 +8565,13 @@
         <v>405</v>
       </c>
       <c r="B407" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C407" t="n">
         <v>1</v>
       </c>
       <c r="D407" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.045022234655297e-08</v>
       </c>
       <c r="E407" t="n">
         <v>100</v>
@@ -8585,13 +8585,13 @@
         <v>406</v>
       </c>
       <c r="B408" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C408" t="n">
         <v>1</v>
       </c>
       <c r="D408" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.045022234655297e-08</v>
       </c>
       <c r="E408" t="n">
         <v>100</v>
@@ -8605,13 +8605,13 @@
         <v>407</v>
       </c>
       <c r="B409" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C409" t="n">
         <v>1</v>
       </c>
       <c r="D409" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>1.045022234655297e-08</v>
       </c>
       <c r="E409" t="n">
         <v>100</v>
@@ -8625,13 +8625,13 @@
         <v>408</v>
       </c>
       <c r="B410" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C410" t="n">
         <v>1</v>
       </c>
       <c r="D410" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E410" t="n">
         <v>100</v>
@@ -8645,13 +8645,13 @@
         <v>409</v>
       </c>
       <c r="B411" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C411" t="n">
         <v>1</v>
       </c>
       <c r="D411" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E411" t="n">
         <v>100</v>
@@ -8665,13 +8665,13 @@
         <v>410</v>
       </c>
       <c r="B412" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C412" t="n">
         <v>1</v>
       </c>
       <c r="D412" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E412" t="n">
         <v>100</v>
@@ -8685,13 +8685,13 @@
         <v>411</v>
       </c>
       <c r="B413" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C413" t="n">
         <v>1</v>
       </c>
       <c r="D413" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E413" t="n">
         <v>100</v>
@@ -8705,13 +8705,13 @@
         <v>412</v>
       </c>
       <c r="B414" t="n">
-        <v>42.40000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="C414" t="n">
         <v>1</v>
       </c>
       <c r="D414" t="n">
-        <v>2.259067506083117e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E414" t="n">
         <v>100</v>
@@ -8725,13 +8725,13 @@
         <v>413</v>
       </c>
       <c r="B415" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C415" t="n">
         <v>1</v>
       </c>
       <c r="D415" t="n">
-        <v>2.017035857269175e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E415" t="n">
         <v>100</v>
@@ -8745,13 +8745,13 @@
         <v>414</v>
       </c>
       <c r="B416" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C416" t="n">
         <v>1</v>
       </c>
       <c r="D416" t="n">
-        <v>2.017035857269175e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E416" t="n">
         <v>100</v>
@@ -8765,13 +8765,13 @@
         <v>415</v>
       </c>
       <c r="B417" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C417" t="n">
         <v>1</v>
       </c>
       <c r="D417" t="n">
-        <v>2.017035857269175e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E417" t="n">
         <v>100</v>
@@ -8785,13 +8785,13 @@
         <v>416</v>
       </c>
       <c r="B418" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C418" t="n">
         <v>1</v>
       </c>
       <c r="D418" t="n">
-        <v>2.017035857269175e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E418" t="n">
         <v>100</v>
@@ -8805,13 +8805,13 @@
         <v>417</v>
       </c>
       <c r="B419" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C419" t="n">
         <v>1</v>
       </c>
       <c r="D419" t="n">
-        <v>2.017035857269175e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E419" t="n">
         <v>100</v>
@@ -8825,13 +8825,13 @@
         <v>418</v>
       </c>
       <c r="B420" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C420" t="n">
         <v>1</v>
       </c>
       <c r="D420" t="n">
-        <v>2.017035857269175e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E420" t="n">
         <v>100</v>
@@ -8845,13 +8845,13 @@
         <v>419</v>
       </c>
       <c r="B421" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C421" t="n">
         <v>1</v>
       </c>
       <c r="D421" t="n">
-        <v>2.017035857269175e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E421" t="n">
         <v>100</v>
@@ -8865,13 +8865,13 @@
         <v>420</v>
       </c>
       <c r="B422" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C422" t="n">
         <v>1</v>
       </c>
       <c r="D422" t="n">
-        <v>1.955866602749126e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E422" t="n">
         <v>100</v>
@@ -8885,13 +8885,13 @@
         <v>421</v>
       </c>
       <c r="B423" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C423" t="n">
         <v>1</v>
       </c>
       <c r="D423" t="n">
-        <v>1.955866602749126e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E423" t="n">
         <v>100</v>
@@ -8905,13 +8905,13 @@
         <v>422</v>
       </c>
       <c r="B424" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C424" t="n">
         <v>1</v>
       </c>
       <c r="D424" t="n">
-        <v>1.955866602749126e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E424" t="n">
         <v>100</v>
@@ -8925,13 +8925,13 @@
         <v>423</v>
       </c>
       <c r="B425" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C425" t="n">
         <v>1</v>
       </c>
       <c r="D425" t="n">
-        <v>1.955866602749126e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E425" t="n">
         <v>100</v>
@@ -8945,13 +8945,13 @@
         <v>424</v>
       </c>
       <c r="B426" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C426" t="n">
         <v>1</v>
       </c>
       <c r="D426" t="n">
-        <v>1.955866602749126e-09</v>
+        <v>9.052396963198438e-09</v>
       </c>
       <c r="E426" t="n">
         <v>100</v>
@@ -8965,13 +8965,13 @@
         <v>425</v>
       </c>
       <c r="B427" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C427" t="n">
         <v>1</v>
       </c>
       <c r="D427" t="n">
-        <v>1.955866602749126e-09</v>
+        <v>8.937859309832481e-09</v>
       </c>
       <c r="E427" t="n">
         <v>100</v>
@@ -8985,13 +8985,13 @@
         <v>426</v>
       </c>
       <c r="B428" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C428" t="n">
         <v>1</v>
       </c>
       <c r="D428" t="n">
-        <v>1.955866602749126e-09</v>
+        <v>8.867011738344526e-09</v>
       </c>
       <c r="E428" t="n">
         <v>100</v>
@@ -9005,13 +9005,13 @@
         <v>427</v>
       </c>
       <c r="B429" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C429" t="n">
         <v>1</v>
       </c>
       <c r="D429" t="n">
-        <v>1.955866602749126e-09</v>
+        <v>8.867011738344526e-09</v>
       </c>
       <c r="E429" t="n">
         <v>100</v>
@@ -9025,13 +9025,13 @@
         <v>428</v>
       </c>
       <c r="B430" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C430" t="n">
         <v>1</v>
       </c>
       <c r="D430" t="n">
-        <v>1.955866602749126e-09</v>
+        <v>8.867011738344526e-09</v>
       </c>
       <c r="E430" t="n">
         <v>100</v>
@@ -9045,13 +9045,13 @@
         <v>429</v>
       </c>
       <c r="B431" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C431" t="n">
         <v>1</v>
       </c>
       <c r="D431" t="n">
-        <v>1.955866602749126e-09</v>
+        <v>7.73135640249846e-09</v>
       </c>
       <c r="E431" t="n">
         <v>100</v>
@@ -9065,13 +9065,13 @@
         <v>430</v>
       </c>
       <c r="B432" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C432" t="n">
         <v>1</v>
       </c>
       <c r="D432" t="n">
-        <v>1.955866602749126e-09</v>
+        <v>7.73135640249846e-09</v>
       </c>
       <c r="E432" t="n">
         <v>100</v>
@@ -9085,13 +9085,13 @@
         <v>431</v>
       </c>
       <c r="B433" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C433" t="n">
         <v>1</v>
       </c>
       <c r="D433" t="n">
-        <v>1.586917636782343e-09</v>
+        <v>7.73135640249846e-09</v>
       </c>
       <c r="E433" t="n">
         <v>100</v>
@@ -9105,13 +9105,13 @@
         <v>432</v>
       </c>
       <c r="B434" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C434" t="n">
         <v>1</v>
       </c>
       <c r="D434" t="n">
-        <v>1.586917636782343e-09</v>
+        <v>7.73135640249846e-09</v>
       </c>
       <c r="E434" t="n">
         <v>100</v>
@@ -9125,13 +9125,13 @@
         <v>433</v>
       </c>
       <c r="B435" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C435" t="n">
         <v>1</v>
       </c>
       <c r="D435" t="n">
-        <v>1.586917636782343e-09</v>
+        <v>7.73135640249846e-09</v>
       </c>
       <c r="E435" t="n">
         <v>100</v>
@@ -9145,13 +9145,13 @@
         <v>434</v>
       </c>
       <c r="B436" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C436" t="n">
         <v>1</v>
       </c>
       <c r="D436" t="n">
-        <v>1.586917636782343e-09</v>
+        <v>7.73135640249846e-09</v>
       </c>
       <c r="E436" t="n">
         <v>100</v>
@@ -9165,13 +9165,13 @@
         <v>435</v>
       </c>
       <c r="B437" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C437" t="n">
         <v>1</v>
       </c>
       <c r="D437" t="n">
-        <v>1.586917636782343e-09</v>
+        <v>7.73135640249846e-09</v>
       </c>
       <c r="E437" t="n">
         <v>100</v>
@@ -9185,13 +9185,13 @@
         <v>436</v>
       </c>
       <c r="B438" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C438" t="n">
         <v>1</v>
       </c>
       <c r="D438" t="n">
-        <v>1.586917636782343e-09</v>
+        <v>7.672483895106369e-09</v>
       </c>
       <c r="E438" t="n">
         <v>100</v>
@@ -9205,13 +9205,13 @@
         <v>437</v>
       </c>
       <c r="B439" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C439" t="n">
         <v>1</v>
       </c>
       <c r="D439" t="n">
-        <v>1.552721219597908e-09</v>
+        <v>7.672483895106369e-09</v>
       </c>
       <c r="E439" t="n">
         <v>100</v>
@@ -9225,13 +9225,13 @@
         <v>438</v>
       </c>
       <c r="B440" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C440" t="n">
         <v>1</v>
       </c>
       <c r="D440" t="n">
-        <v>1.552721219597908e-09</v>
+        <v>7.672483895106369e-09</v>
       </c>
       <c r="E440" t="n">
         <v>100</v>
@@ -9245,13 +9245,13 @@
         <v>439</v>
       </c>
       <c r="B441" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C441" t="n">
         <v>1</v>
       </c>
       <c r="D441" t="n">
-        <v>1.552721219597908e-09</v>
+        <v>7.546772536830528e-09</v>
       </c>
       <c r="E441" t="n">
         <v>100</v>
@@ -9265,13 +9265,13 @@
         <v>440</v>
       </c>
       <c r="B442" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C442" t="n">
         <v>1</v>
       </c>
       <c r="D442" t="n">
-        <v>1.552721219597908e-09</v>
+        <v>7.546772536830528e-09</v>
       </c>
       <c r="E442" t="n">
         <v>100</v>
@@ -9285,13 +9285,13 @@
         <v>441</v>
       </c>
       <c r="B443" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C443" t="n">
         <v>1</v>
       </c>
       <c r="D443" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>7.546772536830528e-09</v>
       </c>
       <c r="E443" t="n">
         <v>100</v>
@@ -9305,13 +9305,13 @@
         <v>442</v>
       </c>
       <c r="B444" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C444" t="n">
         <v>1</v>
       </c>
       <c r="D444" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>7.546772536830528e-09</v>
       </c>
       <c r="E444" t="n">
         <v>100</v>
@@ -9325,13 +9325,13 @@
         <v>443</v>
       </c>
       <c r="B445" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C445" t="n">
         <v>1</v>
       </c>
       <c r="D445" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>7.546772536830528e-09</v>
       </c>
       <c r="E445" t="n">
         <v>100</v>
@@ -9345,13 +9345,13 @@
         <v>444</v>
       </c>
       <c r="B446" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C446" t="n">
         <v>1</v>
       </c>
       <c r="D446" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>7.546772536830528e-09</v>
       </c>
       <c r="E446" t="n">
         <v>100</v>
@@ -9365,13 +9365,13 @@
         <v>445</v>
       </c>
       <c r="B447" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C447" t="n">
         <v>1</v>
       </c>
       <c r="D447" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>7.546772536830528e-09</v>
       </c>
       <c r="E447" t="n">
         <v>100</v>
@@ -9385,13 +9385,13 @@
         <v>446</v>
       </c>
       <c r="B448" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C448" t="n">
         <v>1</v>
       </c>
       <c r="D448" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>7.546772536830528e-09</v>
       </c>
       <c r="E448" t="n">
         <v>100</v>
@@ -9405,13 +9405,13 @@
         <v>447</v>
       </c>
       <c r="B449" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C449" t="n">
         <v>1</v>
       </c>
       <c r="D449" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>7.546772536830528e-09</v>
       </c>
       <c r="E449" t="n">
         <v>100</v>
@@ -9425,13 +9425,13 @@
         <v>448</v>
       </c>
       <c r="B450" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C450" t="n">
         <v>1</v>
       </c>
       <c r="D450" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>7.546772536830528e-09</v>
       </c>
       <c r="E450" t="n">
         <v>100</v>
@@ -9445,13 +9445,13 @@
         <v>449</v>
       </c>
       <c r="B451" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C451" t="n">
         <v>1</v>
       </c>
       <c r="D451" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>7.546772536830528e-09</v>
       </c>
       <c r="E451" t="n">
         <v>100</v>
@@ -9465,13 +9465,13 @@
         <v>450</v>
       </c>
       <c r="B452" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C452" t="n">
         <v>1</v>
       </c>
       <c r="D452" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>7.546772536830528e-09</v>
       </c>
       <c r="E452" t="n">
         <v>100</v>
@@ -9485,13 +9485,13 @@
         <v>451</v>
       </c>
       <c r="B453" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C453" t="n">
         <v>1</v>
       </c>
       <c r="D453" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>6.999657121551592e-09</v>
       </c>
       <c r="E453" t="n">
         <v>100</v>
@@ -9505,13 +9505,13 @@
         <v>452</v>
       </c>
       <c r="B454" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C454" t="n">
         <v>1</v>
       </c>
       <c r="D454" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>6.999657121551592e-09</v>
       </c>
       <c r="E454" t="n">
         <v>100</v>
@@ -9525,13 +9525,13 @@
         <v>453</v>
       </c>
       <c r="B455" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C455" t="n">
         <v>1</v>
       </c>
       <c r="D455" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>6.999657121551592e-09</v>
       </c>
       <c r="E455" t="n">
         <v>100</v>
@@ -9545,13 +9545,13 @@
         <v>454</v>
       </c>
       <c r="B456" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C456" t="n">
         <v>1</v>
       </c>
       <c r="D456" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>6.999657121551592e-09</v>
       </c>
       <c r="E456" t="n">
         <v>100</v>
@@ -9565,13 +9565,13 @@
         <v>455</v>
       </c>
       <c r="B457" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C457" t="n">
         <v>1</v>
       </c>
       <c r="D457" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>6.999657121551592e-09</v>
       </c>
       <c r="E457" t="n">
         <v>100</v>
@@ -9585,13 +9585,13 @@
         <v>456</v>
       </c>
       <c r="B458" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C458" t="n">
         <v>1</v>
       </c>
       <c r="D458" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>6.959762686493188e-09</v>
       </c>
       <c r="E458" t="n">
         <v>100</v>
@@ -9605,13 +9605,13 @@
         <v>457</v>
       </c>
       <c r="B459" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C459" t="n">
         <v>1</v>
       </c>
       <c r="D459" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>6.959762686493188e-09</v>
       </c>
       <c r="E459" t="n">
         <v>100</v>
@@ -9625,13 +9625,13 @@
         <v>458</v>
       </c>
       <c r="B460" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C460" t="n">
         <v>1</v>
       </c>
       <c r="D460" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E460" t="n">
         <v>100</v>
@@ -9645,13 +9645,13 @@
         <v>459</v>
       </c>
       <c r="B461" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C461" t="n">
         <v>1</v>
       </c>
       <c r="D461" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E461" t="n">
         <v>100</v>
@@ -9665,13 +9665,13 @@
         <v>460</v>
       </c>
       <c r="B462" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C462" t="n">
         <v>1</v>
       </c>
       <c r="D462" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E462" t="n">
         <v>100</v>
@@ -9685,13 +9685,13 @@
         <v>461</v>
       </c>
       <c r="B463" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C463" t="n">
         <v>1</v>
       </c>
       <c r="D463" t="n">
-        <v>1.433378936389457e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E463" t="n">
         <v>100</v>
@@ -9705,13 +9705,13 @@
         <v>462</v>
       </c>
       <c r="B464" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C464" t="n">
         <v>1</v>
       </c>
       <c r="D464" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E464" t="n">
         <v>100</v>
@@ -9725,13 +9725,13 @@
         <v>463</v>
       </c>
       <c r="B465" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C465" t="n">
         <v>1</v>
       </c>
       <c r="D465" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E465" t="n">
         <v>100</v>
@@ -9745,13 +9745,13 @@
         <v>464</v>
       </c>
       <c r="B466" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C466" t="n">
         <v>1</v>
       </c>
       <c r="D466" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E466" t="n">
         <v>100</v>
@@ -9765,13 +9765,13 @@
         <v>465</v>
       </c>
       <c r="B467" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C467" t="n">
         <v>1</v>
       </c>
       <c r="D467" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E467" t="n">
         <v>100</v>
@@ -9785,13 +9785,13 @@
         <v>466</v>
       </c>
       <c r="B468" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C468" t="n">
         <v>1</v>
       </c>
       <c r="D468" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E468" t="n">
         <v>100</v>
@@ -9805,13 +9805,13 @@
         <v>467</v>
       </c>
       <c r="B469" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C469" t="n">
         <v>1</v>
       </c>
       <c r="D469" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E469" t="n">
         <v>100</v>
@@ -9825,13 +9825,13 @@
         <v>468</v>
       </c>
       <c r="B470" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C470" t="n">
         <v>1</v>
       </c>
       <c r="D470" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E470" t="n">
         <v>100</v>
@@ -9845,13 +9845,13 @@
         <v>469</v>
       </c>
       <c r="B471" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C471" t="n">
         <v>1</v>
       </c>
       <c r="D471" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E471" t="n">
         <v>100</v>
@@ -9865,13 +9865,13 @@
         <v>470</v>
       </c>
       <c r="B472" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C472" t="n">
         <v>1</v>
       </c>
       <c r="D472" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E472" t="n">
         <v>100</v>
@@ -9885,13 +9885,13 @@
         <v>471</v>
       </c>
       <c r="B473" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C473" t="n">
         <v>1</v>
       </c>
       <c r="D473" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E473" t="n">
         <v>100</v>
@@ -9905,13 +9905,13 @@
         <v>472</v>
       </c>
       <c r="B474" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C474" t="n">
         <v>1</v>
       </c>
       <c r="D474" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E474" t="n">
         <v>100</v>
@@ -9925,13 +9925,13 @@
         <v>473</v>
       </c>
       <c r="B475" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C475" t="n">
         <v>1</v>
       </c>
       <c r="D475" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.931201075372849e-09</v>
       </c>
       <c r="E475" t="n">
         <v>100</v>
@@ -9945,13 +9945,13 @@
         <v>474</v>
       </c>
       <c r="B476" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C476" t="n">
         <v>1</v>
       </c>
       <c r="D476" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.830302189231453e-09</v>
       </c>
       <c r="E476" t="n">
         <v>100</v>
@@ -9965,13 +9965,13 @@
         <v>475</v>
       </c>
       <c r="B477" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C477" t="n">
         <v>1</v>
       </c>
       <c r="D477" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.830302189231453e-09</v>
       </c>
       <c r="E477" t="n">
         <v>100</v>
@@ -9985,13 +9985,13 @@
         <v>476</v>
       </c>
       <c r="B478" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C478" t="n">
         <v>1</v>
       </c>
       <c r="D478" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.830302189231453e-09</v>
       </c>
       <c r="E478" t="n">
         <v>100</v>
@@ -10005,13 +10005,13 @@
         <v>477</v>
       </c>
       <c r="B479" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C479" t="n">
         <v>1</v>
       </c>
       <c r="D479" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.830302189231453e-09</v>
       </c>
       <c r="E479" t="n">
         <v>100</v>
@@ -10025,13 +10025,13 @@
         <v>478</v>
       </c>
       <c r="B480" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C480" t="n">
         <v>1</v>
       </c>
       <c r="D480" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.830302189231453e-09</v>
       </c>
       <c r="E480" t="n">
         <v>100</v>
@@ -10045,13 +10045,13 @@
         <v>479</v>
       </c>
       <c r="B481" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C481" t="n">
         <v>1</v>
       </c>
       <c r="D481" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E481" t="n">
         <v>100</v>
@@ -10065,13 +10065,13 @@
         <v>480</v>
       </c>
       <c r="B482" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C482" t="n">
         <v>1</v>
       </c>
       <c r="D482" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E482" t="n">
         <v>100</v>
@@ -10085,13 +10085,13 @@
         <v>481</v>
       </c>
       <c r="B483" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C483" t="n">
         <v>1</v>
       </c>
       <c r="D483" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E483" t="n">
         <v>100</v>
@@ -10105,13 +10105,13 @@
         <v>482</v>
       </c>
       <c r="B484" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C484" t="n">
         <v>1</v>
       </c>
       <c r="D484" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E484" t="n">
         <v>100</v>
@@ -10125,13 +10125,13 @@
         <v>483</v>
       </c>
       <c r="B485" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C485" t="n">
         <v>1</v>
       </c>
       <c r="D485" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E485" t="n">
         <v>100</v>
@@ -10145,13 +10145,13 @@
         <v>484</v>
       </c>
       <c r="B486" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C486" t="n">
         <v>1</v>
       </c>
       <c r="D486" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E486" t="n">
         <v>100</v>
@@ -10165,13 +10165,13 @@
         <v>485</v>
       </c>
       <c r="B487" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C487" t="n">
         <v>1</v>
       </c>
       <c r="D487" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E487" t="n">
         <v>100</v>
@@ -10185,13 +10185,13 @@
         <v>486</v>
       </c>
       <c r="B488" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C488" t="n">
         <v>1</v>
       </c>
       <c r="D488" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E488" t="n">
         <v>100</v>
@@ -10205,13 +10205,13 @@
         <v>487</v>
       </c>
       <c r="B489" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C489" t="n">
         <v>1</v>
       </c>
       <c r="D489" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E489" t="n">
         <v>100</v>
@@ -10225,13 +10225,13 @@
         <v>488</v>
       </c>
       <c r="B490" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C490" t="n">
         <v>1</v>
       </c>
       <c r="D490" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E490" t="n">
         <v>100</v>
@@ -10245,13 +10245,13 @@
         <v>489</v>
       </c>
       <c r="B491" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C491" t="n">
         <v>1</v>
       </c>
       <c r="D491" t="n">
-        <v>1.274133498989139e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E491" t="n">
         <v>100</v>
@@ -10265,13 +10265,13 @@
         <v>490</v>
       </c>
       <c r="B492" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C492" t="n">
         <v>1</v>
       </c>
       <c r="D492" t="n">
-        <v>1.183621452945349e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E492" t="n">
         <v>100</v>
@@ -10285,13 +10285,13 @@
         <v>491</v>
       </c>
       <c r="B493" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C493" t="n">
         <v>1</v>
       </c>
       <c r="D493" t="n">
-        <v>1.183621452945349e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E493" t="n">
         <v>100</v>
@@ -10305,13 +10305,13 @@
         <v>492</v>
       </c>
       <c r="B494" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C494" t="n">
         <v>1</v>
       </c>
       <c r="D494" t="n">
-        <v>1.183621452945349e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E494" t="n">
         <v>100</v>
@@ -10325,13 +10325,13 @@
         <v>493</v>
       </c>
       <c r="B495" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C495" t="n">
         <v>1</v>
       </c>
       <c r="D495" t="n">
-        <v>1.183621452945349e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E495" t="n">
         <v>100</v>
@@ -10345,13 +10345,13 @@
         <v>494</v>
       </c>
       <c r="B496" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C496" t="n">
         <v>1</v>
       </c>
       <c r="D496" t="n">
-        <v>1.183621452945349e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E496" t="n">
         <v>100</v>
@@ -10365,13 +10365,13 @@
         <v>495</v>
       </c>
       <c r="B497" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C497" t="n">
         <v>1</v>
       </c>
       <c r="D497" t="n">
-        <v>1.183621452945349e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E497" t="n">
         <v>100</v>
@@ -10385,13 +10385,13 @@
         <v>496</v>
       </c>
       <c r="B498" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C498" t="n">
         <v>1</v>
       </c>
       <c r="D498" t="n">
-        <v>1.183621452945349e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E498" t="n">
         <v>100</v>
@@ -10405,13 +10405,13 @@
         <v>497</v>
       </c>
       <c r="B499" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C499" t="n">
         <v>1</v>
       </c>
       <c r="D499" t="n">
-        <v>1.183621452945349e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E499" t="n">
         <v>100</v>
@@ -10425,13 +10425,13 @@
         <v>498</v>
       </c>
       <c r="B500" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C500" t="n">
         <v>1</v>
       </c>
       <c r="D500" t="n">
-        <v>1.183621452945349e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E500" t="n">
         <v>100</v>
@@ -10445,13 +10445,13 @@
         <v>499</v>
       </c>
       <c r="B501" t="n">
-        <v>42.40000000000001</v>
+        <v>50.40000000000001</v>
       </c>
       <c r="C501" t="n">
         <v>1</v>
       </c>
       <c r="D501" t="n">
-        <v>1.183621452945349e-09</v>
+        <v>6.779064442888186e-09</v>
       </c>
       <c r="E501" t="n">
         <v>100</v>
